--- a/Comparison_polynomial_RMEP.xlsx
+++ b/Comparison_polynomial_RMEP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\MEP\RMEP_homotopy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9AFE8D-64A7-4C21-92D0-6E0538AFA47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1299C9C6-ECFB-49B2-B792-63CB552D0344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26676" yWindow="360" windowWidth="18768" windowHeight="17028" activeTab="1" xr2:uid="{7D2D116B-6D63-4BF8-9BBB-ECD7956D1860}"/>
+    <workbookView xWindow="21936" yWindow="636" windowWidth="22176" windowHeight="17028" xr2:uid="{7D2D116B-6D63-4BF8-9BBB-ECD7956D1860}"/>
   </bookViews>
   <sheets>
     <sheet name="All data" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,6 +252,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -329,7 +337,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -386,7 +394,6 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -404,6 +411,10 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -749,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E596BE4F-61BA-409F-8651-028AAF812182}">
-  <dimension ref="A1:V140"/>
+  <dimension ref="A1:V141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
@@ -2983,58 +2994,40 @@
         <v>2</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>80</v>
+        <v>5440</v>
       </c>
       <c r="H39" s="8">
-        <v>0.03</v>
+        <v>2.0400000000000001E-2</v>
       </c>
       <c r="I39" s="10">
-        <v>37.987499999999997</v>
+        <v>51.942999999999998</v>
       </c>
       <c r="J39" s="16">
-        <v>2.2060000000000001E-3</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="K39" s="16">
-        <v>0.40943000000000002</v>
+        <v>43.233600000000003</v>
       </c>
       <c r="L39" s="21">
-        <v>5.5411977591448328E-15</v>
+        <v>3.5300000000000001E-13</v>
       </c>
       <c r="M39" s="21">
-        <v>2.0918206780476542E-16</v>
-      </c>
-      <c r="N39" s="16">
-        <v>0.42109999999999997</v>
-      </c>
-      <c r="O39" s="23">
-        <v>1.2753328104930896E-12</v>
-      </c>
-      <c r="P39" s="23">
-        <v>1.3796726430865116E-13</v>
-      </c>
-      <c r="Q39" s="16">
-        <v>9.4890000000000002E-2</v>
-      </c>
-      <c r="R39" s="23">
-        <v>5.8275631765298554E-14</v>
-      </c>
-      <c r="S39" s="23">
-        <v>2.8881485371812588E-15</v>
+        <v>1.4300000000000001E-16</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
@@ -3045,7 +3038,7 @@
         <v>4</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -3057,43 +3050,43 @@
         <v>5</v>
       </c>
       <c r="G40">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="H40" s="8">
-        <v>2.6666666666666668E-2</v>
+        <v>0.03</v>
       </c>
       <c r="I40" s="10">
-        <v>38.367499999999993</v>
+        <v>37.987499999999997</v>
       </c>
       <c r="J40" s="16">
-        <v>6.3246999999999999E-3</v>
+        <v>2.2060000000000001E-3</v>
       </c>
       <c r="K40" s="16">
-        <v>1.11676252</v>
+        <v>0.40943000000000002</v>
       </c>
       <c r="L40" s="21">
-        <v>5.0466196531129296E-15</v>
+        <v>5.5411977591448328E-15</v>
       </c>
       <c r="M40" s="21">
-        <v>1.844525170398572E-16</v>
+        <v>2.0918206780476542E-16</v>
       </c>
       <c r="N40" s="16">
-        <v>3.5624355000000003</v>
+        <v>0.42109999999999997</v>
       </c>
       <c r="O40" s="23">
-        <v>1.4301884618868175E-12</v>
+        <v>1.2753328104930896E-12</v>
       </c>
       <c r="P40" s="23">
-        <v>6.7696820326208218E-14</v>
+        <v>1.3796726430865116E-13</v>
       </c>
       <c r="Q40" s="16">
-        <v>0.49177758000000005</v>
+        <v>9.4890000000000002E-2</v>
       </c>
       <c r="R40" s="23">
-        <v>2.2681627049913697E-13</v>
+        <v>5.8275631765298554E-14</v>
       </c>
       <c r="S40" s="23">
-        <v>4.8347204822169773E-15</v>
+        <v>2.8881485371812588E-15</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
@@ -3104,55 +3097,55 @@
         <v>4</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41">
         <v>5</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F41">
         <v>5</v>
       </c>
       <c r="G41">
-        <v>560</v>
+        <v>240</v>
       </c>
       <c r="H41" s="8">
-        <v>3.1785714285714285E-2</v>
+        <v>2.6666666666666668E-2</v>
       </c>
       <c r="I41" s="10">
-        <v>39.734999999999999</v>
+        <v>38.367499999999993</v>
       </c>
       <c r="J41" s="16">
-        <v>1.249682E-2</v>
+        <v>6.3246999999999999E-3</v>
       </c>
       <c r="K41" s="16">
-        <v>2.5956132799999998</v>
+        <v>1.11676252</v>
       </c>
       <c r="L41" s="21">
-        <v>5.8178984133070221E-15</v>
+        <v>5.0466196531129296E-15</v>
       </c>
       <c r="M41" s="21">
-        <v>1.7552678014687654E-16</v>
+        <v>1.844525170398572E-16</v>
       </c>
       <c r="N41" s="16">
-        <v>29.830308399999996</v>
+        <v>3.5624355000000003</v>
       </c>
       <c r="O41" s="23">
-        <v>1.0037481474353166E-10</v>
+        <v>1.4301884618868175E-12</v>
       </c>
       <c r="P41" s="23">
-        <v>5.3896923251666829E-12</v>
+        <v>6.7696820326208218E-14</v>
       </c>
       <c r="Q41" s="16">
-        <v>2.8222610800000005</v>
+        <v>0.49177758000000005</v>
       </c>
       <c r="R41" s="23">
-        <v>1.4914790289261541E-12</v>
+        <v>2.2681627049913697E-13</v>
       </c>
       <c r="S41" s="23">
-        <v>2.5131995829118702E-14</v>
+        <v>4.8347204822169773E-15</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
@@ -3163,55 +3156,55 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42">
         <v>5</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G42">
-        <v>1120</v>
+        <v>560</v>
       </c>
       <c r="H42" s="8">
-        <v>3.5178571428571427E-2</v>
+        <v>3.1785714285714285E-2</v>
       </c>
       <c r="I42" s="10">
-        <v>41.370892857142863</v>
+        <v>39.734999999999999</v>
       </c>
       <c r="J42" s="16">
-        <v>2.2536100000000003E-2</v>
+        <v>1.249682E-2</v>
       </c>
       <c r="K42" s="16">
-        <v>5.6644304600000002</v>
+        <v>2.5956132799999998</v>
       </c>
       <c r="L42" s="21">
-        <v>5.5228505323891371E-15</v>
+        <v>5.8178984133070221E-15</v>
       </c>
       <c r="M42" s="21">
-        <v>1.7217899919736916E-16</v>
+        <v>1.7552678014687654E-16</v>
       </c>
       <c r="N42" s="16">
-        <v>129.86155880000001</v>
+        <v>29.830308399999996</v>
       </c>
       <c r="O42" s="23">
-        <v>9.1508468298515182E-12</v>
+        <v>1.0037481474353166E-10</v>
       </c>
       <c r="P42" s="23">
-        <v>2.2952286460001215E-13</v>
+        <v>5.3896923251666829E-12</v>
       </c>
       <c r="Q42" s="16">
-        <v>21.385045633333334</v>
+        <v>2.8222610800000005</v>
       </c>
       <c r="R42" s="23">
-        <v>6.1631865047853873E-9</v>
+        <v>1.4914790289261541E-12</v>
       </c>
       <c r="S42" s="23">
-        <v>3.5561525458048455E-14</v>
+        <v>2.5131995829118702E-14</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
@@ -3222,7 +3215,7 @@
         <v>4</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>5</v>
@@ -3231,46 +3224,46 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>2016</v>
+        <v>1120</v>
       </c>
       <c r="H43" s="8">
-        <v>3.6111111111111108E-2</v>
+        <v>3.5178571428571427E-2</v>
       </c>
       <c r="I43" s="10">
-        <v>42.746329365079369</v>
+        <v>41.370892857142863</v>
       </c>
       <c r="J43" s="16">
-        <v>4.1797960000000002E-2</v>
+        <v>2.2536100000000003E-2</v>
       </c>
       <c r="K43" s="16">
-        <v>11.37132038</v>
+        <v>5.6644304600000002</v>
       </c>
       <c r="L43" s="21">
-        <v>1.7135494145557347E-13</v>
+        <v>5.5228505323891371E-15</v>
       </c>
       <c r="M43" s="21">
-        <v>1.6894842631138455E-16</v>
+        <v>1.7217899919736916E-16</v>
       </c>
       <c r="N43" s="16">
-        <v>510.56971420000002</v>
+        <v>129.86155880000001</v>
       </c>
       <c r="O43" s="23">
-        <v>3.5745671312275591E-11</v>
+        <v>9.1508468298515182E-12</v>
       </c>
       <c r="P43" s="23">
-        <v>8.3649453879974611E-13</v>
+        <v>2.2952286460001215E-13</v>
       </c>
       <c r="Q43" s="16">
-        <v>97.669234900000006</v>
+        <v>21.385045633333334</v>
       </c>
       <c r="R43" s="23">
-        <v>2.7430929112957775E-12</v>
+        <v>6.1631865047853873E-9</v>
       </c>
       <c r="S43" s="23">
-        <v>2.2471541500035049E-14</v>
+        <v>3.5561525458048455E-14</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
@@ -3281,10 +3274,10 @@
         <v>4</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3293,43 +3286,43 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>3360</v>
+        <v>2016</v>
       </c>
       <c r="H44" s="8">
-        <v>4.2460317460317455E-2</v>
+        <v>3.6111111111111108E-2</v>
       </c>
       <c r="I44" s="10">
-        <v>44.881150793650797</v>
+        <v>42.746329365079369</v>
       </c>
       <c r="J44" s="16">
-        <v>7.5065766666666672E-2</v>
+        <v>4.1797960000000002E-2</v>
       </c>
       <c r="K44" s="16">
-        <v>22.238960366666664</v>
+        <v>11.37132038</v>
       </c>
       <c r="L44" s="21">
-        <v>5.2531101393442403E-15</v>
+        <v>1.7135494145557347E-13</v>
       </c>
       <c r="M44" s="21">
-        <v>1.6489594436405943E-16</v>
+        <v>1.6894842631138455E-16</v>
       </c>
       <c r="N44" s="16">
-        <v>1781.36878</v>
+        <v>510.56971420000002</v>
       </c>
       <c r="O44" s="23">
-        <v>5.9507642775381909E-11</v>
+        <v>3.5745671312275591E-11</v>
       </c>
       <c r="P44" s="23">
-        <v>7.9201089920452921E-13</v>
+        <v>8.3649453879974611E-13</v>
       </c>
       <c r="Q44" s="16">
-        <v>410.93238270000001</v>
+        <v>97.669234900000006</v>
       </c>
       <c r="R44" s="23">
-        <v>1.3738714328474426E-11</v>
+        <v>2.7430929112957775E-12</v>
       </c>
       <c r="S44" s="23">
-        <v>3.0228033154174592E-14</v>
+        <v>2.2471541500035049E-14</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
@@ -3340,37 +3333,55 @@
         <v>4</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>3</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>5280</v>
+        <v>3360</v>
       </c>
       <c r="H45" s="8">
-        <v>3.9330808080808077E-2</v>
+        <v>4.2460317460317455E-2</v>
       </c>
       <c r="I45" s="10">
-        <v>45.917992424242421</v>
+        <v>44.881150793650797</v>
       </c>
       <c r="J45" s="16">
-        <v>0.11111920000000002</v>
+        <v>7.5065766666666672E-2</v>
       </c>
       <c r="K45" s="16">
-        <v>36.922244666666671</v>
+        <v>22.238960366666664</v>
       </c>
       <c r="L45" s="21">
-        <v>4.3668165427972223E-13</v>
+        <v>5.2531101393442403E-15</v>
       </c>
       <c r="M45" s="21">
-        <v>1.6669784292848789E-16</v>
+        <v>1.6489594436405943E-16</v>
+      </c>
+      <c r="N45" s="16">
+        <v>1781.36878</v>
+      </c>
+      <c r="O45" s="23">
+        <v>5.9507642775381909E-11</v>
+      </c>
+      <c r="P45" s="23">
+        <v>7.9201089920452921E-13</v>
+      </c>
+      <c r="Q45" s="16">
+        <v>410.93238270000001</v>
+      </c>
+      <c r="R45" s="23">
+        <v>1.3738714328474426E-11</v>
+      </c>
+      <c r="S45" s="23">
+        <v>3.0228033154174592E-14</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
@@ -3378,49 +3389,40 @@
         <v>2</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>192</v>
+        <v>5280</v>
       </c>
       <c r="H46" s="8">
-        <v>2.0833333333333332E-2</v>
+        <v>3.9330808080808077E-2</v>
       </c>
       <c r="I46" s="10">
-        <v>37.521875000000001</v>
+        <v>45.917992424242421</v>
       </c>
       <c r="J46" s="16">
-        <v>5.2798200000000002E-3</v>
+        <v>0.11111920000000002</v>
       </c>
       <c r="K46" s="16">
-        <v>0.97364485999999995</v>
+        <v>36.922244666666671</v>
       </c>
       <c r="L46" s="21">
-        <v>7.7012426288928069E-15</v>
+        <v>4.3668165427972223E-13</v>
       </c>
       <c r="M46" s="21">
-        <v>2.2546127372926512E-16</v>
-      </c>
-      <c r="Q46" s="16">
-        <v>0.64177055999999999</v>
-      </c>
-      <c r="R46" s="23">
-        <v>1.3538601532899307E-13</v>
-      </c>
-      <c r="S46" s="23">
-        <v>2.4996547758392413E-15</v>
+        <v>1.6669784292848789E-16</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
@@ -3431,7 +3433,7 @@
         <v>5</v>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <v>5</v>
@@ -3440,37 +3442,37 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G47">
-        <v>672</v>
+        <v>192</v>
       </c>
       <c r="H47" s="8">
-        <v>3.6309523809523805E-2</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="I47" s="10">
-        <v>39.122916666666661</v>
+        <v>37.521875000000001</v>
       </c>
       <c r="J47" s="16">
-        <v>1.3553379999999999E-2</v>
+        <v>5.2798200000000002E-3</v>
       </c>
       <c r="K47" s="16">
-        <v>3.7771544400000003</v>
+        <v>0.97364485999999995</v>
       </c>
       <c r="L47" s="21">
-        <v>7.0773985983303574E-15</v>
+        <v>7.7012426288928069E-15</v>
       </c>
       <c r="M47" s="21">
-        <v>2.0412408534367993E-16</v>
+        <v>2.2546127372926512E-16</v>
       </c>
       <c r="Q47" s="16">
-        <v>15.3490509</v>
+        <v>0.64177055999999999</v>
       </c>
       <c r="R47" s="23">
-        <v>5.4830975901819574E-13</v>
+        <v>1.3538601532899307E-13</v>
       </c>
       <c r="S47" s="23">
-        <v>7.4958552016553579E-15</v>
+        <v>2.4996547758392413E-15</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
@@ -3481,46 +3483,46 @@
         <v>5</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>1792</v>
+        <v>672</v>
       </c>
       <c r="H48" s="8">
-        <v>4.5572916666666671E-2</v>
+        <v>3.6309523809523805E-2</v>
       </c>
       <c r="I48" s="10">
-        <v>40.850446428571431</v>
+        <v>39.122916666666661</v>
       </c>
       <c r="J48" s="16">
-        <v>3.4092066666666671E-2</v>
+        <v>1.3553379999999999E-2</v>
       </c>
       <c r="K48" s="16">
-        <v>10.995266033333335</v>
+        <v>3.7771544400000003</v>
       </c>
       <c r="L48" s="21">
-        <v>7.6155857634622611E-15</v>
+        <v>7.0773985983303574E-15</v>
       </c>
       <c r="M48" s="21">
-        <v>2.010025437710582E-16</v>
+        <v>2.0412408534367993E-16</v>
       </c>
       <c r="Q48" s="16">
-        <v>146.44020839999999</v>
+        <v>15.3490509</v>
       </c>
       <c r="R48" s="23">
-        <v>5.4876961588084698E-13</v>
+        <v>5.4830975901819574E-13</v>
       </c>
       <c r="S48" s="23">
-        <v>1.1374663138028425E-14</v>
+        <v>7.4958552016553579E-15</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
@@ -3528,49 +3530,49 @@
         <v>2</v>
       </c>
       <c r="B49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>448</v>
+        <v>1792</v>
       </c>
       <c r="H49" s="8">
-        <v>2.8571428571428574E-2</v>
+        <v>4.5572916666666671E-2</v>
       </c>
       <c r="I49" s="10">
-        <v>38.336607142857147</v>
+        <v>40.850446428571431</v>
       </c>
       <c r="J49" s="16">
-        <v>1.4226260000000001E-2</v>
+        <v>3.4092066666666671E-2</v>
       </c>
       <c r="K49" s="16">
-        <v>2.7502735199999999</v>
+        <v>10.995266033333335</v>
       </c>
       <c r="L49" s="21">
-        <v>1.0027558045537166E-14</v>
+        <v>7.6155857634622611E-15</v>
       </c>
       <c r="M49" s="21">
-        <v>2.623352431143917E-16</v>
+        <v>2.010025437710582E-16</v>
       </c>
       <c r="Q49" s="16">
-        <v>20.133113666666667</v>
+        <v>146.44020839999999</v>
       </c>
       <c r="R49" s="23">
-        <v>1.77070626788881E-13</v>
+        <v>5.4876961588084698E-13</v>
       </c>
       <c r="S49" s="23">
-        <v>3.7307312077875035E-15</v>
+        <v>1.1374663138028425E-14</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
@@ -3581,37 +3583,46 @@
         <v>6</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>1792</v>
+        <v>448</v>
       </c>
       <c r="H50" s="8">
-        <v>5.1525297619047616E-2</v>
+        <v>2.8571428571428574E-2</v>
       </c>
       <c r="I50" s="10">
-        <v>40.155133928571431</v>
+        <v>38.336607142857147</v>
       </c>
       <c r="J50" s="16">
-        <v>4.8115899999999996E-2</v>
+        <v>1.4226260000000001E-2</v>
       </c>
       <c r="K50" s="16">
-        <v>12.103082633333335</v>
+        <v>2.7502735199999999</v>
       </c>
       <c r="L50" s="21">
-        <v>9.4005214162338586E-15</v>
+        <v>1.0027558045537166E-14</v>
       </c>
       <c r="M50" s="21">
-        <v>2.3151209136168151E-16</v>
+        <v>2.623352431143917E-16</v>
+      </c>
+      <c r="Q50" s="16">
+        <v>20.133113666666667</v>
+      </c>
+      <c r="R50" s="23">
+        <v>1.77070626788881E-13</v>
+      </c>
+      <c r="S50" s="23">
+        <v>3.7307312077875035E-15</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
@@ -3619,10 +3630,10 @@
         <v>2</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -3631,37 +3642,28 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>1024</v>
+        <v>1792</v>
       </c>
       <c r="H51" s="8">
-        <v>3.90625E-2</v>
+        <v>5.1525297619047616E-2</v>
       </c>
       <c r="I51" s="10">
-        <v>40.292317708333336</v>
+        <v>40.155133928571431</v>
       </c>
       <c r="J51" s="16">
-        <v>1.5277866666666667E-2</v>
+        <v>4.8115899999999996E-2</v>
       </c>
       <c r="K51" s="16">
-        <v>8.2437618666666665</v>
+        <v>12.103082633333335</v>
       </c>
       <c r="L51" s="21">
-        <v>1.2370194975965103E-14</v>
+        <v>9.4005214162338586E-15</v>
       </c>
       <c r="M51" s="21">
-        <v>2.7334373418993603E-16</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>797.36940379999999</v>
-      </c>
-      <c r="R51" s="23">
-        <v>2.8661044400920579E-13</v>
-      </c>
-      <c r="S51" s="23">
-        <v>3.3051754626257715E-15</v>
+        <v>2.3151209136168151E-16</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
@@ -3669,90 +3671,90 @@
         <v>2</v>
       </c>
       <c r="B52">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
         <v>1</v>
       </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
       <c r="G52">
-        <v>11264</v>
+        <v>1024</v>
       </c>
       <c r="H52" s="8">
-        <v>5.3799715909090912E-2</v>
+        <v>3.90625E-2</v>
       </c>
       <c r="I52" s="10">
-        <v>42.40740411931818</v>
+        <v>40.292317708333336</v>
       </c>
       <c r="J52" s="16">
-        <v>6.02141E-2</v>
+        <v>1.5277866666666667E-2</v>
       </c>
       <c r="K52" s="16">
-        <v>175.04502500000001</v>
+        <v>8.2437618666666665</v>
       </c>
       <c r="L52" s="21">
-        <v>1.8098700965739456E-14</v>
+        <v>1.2370194975965103E-14</v>
       </c>
       <c r="M52" s="21">
-        <v>3.4063769655942642E-16</v>
+        <v>2.7334373418993603E-16</v>
+      </c>
+      <c r="Q52" s="16">
+        <v>797.36940379999999</v>
+      </c>
+      <c r="R52" s="23">
+        <v>2.8661044400920579E-13</v>
+      </c>
+      <c r="S52" s="23">
+        <v>3.3051754626257715E-15</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C53">
         <v>2</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>27</v>
+        <v>11264</v>
       </c>
       <c r="H53" s="8">
-        <v>0</v>
+        <v>5.3799715909090912E-2</v>
       </c>
       <c r="I53" s="10">
-        <v>32.888888888888893</v>
+        <v>42.40740411931818</v>
       </c>
       <c r="J53" s="16">
-        <v>6.3906E-4</v>
+        <v>6.02141E-2</v>
       </c>
       <c r="K53" s="16">
-        <v>9.1658920000000005E-2</v>
+        <v>175.04502500000001</v>
       </c>
       <c r="L53" s="21">
-        <v>4.2561687641530617E-15</v>
+        <v>1.8098700965739456E-14</v>
       </c>
       <c r="M53" s="21">
-        <v>2.2130258298635054E-16</v>
-      </c>
-      <c r="Q53" s="16">
-        <v>2.854508E-2</v>
-      </c>
-      <c r="R53" s="23">
-        <v>3.1801846599262689E-14</v>
-      </c>
-      <c r="S53" s="23">
-        <v>3.4381277284581695E-15</v>
+        <v>3.4063769655942642E-16</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
@@ -3763,7 +3765,7 @@
         <v>2</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>5</v>
@@ -3775,34 +3777,34 @@
         <v>5</v>
       </c>
       <c r="G54">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="H54" s="8">
-        <v>1.4814814814814815E-2</v>
+        <v>0</v>
       </c>
       <c r="I54" s="10">
-        <v>36.077777777777776</v>
+        <v>32.888888888888893</v>
       </c>
       <c r="J54" s="16">
-        <v>9.5416000000000012E-4</v>
+        <v>6.3906E-4</v>
       </c>
       <c r="K54" s="16">
-        <v>0.20890132</v>
+        <v>9.1658920000000005E-2</v>
       </c>
       <c r="L54" s="21">
-        <v>4.0318335620883405E-15</v>
+        <v>4.2561687641530617E-15</v>
       </c>
       <c r="M54" s="21">
-        <v>1.6759670384501726E-16</v>
+        <v>2.2130258298635054E-16</v>
       </c>
       <c r="Q54" s="16">
-        <v>5.1364100000000003E-2</v>
+        <v>2.854508E-2</v>
       </c>
       <c r="R54" s="23">
-        <v>1.3323654782831806E-14</v>
+        <v>3.1801846599262689E-14</v>
       </c>
       <c r="S54" s="23">
-        <v>1.0357403266142049E-15</v>
+        <v>3.4381277284581695E-15</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
@@ -3813,7 +3815,7 @@
         <v>2</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D55">
         <v>5</v>
@@ -3825,34 +3827,34 @@
         <v>5</v>
       </c>
       <c r="G55">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="H55" s="8">
-        <v>8.8888888888888889E-3</v>
+        <v>1.4814814814814815E-2</v>
       </c>
       <c r="I55" s="10">
-        <v>37.906666666666666</v>
+        <v>36.077777777777776</v>
       </c>
       <c r="J55" s="16">
-        <v>1.29378E-3</v>
+        <v>9.5416000000000012E-4</v>
       </c>
       <c r="K55" s="16">
-        <v>0.33099373999999998</v>
+        <v>0.20890132</v>
       </c>
       <c r="L55" s="21">
-        <v>4.9287079446836793E-15</v>
+        <v>4.0318335620883405E-15</v>
       </c>
       <c r="M55" s="21">
-        <v>1.5261196194494654E-16</v>
+        <v>1.6759670384501726E-16</v>
       </c>
       <c r="Q55" s="16">
-        <v>8.743244E-2</v>
+        <v>5.1364100000000003E-2</v>
       </c>
       <c r="R55" s="23">
-        <v>4.6025915760122612E-14</v>
+        <v>1.3323654782831806E-14</v>
       </c>
       <c r="S55" s="23">
-        <v>1.3676050933226177E-15</v>
+        <v>1.0357403266142049E-15</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
@@ -3863,7 +3865,7 @@
         <v>2</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D56">
         <v>5</v>
@@ -3875,34 +3877,34 @@
         <v>5</v>
       </c>
       <c r="G56">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="H56" s="8">
-        <v>2.074074074074074E-2</v>
+        <v>8.8888888888888889E-3</v>
       </c>
       <c r="I56" s="10">
-        <v>40.038518518518515</v>
+        <v>37.906666666666666</v>
       </c>
       <c r="J56" s="16">
-        <v>1.5685800000000004E-3</v>
+        <v>1.29378E-3</v>
       </c>
       <c r="K56" s="16">
-        <v>0.58145332000000005</v>
+        <v>0.33099373999999998</v>
       </c>
       <c r="L56" s="21">
-        <v>4.9445411614644109E-15</v>
+        <v>4.9287079446836793E-15</v>
       </c>
       <c r="M56" s="21">
-        <v>1.5466924252457587E-16</v>
+        <v>1.5261196194494654E-16</v>
       </c>
       <c r="Q56" s="16">
-        <v>0.1536121</v>
+        <v>8.743244E-2</v>
       </c>
       <c r="R56" s="23">
-        <v>8.8553182149461077E-14</v>
+        <v>4.6025915760122612E-14</v>
       </c>
       <c r="S56" s="23">
-        <v>2.8675364011584599E-15</v>
+        <v>1.3676050933226177E-15</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
@@ -3913,7 +3915,7 @@
         <v>2</v>
       </c>
       <c r="C57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57">
         <v>5</v>
@@ -3925,34 +3927,34 @@
         <v>5</v>
       </c>
       <c r="G57">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="H57" s="8">
-        <v>1.9047619047619049E-2</v>
+        <v>2.074074074074074E-2</v>
       </c>
       <c r="I57" s="10">
-        <v>42.395767195767192</v>
+        <v>40.038518518518515</v>
       </c>
       <c r="J57" s="16">
-        <v>1.9922199999999998E-3</v>
+        <v>1.5685800000000004E-3</v>
       </c>
       <c r="K57" s="16">
-        <v>0.88395478000000005</v>
+        <v>0.58145332000000005</v>
       </c>
       <c r="L57" s="21">
-        <v>4.7806894080492796E-15</v>
+        <v>4.9445411614644109E-15</v>
       </c>
       <c r="M57" s="21">
-        <v>1.5371268637982109E-16</v>
+        <v>1.5466924252457587E-16</v>
       </c>
       <c r="Q57" s="16">
-        <v>0.27204255999999999</v>
+        <v>0.1536121</v>
       </c>
       <c r="R57" s="23">
-        <v>7.7780423021763885E-12</v>
+        <v>8.8553182149461077E-14</v>
       </c>
       <c r="S57" s="23">
-        <v>3.3579250912144337E-14</v>
+        <v>2.8675364011584599E-15</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
@@ -3963,7 +3965,7 @@
         <v>2</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <v>5</v>
@@ -3975,34 +3977,34 @@
         <v>5</v>
       </c>
       <c r="G58">
-        <v>252</v>
+        <v>189</v>
       </c>
       <c r="H58" s="8">
-        <v>1.4285714285714287E-2</v>
+        <v>1.9047619047619049E-2</v>
       </c>
       <c r="I58" s="10">
-        <v>43.134920634920633</v>
+        <v>42.395767195767192</v>
       </c>
       <c r="J58" s="16">
-        <v>2.2715399999999998E-3</v>
+        <v>1.9922199999999998E-3</v>
       </c>
       <c r="K58" s="16">
-        <v>1.1752707599999999</v>
+        <v>0.88395478000000005</v>
       </c>
       <c r="L58" s="21">
-        <v>8.5891947603418365E-15</v>
+        <v>4.7806894080492796E-15</v>
       </c>
       <c r="M58" s="21">
-        <v>1.5513964501155206E-16</v>
+        <v>1.5371268637982109E-16</v>
       </c>
       <c r="Q58" s="16">
-        <v>0.49989713999999996</v>
+        <v>0.27204255999999999</v>
       </c>
       <c r="R58" s="23">
-        <v>2.4386587112576128E-12</v>
+        <v>7.7780423021763885E-12</v>
       </c>
       <c r="S58" s="23">
-        <v>2.0429834921376438E-14</v>
+        <v>3.3579250912144337E-14</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
@@ -4013,7 +4015,7 @@
         <v>2</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D59">
         <v>5</v>
@@ -4025,34 +4027,34 @@
         <v>5</v>
       </c>
       <c r="G59">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="H59" s="8">
-        <v>1.4814814814814815E-2</v>
+        <v>1.4285714285714287E-2</v>
       </c>
       <c r="I59" s="10">
-        <v>43.688271604938265</v>
+        <v>43.134920634920633</v>
       </c>
       <c r="J59" s="16">
-        <v>2.9870000000000001E-3</v>
+        <v>2.2715399999999998E-3</v>
       </c>
       <c r="K59" s="16">
-        <v>1.5456309799999999</v>
+        <v>1.1752707599999999</v>
       </c>
       <c r="L59" s="21">
-        <v>5.121666949634972E-15</v>
+        <v>8.5891947603418365E-15</v>
       </c>
       <c r="M59" s="21">
-        <v>1.5208937681619583E-16</v>
+        <v>1.5513964501155206E-16</v>
       </c>
       <c r="Q59" s="16">
-        <v>0.86330987999999986</v>
+        <v>0.49989713999999996</v>
       </c>
       <c r="R59" s="23">
-        <v>7.9595269932831912E-11</v>
+        <v>2.4386587112576128E-12</v>
       </c>
       <c r="S59" s="23">
-        <v>2.2173494654568662E-14</v>
+        <v>2.0429834921376438E-14</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
@@ -4063,7 +4065,7 @@
         <v>2</v>
       </c>
       <c r="C60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D60">
         <v>5</v>
@@ -4075,34 +4077,34 @@
         <v>5</v>
       </c>
       <c r="G60">
-        <v>405</v>
+        <v>324</v>
       </c>
       <c r="H60" s="8">
-        <v>1.8765432098765432E-2</v>
+        <v>1.4814814814814815E-2</v>
       </c>
       <c r="I60" s="10">
-        <v>45.894814814814815</v>
+        <v>43.688271604938265</v>
       </c>
       <c r="J60" s="16">
-        <v>3.6194600000000001E-3</v>
+        <v>2.9870000000000001E-3</v>
       </c>
       <c r="K60" s="16">
-        <v>2.2644156999999998</v>
+        <v>1.5456309799999999</v>
       </c>
       <c r="L60" s="21">
-        <v>5.1193607210505721E-15</v>
+        <v>5.121666949634972E-15</v>
       </c>
       <c r="M60" s="21">
-        <v>1.5345349550103896E-16</v>
+        <v>1.5208937681619583E-16</v>
       </c>
       <c r="Q60" s="16">
-        <v>1.3349343</v>
+        <v>0.86330987999999986</v>
       </c>
       <c r="R60" s="23">
-        <v>3.6627653547964979E-11</v>
+        <v>7.9595269932831912E-11</v>
       </c>
       <c r="S60" s="23">
-        <v>3.048213121728625E-13</v>
+        <v>2.2173494654568662E-14</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.3">
@@ -4113,7 +4115,7 @@
         <v>2</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D61">
         <v>5</v>
@@ -4125,34 +4127,34 @@
         <v>5</v>
       </c>
       <c r="G61">
-        <v>495</v>
+        <v>405</v>
       </c>
       <c r="H61" s="8">
-        <v>1.1313131313131311E-2</v>
+        <v>1.8765432098765432E-2</v>
       </c>
       <c r="I61" s="10">
-        <v>46.256161616161613</v>
+        <v>45.894814814814815</v>
       </c>
       <c r="J61" s="16">
-        <v>4.4704000000000002E-3</v>
+        <v>3.6194600000000001E-3</v>
       </c>
       <c r="K61" s="16">
-        <v>2.9446504199999999</v>
+        <v>2.2644156999999998</v>
       </c>
       <c r="L61" s="21">
-        <v>4.8462105104512981E-15</v>
+        <v>5.1193607210505721E-15</v>
       </c>
       <c r="M61" s="21">
-        <v>1.5244407417773821E-16</v>
+        <v>1.5345349550103896E-16</v>
       </c>
       <c r="Q61" s="16">
-        <v>2.3797572799999998</v>
+        <v>1.3349343</v>
       </c>
       <c r="R61" s="23">
-        <v>6.1081652289869181E-11</v>
+        <v>3.6627653547964979E-11</v>
       </c>
       <c r="S61" s="23">
-        <v>1.798660276248687E-13</v>
+        <v>3.048213121728625E-13</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
@@ -4163,7 +4165,7 @@
         <v>2</v>
       </c>
       <c r="C62">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D62">
         <v>5</v>
@@ -4175,34 +4177,34 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>594</v>
+        <v>495</v>
       </c>
       <c r="H62" s="8">
-        <v>9.427609427609427E-3</v>
+        <v>1.1313131313131311E-2</v>
       </c>
       <c r="I62" s="10">
-        <v>47.626936026936022</v>
+        <v>46.256161616161613</v>
       </c>
       <c r="J62" s="16">
-        <v>5.2147000000000001E-3</v>
+        <v>4.4704000000000002E-3</v>
       </c>
       <c r="K62" s="16">
-        <v>3.7090702800000002</v>
+        <v>2.9446504199999999</v>
       </c>
       <c r="L62" s="21">
-        <v>5.3718406056918642E-15</v>
+        <v>4.8462105104512981E-15</v>
       </c>
       <c r="M62" s="21">
-        <v>1.4995801321839486E-16</v>
+        <v>1.5244407417773821E-16</v>
       </c>
       <c r="Q62" s="16">
-        <v>3.9744627600000002</v>
+        <v>2.3797572799999998</v>
       </c>
       <c r="R62" s="23">
-        <v>5.3068194552882293E-10</v>
+        <v>6.1081652289869181E-11</v>
       </c>
       <c r="S62" s="23">
-        <v>2.1401030438504456E-12</v>
+        <v>1.798660276248687E-13</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.3">
@@ -4213,7 +4215,7 @@
         <v>2</v>
       </c>
       <c r="C63">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D63">
         <v>5</v>
@@ -4225,34 +4227,34 @@
         <v>5</v>
       </c>
       <c r="G63">
-        <v>702</v>
+        <v>594</v>
       </c>
       <c r="H63" s="8">
-        <v>1.4814814814814815E-2</v>
+        <v>9.427609427609427E-3</v>
       </c>
       <c r="I63" s="10">
-        <v>49.31424501424501</v>
+        <v>47.626936026936022</v>
       </c>
       <c r="J63" s="16">
-        <v>6.2795600000000009E-3</v>
+        <v>5.2147000000000001E-3</v>
       </c>
       <c r="K63" s="16">
-        <v>4.4542152000000002</v>
+        <v>3.7090702800000002</v>
       </c>
       <c r="L63" s="21">
-        <v>4.9115120590150871E-15</v>
+        <v>5.3718406056918642E-15</v>
       </c>
       <c r="M63" s="21">
-        <v>1.499955509666691E-16</v>
+        <v>1.4995801321839486E-16</v>
       </c>
       <c r="Q63" s="16">
-        <v>5.9765022200000004</v>
+        <v>3.9744627600000002</v>
       </c>
       <c r="R63" s="23">
-        <v>1.0453560804755489E-9</v>
+        <v>5.3068194552882293E-10</v>
       </c>
       <c r="S63" s="23">
-        <v>2.4175477964734426E-12</v>
+        <v>2.1401030438504456E-12</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
@@ -4263,7 +4265,7 @@
         <v>2</v>
       </c>
       <c r="C64">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D64">
         <v>5</v>
@@ -4275,34 +4277,34 @@
         <v>5</v>
       </c>
       <c r="G64">
-        <v>819</v>
+        <v>702</v>
       </c>
       <c r="H64" s="8">
-        <v>1.0744810744810745E-2</v>
+        <v>1.4814814814814815E-2</v>
       </c>
       <c r="I64" s="10">
-        <v>49.301587301587304</v>
+        <v>49.31424501424501</v>
       </c>
       <c r="J64" s="16">
-        <v>7.0409000000000001E-3</v>
+        <v>6.2795600000000009E-3</v>
       </c>
       <c r="K64" s="16">
-        <v>5.0332620600000002</v>
+        <v>4.4542152000000002</v>
       </c>
       <c r="L64" s="21">
-        <v>2.6856740084769089E-14</v>
+        <v>4.9115120590150871E-15</v>
       </c>
       <c r="M64" s="21">
-        <v>1.5149843432339006E-16</v>
+        <v>1.499955509666691E-16</v>
       </c>
       <c r="Q64" s="16">
-        <v>8.5986568400000003</v>
+        <v>5.9765022200000004</v>
       </c>
       <c r="R64" s="23">
-        <v>1.7398328697587679E-8</v>
+        <v>1.0453560804755489E-9</v>
       </c>
       <c r="S64" s="23">
-        <v>1.4951519136776875E-12</v>
+        <v>2.4175477964734426E-12</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.3">
@@ -4313,7 +4315,7 @@
         <v>2</v>
       </c>
       <c r="C65">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D65">
         <v>5</v>
@@ -4325,34 +4327,34 @@
         <v>5</v>
       </c>
       <c r="G65">
-        <v>945</v>
+        <v>819</v>
       </c>
       <c r="H65" s="8">
-        <v>1.1005291005291006E-2</v>
+        <v>1.0744810744810745E-2</v>
       </c>
       <c r="I65" s="10">
-        <v>51.080423280423275</v>
+        <v>49.301587301587304</v>
       </c>
       <c r="J65" s="16">
-        <v>7.9940000000000011E-3</v>
+        <v>7.0409000000000001E-3</v>
       </c>
       <c r="K65" s="16">
-        <v>6.4888700200000002</v>
+        <v>5.0332620600000002</v>
       </c>
       <c r="L65" s="21">
-        <v>4.1352117217316967E-14</v>
+        <v>2.6856740084769089E-14</v>
       </c>
       <c r="M65" s="21">
-        <v>1.4984208065773374E-16</v>
+        <v>1.5149843432339006E-16</v>
       </c>
       <c r="Q65" s="16">
-        <v>13.158509120000002</v>
+        <v>8.5986568400000003</v>
       </c>
       <c r="R65" s="23">
-        <v>2.6602565171133452E-8</v>
+        <v>1.7398328697587679E-8</v>
       </c>
       <c r="S65" s="23">
-        <v>1.714532272295522E-11</v>
+        <v>1.4951519136776875E-12</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.3">
@@ -4363,7 +4365,7 @@
         <v>2</v>
       </c>
       <c r="C66">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D66">
         <v>5</v>
@@ -4372,37 +4374,37 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G66">
-        <v>1080</v>
+        <v>945</v>
       </c>
       <c r="H66" s="8">
-        <v>1.2592592592592593E-2</v>
+        <v>1.1005291005291006E-2</v>
       </c>
       <c r="I66" s="10">
-        <v>52.029999999999994</v>
+        <v>51.080423280423275</v>
       </c>
       <c r="J66" s="16">
-        <v>9.1368999999999999E-3</v>
+        <v>7.9940000000000011E-3</v>
       </c>
       <c r="K66" s="16">
-        <v>7.7876606600000002</v>
+        <v>6.4888700200000002</v>
       </c>
       <c r="L66" s="21">
-        <v>7.922083915529233E-15</v>
+        <v>4.1352117217316967E-14</v>
       </c>
       <c r="M66" s="21">
-        <v>1.5161839517376015E-16</v>
+        <v>1.4984208065773374E-16</v>
       </c>
       <c r="Q66" s="16">
-        <v>20.056435433333334</v>
+        <v>13.158509120000002</v>
       </c>
       <c r="R66" s="23">
-        <v>1.0943507746216213E-8</v>
+        <v>2.6602565171133452E-8</v>
       </c>
       <c r="S66" s="23">
-        <v>4.7120867676474765E-11</v>
+        <v>1.714532272295522E-11</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.3">
@@ -4410,10 +4412,10 @@
         <v>3</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D67">
         <v>5</v>
@@ -4422,37 +4424,37 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>108</v>
+        <v>1080</v>
       </c>
       <c r="H67" s="8">
-        <v>3.7037037037037035E-2</v>
+        <v>1.2592592592592593E-2</v>
       </c>
       <c r="I67" s="10">
-        <v>36.062962962962963</v>
+        <v>52.029999999999994</v>
       </c>
       <c r="J67" s="16">
-        <v>1.0230600000000001E-3</v>
+        <v>9.1368999999999999E-3</v>
       </c>
       <c r="K67" s="16">
-        <v>0.51993237999999997</v>
+        <v>7.7876606600000002</v>
       </c>
       <c r="L67" s="21">
-        <v>8.0020207020319176E-15</v>
+        <v>7.922083915529233E-15</v>
       </c>
       <c r="M67" s="21">
-        <v>2.6401356046232522E-16</v>
+        <v>1.5161839517376015E-16</v>
       </c>
       <c r="Q67" s="16">
-        <v>0.13805464000000001</v>
+        <v>20.056435433333334</v>
       </c>
       <c r="R67" s="23">
-        <v>6.1742403055698919E-14</v>
+        <v>1.0943507746216213E-8</v>
       </c>
       <c r="S67" s="23">
-        <v>2.7898030880139854E-15</v>
+        <v>4.7120867676474765E-11</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
@@ -4463,7 +4465,7 @@
         <v>3</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D68">
         <v>5</v>
@@ -4475,34 +4477,34 @@
         <v>5</v>
       </c>
       <c r="G68">
-        <v>270</v>
+        <v>108</v>
       </c>
       <c r="H68" s="8">
-        <v>2.5185185185185182E-2</v>
+        <v>3.7037037037037035E-2</v>
       </c>
       <c r="I68" s="10">
-        <v>36.760000000000005</v>
+        <v>36.062962962962963</v>
       </c>
       <c r="J68" s="16">
-        <v>1.9344199999999998E-3</v>
+        <v>1.0230600000000001E-3</v>
       </c>
       <c r="K68" s="16">
-        <v>1.2148881799999998</v>
+        <v>0.51993237999999997</v>
       </c>
       <c r="L68" s="21">
-        <v>7.9456773098599116E-15</v>
+        <v>8.0020207020319176E-15</v>
       </c>
       <c r="M68" s="21">
-        <v>2.1012998842695789E-16</v>
+        <v>2.6401356046232522E-16</v>
       </c>
       <c r="Q68" s="16">
-        <v>0.50736621999999998</v>
+        <v>0.13805464000000001</v>
       </c>
       <c r="R68" s="23">
-        <v>2.6559135752706161E-13</v>
+        <v>6.1742403055698919E-14</v>
       </c>
       <c r="S68" s="23">
-        <v>5.1377607995568668E-15</v>
+        <v>2.7898030880139854E-15</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
@@ -4513,7 +4515,7 @@
         <v>3</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D69">
         <v>5</v>
@@ -4525,34 +4527,34 @@
         <v>5</v>
       </c>
       <c r="G69">
-        <v>540</v>
+        <v>270</v>
       </c>
       <c r="H69" s="8">
-        <v>3.6666666666666667E-2</v>
+        <v>2.5185185185185182E-2</v>
       </c>
       <c r="I69" s="10">
-        <v>39.660000000000004</v>
+        <v>36.760000000000005</v>
       </c>
       <c r="J69" s="16">
-        <v>3.2444999999999996E-3</v>
+        <v>1.9344199999999998E-3</v>
       </c>
       <c r="K69" s="16">
-        <v>2.6355545600000001</v>
+        <v>1.2148881799999998</v>
       </c>
       <c r="L69" s="21">
-        <v>8.3015967425098647E-15</v>
+        <v>7.9456773098599116E-15</v>
       </c>
       <c r="M69" s="21">
-        <v>1.9672985433899646E-16</v>
+        <v>2.1012998842695789E-16</v>
       </c>
       <c r="Q69" s="16">
-        <v>1.7538317999999999</v>
+        <v>0.50736621999999998</v>
       </c>
       <c r="R69" s="23">
-        <v>1.5960329950476179E-12</v>
+        <v>2.6559135752706161E-13</v>
       </c>
       <c r="S69" s="23">
-        <v>1.7539978609927137E-14</v>
+        <v>5.1377607995568668E-15</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
@@ -4563,7 +4565,7 @@
         <v>3</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <v>5</v>
@@ -4575,34 +4577,34 @@
         <v>5</v>
       </c>
       <c r="G70">
-        <v>945</v>
+        <v>540</v>
       </c>
       <c r="H70" s="8">
-        <v>2.6455026455026457E-2</v>
+        <v>3.6666666666666667E-2</v>
       </c>
       <c r="I70" s="10">
-        <v>40.404656084656082</v>
+        <v>39.660000000000004</v>
       </c>
       <c r="J70" s="16">
-        <v>4.7960599999999996E-3</v>
+        <v>3.2444999999999996E-3</v>
       </c>
       <c r="K70" s="16">
-        <v>5.0415852799999996</v>
+        <v>2.6355545600000001</v>
       </c>
       <c r="L70" s="21">
-        <v>8.5804174987120619E-15</v>
+        <v>8.3015967425098647E-15</v>
       </c>
       <c r="M70" s="21">
-        <v>1.9466751076203014E-16</v>
+        <v>1.9672985433899646E-16</v>
       </c>
       <c r="Q70" s="16">
-        <v>6.6834589399999995</v>
+        <v>1.7538317999999999</v>
       </c>
       <c r="R70" s="23">
-        <v>2.623802334192494E-12</v>
+        <v>1.5960329950476179E-12</v>
       </c>
       <c r="S70" s="23">
-        <v>2.2520916826954586E-14</v>
+        <v>1.7539978609927137E-14</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
@@ -4613,7 +4615,7 @@
         <v>3</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D71">
         <v>5</v>
@@ -4622,37 +4624,37 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G71">
-        <v>1512</v>
+        <v>945</v>
       </c>
       <c r="H71" s="8">
-        <v>2.9497354497354498E-2</v>
+        <v>2.6455026455026457E-2</v>
       </c>
       <c r="I71" s="10">
-        <v>42.146031746031746</v>
+        <v>40.404656084656082</v>
       </c>
       <c r="J71" s="16">
-        <v>7.5474399999999999E-3</v>
+        <v>4.7960599999999996E-3</v>
       </c>
       <c r="K71" s="16">
-        <v>8.8886184400000001</v>
+        <v>5.0415852799999996</v>
       </c>
       <c r="L71" s="21">
-        <v>8.9624879229879406E-15</v>
+        <v>8.5804174987120619E-15</v>
       </c>
       <c r="M71" s="21">
-        <v>1.9137951661432257E-16</v>
+        <v>1.9466751076203014E-16</v>
       </c>
       <c r="Q71" s="16">
-        <v>24.829009833333334</v>
+        <v>6.6834589399999995</v>
       </c>
       <c r="R71" s="23">
-        <v>2.984175967336341E-11</v>
+        <v>2.623802334192494E-12</v>
       </c>
       <c r="S71" s="23">
-        <v>3.8407648070897666E-14</v>
+        <v>2.2520916826954586E-14</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
@@ -4663,46 +4665,46 @@
         <v>3</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G72">
-        <v>2268</v>
+        <v>1512</v>
       </c>
       <c r="H72" s="8">
-        <v>2.9394473838918286E-2</v>
+        <v>2.9497354497354498E-2</v>
       </c>
       <c r="I72" s="10">
-        <v>43.35479129923575</v>
+        <v>42.146031746031746</v>
       </c>
       <c r="J72" s="16">
-        <v>1.0613766666666668E-2</v>
+        <v>7.5474399999999999E-3</v>
       </c>
       <c r="K72" s="16">
-        <v>14.110998100000002</v>
+        <v>8.8886184400000001</v>
       </c>
       <c r="L72" s="21">
-        <v>8.4688324952415906E-15</v>
+        <v>8.9624879229879406E-15</v>
       </c>
       <c r="M72" s="21">
-        <v>1.8858153624902753E-16</v>
+        <v>1.9137951661432257E-16</v>
       </c>
       <c r="Q72" s="16">
-        <v>96.311044699999997</v>
+        <v>24.829009833333334</v>
       </c>
       <c r="R72" s="23">
-        <v>2.4540004226204457E-11</v>
+        <v>2.984175967336341E-11</v>
       </c>
       <c r="S72" s="23">
-        <v>1.9252283186548664E-13</v>
+        <v>3.8407648070897666E-14</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
@@ -4710,49 +4712,49 @@
         <v>3</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>405</v>
+        <v>2268</v>
       </c>
       <c r="H73" s="8">
-        <v>4.0493827160493823E-2</v>
+        <v>2.9394473838918286E-2</v>
       </c>
       <c r="I73" s="10">
-        <v>35.772839506172843</v>
+        <v>43.35479129923575</v>
       </c>
       <c r="J73" s="16">
-        <v>2.52104E-3</v>
+        <v>1.0613766666666668E-2</v>
       </c>
       <c r="K73" s="16">
-        <v>2.0923164999999999</v>
+        <v>14.110998100000002</v>
       </c>
       <c r="L73" s="21">
-        <v>1.438428392894029E-14</v>
+        <v>8.4688324952415906E-15</v>
       </c>
       <c r="M73" s="21">
-        <v>2.9091890924767366E-16</v>
+        <v>1.8858153624902753E-16</v>
       </c>
       <c r="Q73" s="16">
-        <v>1.4845759599999999</v>
+        <v>96.311044699999997</v>
       </c>
       <c r="R73" s="23">
-        <v>6.4224237568373453E-14</v>
+        <v>2.4540004226204457E-11</v>
       </c>
       <c r="S73" s="23">
-        <v>4.0480732249425257E-15</v>
+        <v>1.9252283186548664E-13</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.3">
@@ -4760,10 +4762,10 @@
         <v>3</v>
       </c>
       <c r="B74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -4772,37 +4774,28 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>1215</v>
-      </c>
-      <c r="H74" s="8">
-        <v>4.8285322359396435E-2</v>
-      </c>
-      <c r="I74" s="10">
-        <v>38.020850480109736</v>
-      </c>
-      <c r="J74" s="16">
-        <v>6.2750999999999996E-3</v>
-      </c>
-      <c r="K74" s="16">
-        <v>7.1276070666666671</v>
-      </c>
-      <c r="L74" s="21">
-        <v>4.2785078587581009E-14</v>
-      </c>
-      <c r="M74" s="21">
-        <v>2.5526724123364401E-16</v>
-      </c>
-      <c r="Q74" s="16">
-        <v>22.499410633333337</v>
-      </c>
-      <c r="R74" s="23">
-        <v>1.0201482406593588E-12</v>
-      </c>
-      <c r="S74" s="23">
-        <v>8.7462265710671536E-15</v>
+        <v>3240</v>
+      </c>
+      <c r="H74" s="49">
+        <v>0.02</v>
+      </c>
+      <c r="I74" s="50">
+        <v>45.155999999999999</v>
+      </c>
+      <c r="J74" s="51">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="K74" s="51">
+        <v>20.454000000000001</v>
+      </c>
+      <c r="L74" s="52">
+        <v>8.4800000000000005E-15</v>
+      </c>
+      <c r="M74" s="52">
+        <v>1.8700000000000001E-16</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.3">
@@ -4810,49 +4803,49 @@
         <v>3</v>
       </c>
       <c r="B75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75">
         <v>2</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E75">
         <v>0</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G75">
-        <v>1458</v>
+        <v>405</v>
       </c>
       <c r="H75" s="8">
-        <v>5.8984910836762688E-2</v>
+        <v>4.0493827160493823E-2</v>
       </c>
       <c r="I75" s="10">
-        <v>37.772519433013265</v>
+        <v>35.772839506172843</v>
       </c>
       <c r="J75" s="16">
-        <v>4.7204666666666667E-3</v>
+        <v>2.52104E-3</v>
       </c>
       <c r="K75" s="16">
-        <v>11.113312899999999</v>
+        <v>2.0923164999999999</v>
       </c>
       <c r="L75" s="21">
-        <v>2.162323697391369E-14</v>
+        <v>1.438428392894029E-14</v>
       </c>
       <c r="M75" s="21">
-        <v>3.3125786688416323E-16</v>
+        <v>2.9091890924767366E-16</v>
       </c>
       <c r="Q75" s="16">
-        <v>122.30894290000001</v>
+        <v>1.4845759599999999</v>
       </c>
       <c r="R75" s="23">
-        <v>4.3606464890911999E-13</v>
+        <v>6.4224237568373453E-14</v>
       </c>
       <c r="S75" s="23">
-        <v>5.7434796010409036E-15</v>
+        <v>4.0480732249425257E-15</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.3">
@@ -4860,140 +4853,140 @@
         <v>3</v>
       </c>
       <c r="B76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G76">
-        <v>5103</v>
+        <v>1215</v>
       </c>
       <c r="H76" s="8">
-        <v>6.8979031941994909E-2</v>
+        <v>4.8285322359396435E-2</v>
       </c>
       <c r="I76" s="10">
-        <v>39.8432294728591</v>
+        <v>38.020850480109736</v>
       </c>
       <c r="J76" s="16">
-        <v>1.4519900000000001E-2</v>
+        <v>6.2750999999999996E-3</v>
       </c>
       <c r="K76" s="16">
-        <v>48.186458100000003</v>
+        <v>7.1276070666666671</v>
       </c>
       <c r="L76" s="21">
-        <v>1.2265086244831076E-13</v>
+        <v>4.2785078587581009E-14</v>
       </c>
       <c r="M76" s="21">
-        <v>3.0241030583310743E-16</v>
+        <v>2.5526724123364401E-16</v>
+      </c>
+      <c r="Q76" s="16">
+        <v>22.499410633333337</v>
+      </c>
+      <c r="R76" s="23">
+        <v>1.0201482406593588E-12</v>
+      </c>
+      <c r="S76" s="23">
+        <v>8.7462265710671536E-15</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C77">
         <v>2</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>48</v>
+        <v>1458</v>
       </c>
       <c r="H77" s="8">
-        <v>2.4999999999999998E-2</v>
+        <v>5.8984910836762688E-2</v>
       </c>
       <c r="I77" s="10">
-        <v>35.091666666666661</v>
+        <v>37.772519433013265</v>
       </c>
       <c r="J77" s="16">
-        <v>6.6166E-4</v>
+        <v>4.7204666666666667E-3</v>
       </c>
       <c r="K77" s="16">
-        <v>0.20406301999999998</v>
+        <v>11.113312899999999</v>
       </c>
       <c r="L77" s="21">
-        <v>5.1636162701444704E-15</v>
+        <v>2.162323697391369E-14</v>
       </c>
       <c r="M77" s="21">
-        <v>2.4050541761169982E-16</v>
+        <v>3.3125786688416323E-16</v>
       </c>
       <c r="Q77" s="16">
-        <v>5.1319119999999996E-2</v>
+        <v>122.30894290000001</v>
       </c>
       <c r="R77" s="23">
-        <v>1.9039088267757576E-14</v>
+        <v>4.3606464890911999E-13</v>
       </c>
       <c r="S77" s="23">
-        <v>1.9803021753882212E-15</v>
+        <v>5.7434796010409036E-15</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C78">
         <v>3</v>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G78">
-        <v>96</v>
+        <v>5103</v>
       </c>
       <c r="H78" s="8">
-        <v>2.4999999999999998E-2</v>
+        <v>6.8979031941994909E-2</v>
       </c>
       <c r="I78" s="10">
-        <v>35.543750000000003</v>
+        <v>39.8432294728591</v>
       </c>
       <c r="J78" s="16">
-        <v>8.9022000000000005E-4</v>
+        <v>1.4519900000000001E-2</v>
       </c>
       <c r="K78" s="16">
-        <v>0.35155676000000002</v>
+        <v>48.186458100000003</v>
       </c>
       <c r="L78" s="21">
-        <v>6.6044339903193766E-15</v>
+        <v>1.2265086244831076E-13</v>
       </c>
       <c r="M78" s="21">
-        <v>2.0503553178939857E-16</v>
-      </c>
-      <c r="Q78" s="16">
-        <v>0.1038462</v>
-      </c>
-      <c r="R78" s="23">
-        <v>3.1544251439102089E-14</v>
-      </c>
-      <c r="S78" s="23">
-        <v>2.5974700552963143E-15</v>
+        <v>3.0241030583310743E-16</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.3">
@@ -5004,7 +4997,7 @@
         <v>2</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D79">
         <v>5</v>
@@ -5016,34 +5009,34 @@
         <v>5</v>
       </c>
       <c r="G79">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="H79" s="8">
-        <v>1.7499999999999998E-2</v>
+        <v>2.4999999999999998E-2</v>
       </c>
       <c r="I79" s="10">
-        <v>37.651250000000005</v>
+        <v>35.091666666666661</v>
       </c>
       <c r="J79" s="16">
-        <v>1.12224E-3</v>
+        <v>6.6166E-4</v>
       </c>
       <c r="K79" s="16">
-        <v>0.63653746</v>
+        <v>0.20406301999999998</v>
       </c>
       <c r="L79" s="21">
-        <v>8.3112832032632516E-15</v>
+        <v>5.1636162701444704E-15</v>
       </c>
       <c r="M79" s="21">
-        <v>1.9875401159569674E-16</v>
+        <v>2.4050541761169982E-16</v>
       </c>
       <c r="Q79" s="16">
-        <v>0.20346367999999998</v>
+        <v>5.1319119999999996E-2</v>
       </c>
       <c r="R79" s="23">
-        <v>9.778811515855743E-13</v>
+        <v>1.9039088267757576E-14</v>
       </c>
       <c r="S79" s="23">
-        <v>2.2822300132756392E-14</v>
+        <v>1.9803021753882212E-15</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
@@ -5054,7 +5047,7 @@
         <v>2</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D80">
         <v>5</v>
@@ -5066,34 +5059,34 @@
         <v>5</v>
       </c>
       <c r="G80">
-        <v>240</v>
+        <v>96</v>
       </c>
       <c r="H80" s="8">
-        <v>2.5000000000000001E-2</v>
+        <v>2.4999999999999998E-2</v>
       </c>
       <c r="I80" s="10">
-        <v>39.858333333333334</v>
+        <v>35.543750000000003</v>
       </c>
       <c r="J80" s="16">
-        <v>1.5599599999999998E-3</v>
+        <v>8.9022000000000005E-4</v>
       </c>
       <c r="K80" s="16">
-        <v>1.0186321599999999</v>
+        <v>0.35155676000000002</v>
       </c>
       <c r="L80" s="21">
-        <v>8.0165326312548139E-15</v>
+        <v>6.6044339903193766E-15</v>
       </c>
       <c r="M80" s="21">
-        <v>1.9164943387905609E-16</v>
+        <v>2.0503553178939857E-16</v>
       </c>
       <c r="Q80" s="16">
-        <v>0.41042536000000007</v>
+        <v>0.1038462</v>
       </c>
       <c r="R80" s="23">
-        <v>1.8151501146785406E-13</v>
+        <v>3.1544251439102089E-14</v>
       </c>
       <c r="S80" s="23">
-        <v>3.5174345616668639E-15</v>
+        <v>2.5974700552963143E-15</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.3">
@@ -5104,7 +5097,7 @@
         <v>2</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D81">
         <v>5</v>
@@ -5116,34 +5109,34 @@
         <v>5</v>
       </c>
       <c r="G81">
-        <v>336</v>
+        <v>160</v>
       </c>
       <c r="H81" s="8">
-        <v>1.6666666666666666E-2</v>
+        <v>1.7499999999999998E-2</v>
       </c>
       <c r="I81" s="10">
-        <v>41.69583333333334</v>
+        <v>37.651250000000005</v>
       </c>
       <c r="J81" s="16">
-        <v>1.9404399999999999E-3</v>
+        <v>1.12224E-3</v>
       </c>
       <c r="K81" s="16">
-        <v>1.5951258799999999</v>
+        <v>0.63653746</v>
       </c>
       <c r="L81" s="21">
-        <v>8.2164339524242991E-15</v>
+        <v>8.3112832032632516E-15</v>
       </c>
       <c r="M81" s="21">
-        <v>1.8189827594694064E-16</v>
+        <v>1.9875401159569674E-16</v>
       </c>
       <c r="Q81" s="16">
-        <v>0.86774325999999991</v>
+        <v>0.20346367999999998</v>
       </c>
       <c r="R81" s="23">
-        <v>1.9036289092995512E-12</v>
+        <v>9.778811515855743E-13</v>
       </c>
       <c r="S81" s="23">
-        <v>2.451769638850862E-14</v>
+        <v>2.2822300132756392E-14</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.3">
@@ -5154,7 +5147,7 @@
         <v>2</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D82">
         <v>5</v>
@@ -5166,34 +5159,34 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>448</v>
+        <v>240</v>
       </c>
       <c r="H82" s="8">
-        <v>1.9642857142857146E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I82" s="10">
-        <v>42.666964285714279</v>
+        <v>39.858333333333334</v>
       </c>
       <c r="J82" s="16">
-        <v>2.43888E-3</v>
+        <v>1.5599599999999998E-3</v>
       </c>
       <c r="K82" s="16">
-        <v>2.1699046600000003</v>
+        <v>1.0186321599999999</v>
       </c>
       <c r="L82" s="21">
-        <v>8.0746483171160317E-15</v>
+        <v>8.0165326312548139E-15</v>
       </c>
       <c r="M82" s="21">
-        <v>1.8361153524691382E-16</v>
+        <v>1.9164943387905609E-16</v>
       </c>
       <c r="Q82" s="16">
-        <v>1.41559104</v>
+        <v>0.41042536000000007</v>
       </c>
       <c r="R82" s="23">
-        <v>7.8049497441862349E-11</v>
+        <v>1.8151501146785406E-13</v>
       </c>
       <c r="S82" s="23">
-        <v>1.1124407655959028E-13</v>
+        <v>3.5174345616668639E-15</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.3">
@@ -5204,7 +5197,7 @@
         <v>2</v>
       </c>
       <c r="C83">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -5216,34 +5209,34 @@
         <v>5</v>
       </c>
       <c r="G83">
-        <v>576</v>
+        <v>336</v>
       </c>
       <c r="H83" s="8">
-        <v>1.6319444444444445E-2</v>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="I83" s="10">
-        <v>43.930902777777774</v>
+        <v>41.69583333333334</v>
       </c>
       <c r="J83" s="16">
-        <v>2.9625200000000002E-3</v>
+        <v>1.9404399999999999E-3</v>
       </c>
       <c r="K83" s="16">
-        <v>3.0337073399999999</v>
+        <v>1.5951258799999999</v>
       </c>
       <c r="L83" s="21">
-        <v>8.7563421659102526E-15</v>
+        <v>8.2164339524242991E-15</v>
       </c>
       <c r="M83" s="21">
-        <v>1.8086193569675066E-16</v>
+        <v>1.8189827594694064E-16</v>
       </c>
       <c r="Q83" s="16">
-        <v>2.6988541599999998</v>
+        <v>0.86774325999999991</v>
       </c>
       <c r="R83" s="23">
-        <v>3.1965184679858536E-10</v>
+        <v>1.9036289092995512E-12</v>
       </c>
       <c r="S83" s="23">
-        <v>1.8248833852568277E-13</v>
+        <v>2.451769638850862E-14</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.3">
@@ -5254,7 +5247,7 @@
         <v>2</v>
       </c>
       <c r="C84">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D84">
         <v>5</v>
@@ -5266,34 +5259,34 @@
         <v>5</v>
       </c>
       <c r="G84">
-        <v>720</v>
+        <v>448</v>
       </c>
       <c r="H84" s="8">
-        <v>1.7499999999999998E-2</v>
+        <v>1.9642857142857146E-2</v>
       </c>
       <c r="I84" s="10">
-        <v>45.905277777777783</v>
+        <v>42.666964285714279</v>
       </c>
       <c r="J84" s="16">
-        <v>3.6048000000000005E-3</v>
+        <v>2.43888E-3</v>
       </c>
       <c r="K84" s="16">
-        <v>4.1214200400000003</v>
+        <v>2.1699046600000003</v>
       </c>
       <c r="L84" s="21">
-        <v>8.1221604086442086E-15</v>
+        <v>8.0746483171160317E-15</v>
       </c>
       <c r="M84" s="21">
-        <v>1.7674696975267334E-16</v>
+        <v>1.8361153524691382E-16</v>
       </c>
       <c r="Q84" s="16">
-        <v>5.3663346399999998</v>
+        <v>1.41559104</v>
       </c>
       <c r="R84" s="23">
-        <v>8.9366837878838275E-11</v>
+        <v>7.8049497441862349E-11</v>
       </c>
       <c r="S84" s="23">
-        <v>5.983322273343556E-13</v>
+        <v>1.1124407655959028E-13</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.3">
@@ -5304,7 +5297,7 @@
         <v>2</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -5316,34 +5309,34 @@
         <v>5</v>
       </c>
       <c r="G85">
-        <v>880</v>
+        <v>576</v>
       </c>
       <c r="H85" s="8">
-        <v>1.0909090909090908E-2</v>
+        <v>1.6319444444444445E-2</v>
       </c>
       <c r="I85" s="10">
-        <v>46.384545454545453</v>
+        <v>43.930902777777774</v>
       </c>
       <c r="J85" s="16">
-        <v>4.5217199999999999E-3</v>
+        <v>2.9625200000000002E-3</v>
       </c>
       <c r="K85" s="16">
-        <v>5.1804248600000005</v>
+        <v>3.0337073399999999</v>
       </c>
       <c r="L85" s="21">
-        <v>4.0563133109035229E-13</v>
+        <v>8.7563421659102526E-15</v>
       </c>
       <c r="M85" s="21">
-        <v>1.7946917554982332E-16</v>
+        <v>1.8086193569675066E-16</v>
       </c>
       <c r="Q85" s="16">
-        <v>8.6941763399999985</v>
+        <v>2.6988541599999998</v>
       </c>
       <c r="R85" s="23">
-        <v>3.4883819294068199E-10</v>
+        <v>3.1965184679858536E-10</v>
       </c>
       <c r="S85" s="23">
-        <v>1.266692535217473E-12</v>
+        <v>1.8248833852568277E-13</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.3">
@@ -5354,7 +5347,7 @@
         <v>2</v>
       </c>
       <c r="C86">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D86">
         <v>5</v>
@@ -5363,37 +5356,37 @@
         <v>0</v>
       </c>
       <c r="F86">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G86">
-        <v>1056</v>
+        <v>720</v>
       </c>
       <c r="H86" s="8">
-        <v>1.3636363636363637E-2</v>
+        <v>1.7499999999999998E-2</v>
       </c>
       <c r="I86" s="10">
-        <v>47.596780303030307</v>
+        <v>45.905277777777783</v>
       </c>
       <c r="J86" s="16">
-        <v>5.1335600000000006E-3</v>
+        <v>3.6048000000000005E-3</v>
       </c>
       <c r="K86" s="16">
-        <v>6.70655512</v>
+        <v>4.1214200400000003</v>
       </c>
       <c r="L86" s="21">
-        <v>8.856099390063399E-15</v>
+        <v>8.1221604086442086E-15</v>
       </c>
       <c r="M86" s="21">
-        <v>1.8085618481595117E-16</v>
+        <v>1.7674696975267334E-16</v>
       </c>
       <c r="Q86" s="16">
-        <v>15.056374466666668</v>
+        <v>5.3663346399999998</v>
       </c>
       <c r="R86" s="23">
-        <v>2.4295018337047839E-8</v>
+        <v>8.9366837878838275E-11</v>
       </c>
       <c r="S86" s="23">
-        <v>2.308890906404235E-12</v>
+        <v>5.983322273343556E-13</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.3">
@@ -5404,7 +5397,7 @@
         <v>2</v>
       </c>
       <c r="C87">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D87">
         <v>5</v>
@@ -5413,37 +5406,37 @@
         <v>0</v>
       </c>
       <c r="F87">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G87">
-        <v>1248</v>
+        <v>880</v>
       </c>
       <c r="H87" s="8">
-        <v>9.935897435897437E-3</v>
+        <v>1.0909090909090908E-2</v>
       </c>
       <c r="I87" s="10">
-        <v>48.495993589743591</v>
+        <v>46.384545454545453</v>
       </c>
       <c r="J87" s="16">
-        <v>6.1504000000000003E-3</v>
+        <v>4.5217199999999999E-3</v>
       </c>
       <c r="K87" s="16">
-        <v>8.1608353799999982</v>
+        <v>5.1804248600000005</v>
       </c>
       <c r="L87" s="21">
-        <v>4.5313439140602873E-14</v>
+        <v>4.0563133109035229E-13</v>
       </c>
       <c r="M87" s="21">
-        <v>1.7779168818308106E-16</v>
+        <v>1.7946917554982332E-16</v>
       </c>
       <c r="Q87" s="16">
-        <v>25.834941299999997</v>
+        <v>8.6941763399999985</v>
       </c>
       <c r="R87" s="23">
-        <v>1.1219879282896385E-7</v>
+        <v>3.4883819294068199E-10</v>
       </c>
       <c r="S87" s="23">
-        <v>6.0061331322282475E-11</v>
+        <v>1.266692535217473E-12</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.3">
@@ -5454,46 +5447,46 @@
         <v>2</v>
       </c>
       <c r="C88">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D88">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E88">
         <v>0</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G88">
-        <v>1456</v>
+        <v>1056</v>
       </c>
       <c r="H88" s="8">
-        <v>1.510989010989011E-2</v>
+        <v>1.3636363636363637E-2</v>
       </c>
       <c r="I88" s="10">
-        <v>50.130494505494504</v>
+        <v>47.596780303030307</v>
       </c>
       <c r="J88" s="16">
-        <v>7.1642999999999993E-3</v>
+        <v>5.1335600000000006E-3</v>
       </c>
       <c r="K88" s="16">
-        <v>10.554905466666666</v>
+        <v>6.70655512</v>
       </c>
       <c r="L88" s="21">
-        <v>7.1176206096708818E-13</v>
+        <v>8.856099390063399E-15</v>
       </c>
       <c r="M88" s="21">
-        <v>1.7861793287256898E-16</v>
+        <v>1.8085618481595117E-16</v>
       </c>
       <c r="Q88" s="16">
-        <v>43.764413300000001</v>
+        <v>15.056374466666668</v>
       </c>
       <c r="R88" s="23">
-        <v>4.2691807837727752E-8</v>
+        <v>2.4295018337047839E-8</v>
       </c>
       <c r="S88" s="23">
-        <v>6.2430990554405218E-11</v>
+        <v>2.308890906404235E-12</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.3">
@@ -5504,46 +5497,46 @@
         <v>2</v>
       </c>
       <c r="C89">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D89">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G89">
-        <v>1680</v>
+        <v>1248</v>
       </c>
       <c r="H89" s="8">
-        <v>1.1309523809523809E-2</v>
+        <v>9.935897435897437E-3</v>
       </c>
       <c r="I89" s="10">
-        <v>50.704563492063492</v>
+        <v>48.495993589743591</v>
       </c>
       <c r="J89" s="16">
-        <v>8.1736666666666676E-3</v>
+        <v>6.1504000000000003E-3</v>
       </c>
       <c r="K89" s="16">
-        <v>12.699480933333334</v>
+        <v>8.1608353799999982</v>
       </c>
       <c r="L89" s="21">
-        <v>8.8981459305272474E-15</v>
+        <v>4.5313439140602873E-14</v>
       </c>
       <c r="M89" s="21">
-        <v>1.7513656631602058E-16</v>
+        <v>1.7779168818308106E-16</v>
       </c>
       <c r="Q89" s="16">
-        <v>68.735169999999997</v>
+        <v>25.834941299999997</v>
       </c>
       <c r="R89" s="23">
-        <v>2.9854311789293022E-7</v>
+        <v>1.1219879282896385E-7</v>
       </c>
       <c r="S89" s="23">
-        <v>2.3696610952665727E-10</v>
+        <v>6.0061331322282475E-11</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.3">
@@ -5554,7 +5547,7 @@
         <v>2</v>
       </c>
       <c r="C90">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -5566,34 +5559,34 @@
         <v>1</v>
       </c>
       <c r="G90">
-        <v>1920</v>
+        <v>1456</v>
       </c>
       <c r="H90" s="8">
-        <v>1.2847222222222223E-2</v>
+        <v>1.510989010989011E-2</v>
       </c>
       <c r="I90" s="10">
-        <v>51.958506944444444</v>
+        <v>50.130494505494504</v>
       </c>
       <c r="J90" s="16">
-        <v>9.1122333333333323E-3</v>
+        <v>7.1642999999999993E-3</v>
       </c>
       <c r="K90" s="16">
-        <v>15.405627433333331</v>
+        <v>10.554905466666666</v>
       </c>
       <c r="L90" s="21">
-        <v>8.5753805662679717E-15</v>
+        <v>7.1176206096708818E-13</v>
       </c>
       <c r="M90" s="21">
-        <v>1.7745128677302042E-16</v>
+        <v>1.7861793287256898E-16</v>
       </c>
       <c r="Q90" s="16">
-        <v>115.3274906</v>
+        <v>43.764413300000001</v>
       </c>
       <c r="R90" s="23">
-        <v>9.7650735782652114E-8</v>
+        <v>4.2691807837727752E-8</v>
       </c>
       <c r="S90" s="23">
-        <v>1.468131376872587E-10</v>
+        <v>6.2430990554405218E-11</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.3">
@@ -5601,49 +5594,49 @@
         <v>4</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G91">
-        <v>256</v>
+        <v>1680</v>
       </c>
       <c r="H91" s="8">
-        <v>3.7499999999999999E-2</v>
+        <v>1.1309523809523809E-2</v>
       </c>
       <c r="I91" s="10">
-        <v>34.6796875</v>
+        <v>50.704563492063492</v>
       </c>
       <c r="J91" s="16">
-        <v>1.0819E-3</v>
+        <v>8.1736666666666676E-3</v>
       </c>
       <c r="K91" s="16">
-        <v>1.2695744000000002</v>
+        <v>12.699480933333334</v>
       </c>
       <c r="L91" s="21">
-        <v>2.0132970511526198E-14</v>
+        <v>8.8981459305272474E-15</v>
       </c>
       <c r="M91" s="21">
-        <v>3.1160955247749329E-16</v>
+        <v>1.7513656631602058E-16</v>
       </c>
       <c r="Q91" s="16">
-        <v>0.54818089999999997</v>
+        <v>68.735169999999997</v>
       </c>
       <c r="R91" s="23">
-        <v>4.6418020215540686E-13</v>
+        <v>2.9854311789293022E-7</v>
       </c>
       <c r="S91" s="23">
-        <v>4.7421697260468803E-15</v>
+        <v>2.3696610952665727E-10</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.3">
@@ -5651,49 +5644,49 @@
         <v>4</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D92">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G92">
-        <v>640</v>
+        <v>1920</v>
       </c>
       <c r="H92" s="8">
-        <v>4.4687500000000005E-2</v>
+        <v>1.2847222222222223E-2</v>
       </c>
       <c r="I92" s="10">
-        <v>37.266875000000006</v>
+        <v>51.958506944444444</v>
       </c>
       <c r="J92" s="16">
-        <v>1.9033400000000003E-3</v>
+        <v>9.1122333333333323E-3</v>
       </c>
       <c r="K92" s="16">
-        <v>3.4576043599999999</v>
+        <v>15.405627433333331</v>
       </c>
       <c r="L92" s="21">
-        <v>1.7151996279412218E-14</v>
+        <v>8.5753805662679717E-15</v>
       </c>
       <c r="M92" s="21">
-        <v>2.7287804132474252E-16</v>
+        <v>1.7745128677302042E-16</v>
       </c>
       <c r="Q92" s="16">
-        <v>2.5991152799999995</v>
+        <v>115.3274906</v>
       </c>
       <c r="R92" s="23">
-        <v>5.8968561566010554E-12</v>
+        <v>9.7650735782652114E-8</v>
       </c>
       <c r="S92" s="23">
-        <v>5.5666729068412767E-15</v>
+        <v>1.468131376872587E-10</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.3">
@@ -5704,7 +5697,7 @@
         <v>3</v>
       </c>
       <c r="C93">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D93">
         <v>5</v>
@@ -5713,37 +5706,37 @@
         <v>0</v>
       </c>
       <c r="F93">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G93">
-        <v>1280</v>
+        <v>256</v>
       </c>
       <c r="H93" s="8">
-        <v>4.8437500000000001E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="I93" s="10">
-        <v>39.59796875</v>
+        <v>34.6796875</v>
       </c>
       <c r="J93" s="16">
-        <v>3.72822E-3</v>
+        <v>1.0819E-3</v>
       </c>
       <c r="K93" s="16">
-        <v>7.8842147200000001</v>
+        <v>1.2695744000000002</v>
       </c>
       <c r="L93" s="21">
-        <v>2.9964443174956343E-14</v>
+        <v>2.0132970511526198E-14</v>
       </c>
       <c r="M93" s="21">
-        <v>2.5838472390410206E-16</v>
+        <v>3.1160955247749329E-16</v>
       </c>
       <c r="Q93" s="16">
-        <v>13.694324433333334</v>
+        <v>0.54818089999999997</v>
       </c>
       <c r="R93" s="23">
-        <v>5.6072664396495966E-12</v>
+        <v>4.6418020215540686E-13</v>
       </c>
       <c r="S93" s="23">
-        <v>1.0970575168905956E-14</v>
+        <v>4.7421697260468803E-15</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.3">
@@ -5754,46 +5747,46 @@
         <v>3</v>
       </c>
       <c r="C94">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E94">
         <v>0</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G94">
-        <v>2240</v>
+        <v>640</v>
       </c>
       <c r="H94" s="8">
-        <v>3.4375000000000003E-2</v>
+        <v>4.4687500000000005E-2</v>
       </c>
       <c r="I94" s="10">
-        <v>39.656845238095237</v>
+        <v>37.266875000000006</v>
       </c>
       <c r="J94" s="16">
-        <v>6.4512333333333338E-3</v>
+        <v>1.9033400000000003E-3</v>
       </c>
       <c r="K94" s="16">
-        <v>14.612070233333334</v>
+        <v>3.4576043599999999</v>
       </c>
       <c r="L94" s="21">
-        <v>1.0285622689536414E-12</v>
+        <v>1.7151996279412218E-14</v>
       </c>
       <c r="M94" s="21">
-        <v>2.4789962864686991E-16</v>
+        <v>2.7287804132474252E-16</v>
       </c>
       <c r="Q94" s="16">
-        <v>78.473416999999998</v>
+        <v>2.5991152799999995</v>
       </c>
       <c r="R94" s="23">
-        <v>1.8499076792100177E-11</v>
+        <v>5.8968561566010554E-12</v>
       </c>
       <c r="S94" s="23">
-        <v>3.3888450136734267E-14</v>
+        <v>5.5666729068412767E-15</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.3">
@@ -5801,13 +5794,13 @@
         <v>4</v>
       </c>
       <c r="B95">
+        <v>3</v>
+      </c>
+      <c r="C95">
         <v>4</v>
       </c>
-      <c r="C95">
-        <v>2</v>
-      </c>
       <c r="D95">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5819,31 +5812,31 @@
         <v>1280</v>
       </c>
       <c r="H95" s="8">
-        <v>7.239583333333334E-2</v>
+        <v>4.8437500000000001E-2</v>
       </c>
       <c r="I95" s="10">
-        <v>37.006510416666664</v>
+        <v>39.59796875</v>
       </c>
       <c r="J95" s="16">
-        <v>2.7899666666666664E-3</v>
+        <v>3.72822E-3</v>
       </c>
       <c r="K95" s="16">
-        <v>10.7165324</v>
+        <v>7.8842147200000001</v>
       </c>
       <c r="L95" s="21">
-        <v>4.4504646015332152E-14</v>
+        <v>2.9964443174956343E-14</v>
       </c>
       <c r="M95" s="21">
-        <v>3.8130984615729509E-16</v>
+        <v>2.5838472390410206E-16</v>
       </c>
       <c r="Q95" s="16">
-        <v>26.523647033333333</v>
+        <v>13.694324433333334</v>
       </c>
       <c r="R95" s="23">
-        <v>4.1193002835668419E-11</v>
+        <v>5.6072664396495966E-12</v>
       </c>
       <c r="S95" s="23">
-        <v>8.1716021343870607E-15</v>
+        <v>1.0970575168905956E-14</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.3">
@@ -5851,140 +5844,140 @@
         <v>4</v>
       </c>
       <c r="B96">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D96">
+        <v>3</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
         <v>1</v>
       </c>
-      <c r="E96">
-        <v>0</v>
-      </c>
-      <c r="F96">
-        <v>0</v>
-      </c>
       <c r="G96">
-        <v>3840</v>
+        <v>2240</v>
       </c>
       <c r="H96" s="8">
-        <v>6.458333333333334E-2</v>
+        <v>3.4375000000000003E-2</v>
       </c>
       <c r="I96" s="10">
-        <v>38.025260416666669</v>
+        <v>39.656845238095237</v>
       </c>
       <c r="J96" s="16">
-        <v>7.5215000000000004E-3</v>
+        <v>6.4512333333333338E-3</v>
       </c>
       <c r="K96" s="16">
-        <v>33.928097700000002</v>
+        <v>14.612070233333334</v>
       </c>
       <c r="L96" s="21">
-        <v>2.8704818616543717E-14</v>
+        <v>1.0285622689536414E-12</v>
       </c>
       <c r="M96" s="21">
-        <v>3.4110084723815503E-16</v>
+        <v>2.4789962864686991E-16</v>
+      </c>
+      <c r="Q96" s="16">
+        <v>78.473416999999998</v>
+      </c>
+      <c r="R96" s="23">
+        <v>1.8499076792100177E-11</v>
+      </c>
+      <c r="S96" s="23">
+        <v>3.3888450136734267E-14</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G97">
-        <v>75</v>
+        <v>1280</v>
       </c>
       <c r="H97" s="8">
-        <v>3.2000000000000001E-2</v>
+        <v>7.239583333333334E-2</v>
       </c>
       <c r="I97" s="10">
-        <v>34.058666666666667</v>
+        <v>37.006510416666664</v>
       </c>
       <c r="J97" s="16">
-        <v>6.623E-4</v>
+        <v>2.7899666666666664E-3</v>
       </c>
       <c r="K97" s="16">
-        <v>0.31772778000000002</v>
+        <v>10.7165324</v>
       </c>
       <c r="L97" s="21">
-        <v>8.1802588652744995E-15</v>
+        <v>4.4504646015332152E-14</v>
       </c>
       <c r="M97" s="21">
-        <v>2.7054990438010407E-16</v>
+        <v>3.8130984615729509E-16</v>
       </c>
       <c r="Q97" s="16">
-        <v>9.5071459999999997E-2</v>
+        <v>26.523647033333333</v>
       </c>
       <c r="R97" s="23">
-        <v>2.1230176129388547E-13</v>
+        <v>4.1193002835668419E-11</v>
       </c>
       <c r="S97" s="23">
-        <v>2.6554082342794527E-15</v>
+        <v>8.1716021343870607E-15</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C98">
         <v>3</v>
       </c>
       <c r="D98">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E98">
         <v>0</v>
       </c>
       <c r="F98">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>150</v>
+        <v>3840</v>
       </c>
       <c r="H98" s="8">
-        <v>3.7333333333333329E-2</v>
+        <v>6.458333333333334E-2</v>
       </c>
       <c r="I98" s="10">
-        <v>36.805333333333337</v>
+        <v>38.025260416666669</v>
       </c>
       <c r="J98" s="16">
-        <v>8.6505999999999996E-4</v>
+        <v>7.5215000000000004E-3</v>
       </c>
       <c r="K98" s="16">
-        <v>0.68472791999999993</v>
+        <v>33.928097700000002</v>
       </c>
       <c r="L98" s="21">
-        <v>7.9992386291296098E-14</v>
+        <v>2.8704818616543717E-14</v>
       </c>
       <c r="M98" s="21">
-        <v>2.3437174106603008E-16</v>
-      </c>
-      <c r="Q98" s="16">
-        <v>0.20571149999999999</v>
-      </c>
-      <c r="R98" s="23">
-        <v>3.9276827367189106E-13</v>
-      </c>
-      <c r="S98" s="23">
-        <v>3.887301769157956E-15</v>
+        <v>3.4110084723815503E-16</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.3">
@@ -5995,7 +5988,7 @@
         <v>2</v>
       </c>
       <c r="C99">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D99">
         <v>5</v>
@@ -6007,34 +6000,34 @@
         <v>5</v>
       </c>
       <c r="G99">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="H99" s="8">
-        <v>2.7199999999999998E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="I99" s="10">
-        <v>37.944000000000003</v>
+        <v>34.058666666666667</v>
       </c>
       <c r="J99" s="16">
-        <v>1.1263600000000001E-3</v>
+        <v>6.623E-4</v>
       </c>
       <c r="K99" s="16">
-        <v>1.1483679399999998</v>
+        <v>0.31772778000000002</v>
       </c>
       <c r="L99" s="21">
-        <v>1.4703385801104632E-14</v>
+        <v>8.1802588652744995E-15</v>
       </c>
       <c r="M99" s="21">
-        <v>2.249163067383749E-16</v>
+        <v>2.7054990438010407E-16</v>
       </c>
       <c r="Q99" s="16">
-        <v>0.45794532000000004</v>
+        <v>9.5071459999999997E-2</v>
       </c>
       <c r="R99" s="23">
-        <v>7.9015136443126549E-13</v>
+        <v>2.1230176129388547E-13</v>
       </c>
       <c r="S99" s="23">
-        <v>1.0980834697690558E-14</v>
+        <v>2.6554082342794527E-15</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.3">
@@ -6045,7 +6038,7 @@
         <v>2</v>
       </c>
       <c r="C100">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D100">
         <v>5</v>
@@ -6057,34 +6050,34 @@
         <v>5</v>
       </c>
       <c r="G100">
-        <v>375</v>
+        <v>150</v>
       </c>
       <c r="H100" s="8">
-        <v>2.4E-2</v>
+        <v>3.7333333333333329E-2</v>
       </c>
       <c r="I100" s="10">
-        <v>39.789333333333332</v>
+        <v>36.805333333333337</v>
       </c>
       <c r="J100" s="16">
-        <v>1.5102200000000001E-3</v>
+        <v>8.6505999999999996E-4</v>
       </c>
       <c r="K100" s="16">
-        <v>1.8615628799999999</v>
+        <v>0.68472791999999993</v>
       </c>
       <c r="L100" s="21">
-        <v>1.5468578750210955E-14</v>
+        <v>7.9992386291296098E-14</v>
       </c>
       <c r="M100" s="21">
-        <v>2.2084568777386575E-16</v>
+        <v>2.3437174106603008E-16</v>
       </c>
       <c r="Q100" s="16">
-        <v>0.94974728000000008</v>
+        <v>0.20571149999999999</v>
       </c>
       <c r="R100" s="23">
-        <v>2.9094147727193586E-12</v>
+        <v>3.9276827367189106E-13</v>
       </c>
       <c r="S100" s="23">
-        <v>7.9947913515779821E-14</v>
+        <v>3.887301769157956E-15</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.3">
@@ -6095,7 +6088,7 @@
         <v>2</v>
       </c>
       <c r="C101">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D101">
         <v>5</v>
@@ -6107,34 +6100,34 @@
         <v>5</v>
       </c>
       <c r="G101">
-        <v>525</v>
+        <v>250</v>
       </c>
       <c r="H101" s="8">
-        <v>2.1333333333333333E-2</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="I101" s="10">
-        <v>41.500571428571426</v>
+        <v>37.944000000000003</v>
       </c>
       <c r="J101" s="16">
-        <v>1.9948000000000001E-3</v>
+        <v>1.1263600000000001E-3</v>
       </c>
       <c r="K101" s="16">
-        <v>2.8250143000000003</v>
+        <v>1.1483679399999998</v>
       </c>
       <c r="L101" s="21">
-        <v>1.4833348118405114E-14</v>
+        <v>1.4703385801104632E-14</v>
       </c>
       <c r="M101" s="21">
-        <v>2.1174835996058322E-16</v>
+        <v>2.249163067383749E-16</v>
       </c>
       <c r="Q101" s="16">
-        <v>2.0045685999999998</v>
+        <v>0.45794532000000004</v>
       </c>
       <c r="R101" s="23">
-        <v>9.6685578236614547E-12</v>
+        <v>7.9015136443126549E-13</v>
       </c>
       <c r="S101" s="23">
-        <v>5.0820155852136305E-14</v>
+        <v>1.0980834697690558E-14</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.3">
@@ -6145,7 +6138,7 @@
         <v>2</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -6157,34 +6150,34 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>700</v>
+        <v>375</v>
       </c>
       <c r="H102" s="8">
-        <v>2.4285714285714285E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="I102" s="10">
-        <v>43.141428571428577</v>
+        <v>39.789333333333332</v>
       </c>
       <c r="J102" s="16">
-        <v>2.5738999999999996E-3</v>
+        <v>1.5102200000000001E-3</v>
       </c>
       <c r="K102" s="16">
-        <v>4.0745186200000001</v>
+        <v>1.8615628799999999</v>
       </c>
       <c r="L102" s="21">
-        <v>3.8779438915317176E-13</v>
+        <v>1.5468578750210955E-14</v>
       </c>
       <c r="M102" s="21">
-        <v>2.1531211961687913E-16</v>
+        <v>2.2084568777386575E-16</v>
       </c>
       <c r="Q102" s="16">
-        <v>4.3959003600000006</v>
+        <v>0.94974728000000008</v>
       </c>
       <c r="R102" s="23">
-        <v>1.5402273032896525E-10</v>
+        <v>2.9094147727193586E-12</v>
       </c>
       <c r="S102" s="23">
-        <v>1.3596143244377566E-13</v>
+        <v>7.9947913515779821E-14</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.3">
@@ -6195,7 +6188,7 @@
         <v>2</v>
       </c>
       <c r="C103">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D103">
         <v>5</v>
@@ -6207,34 +6200,34 @@
         <v>5</v>
       </c>
       <c r="G103">
-        <v>900</v>
+        <v>525</v>
       </c>
       <c r="H103" s="8">
-        <v>2.0222222222222221E-2</v>
+        <v>2.1333333333333333E-2</v>
       </c>
       <c r="I103" s="10">
-        <v>44.225555555555552</v>
+        <v>41.500571428571426</v>
       </c>
       <c r="J103" s="16">
-        <v>2.9292000000000003E-3</v>
+        <v>1.9948000000000001E-3</v>
       </c>
       <c r="K103" s="16">
-        <v>5.5390185399999998</v>
+        <v>2.8250143000000003</v>
       </c>
       <c r="L103" s="21">
-        <v>1.4901997469166348E-14</v>
+        <v>1.4833348118405114E-14</v>
       </c>
       <c r="M103" s="21">
-        <v>2.1025872780187197E-16</v>
+        <v>2.1174835996058322E-16</v>
       </c>
       <c r="Q103" s="16">
-        <v>8.3908084400000007</v>
+        <v>2.0045685999999998</v>
       </c>
       <c r="R103" s="23">
-        <v>9.3880357060867293E-11</v>
+        <v>9.6685578236614547E-12</v>
       </c>
       <c r="S103" s="23">
-        <v>3.3585867021730076E-13</v>
+        <v>5.0820155852136305E-14</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.3">
@@ -6245,7 +6238,7 @@
         <v>2</v>
       </c>
       <c r="C104">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D104">
         <v>5</v>
@@ -6254,37 +6247,37 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G104">
-        <v>1125</v>
+        <v>700</v>
       </c>
       <c r="H104" s="8">
-        <v>1.2977777777777777E-2</v>
+        <v>2.4285714285714285E-2</v>
       </c>
       <c r="I104" s="10">
-        <v>45.380622222222222</v>
+        <v>43.141428571428577</v>
       </c>
       <c r="J104" s="16">
-        <v>3.96716E-3</v>
+        <v>2.5738999999999996E-3</v>
       </c>
       <c r="K104" s="16">
-        <v>7.6967464799999998</v>
+        <v>4.0745186200000001</v>
       </c>
       <c r="L104" s="21">
-        <v>1.5187790760508941E-14</v>
+        <v>3.8779438915317176E-13</v>
       </c>
       <c r="M104" s="21">
-        <v>2.0590819941881997E-16</v>
+        <v>2.1531211961687913E-16</v>
       </c>
       <c r="Q104" s="16">
-        <v>16.5025662</v>
+        <v>4.3959003600000006</v>
       </c>
       <c r="R104" s="23">
-        <v>4.6948410934586531E-9</v>
+        <v>1.5402273032896525E-10</v>
       </c>
       <c r="S104" s="23">
-        <v>1.2651012022538633E-11</v>
+        <v>1.3596143244377566E-13</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.3">
@@ -6295,7 +6288,7 @@
         <v>2</v>
       </c>
       <c r="C105">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D105">
         <v>5</v>
@@ -6304,37 +6297,37 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G105">
-        <v>1375</v>
+        <v>900</v>
       </c>
       <c r="H105" s="8">
-        <v>1.5854545454545454E-2</v>
+        <v>2.0222222222222221E-2</v>
       </c>
       <c r="I105" s="10">
-        <v>46.487854545454546</v>
+        <v>44.225555555555552</v>
       </c>
       <c r="J105" s="16">
-        <v>4.53806E-3</v>
+        <v>2.9292000000000003E-3</v>
       </c>
       <c r="K105" s="16">
-        <v>9.8030528199999996</v>
+        <v>5.5390185399999998</v>
       </c>
       <c r="L105" s="21">
-        <v>4.6464405109889013E-14</v>
+        <v>1.4901997469166348E-14</v>
       </c>
       <c r="M105" s="21">
-        <v>2.068181647074715E-16</v>
+        <v>2.1025872780187197E-16</v>
       </c>
       <c r="Q105" s="16">
-        <v>31.790000933333335</v>
+        <v>8.3908084400000007</v>
       </c>
       <c r="R105" s="23">
-        <v>4.1617999672704015E-9</v>
+        <v>9.3880357060867293E-11</v>
       </c>
       <c r="S105" s="23">
-        <v>1.6428829304690858E-12</v>
+        <v>3.3585867021730076E-13</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.3">
@@ -6342,10 +6335,10 @@
         <v>5</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D106">
         <v>5</v>
@@ -6354,37 +6347,37 @@
         <v>0</v>
       </c>
       <c r="F106">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G106">
-        <v>500</v>
+        <v>1125</v>
       </c>
       <c r="H106" s="8">
-        <v>6.5200000000000008E-2</v>
+        <v>1.2977777777777777E-2</v>
       </c>
       <c r="I106" s="10">
-        <v>35.793599999999998</v>
+        <v>45.380622222222222</v>
       </c>
       <c r="J106" s="16">
-        <v>1.0643599999999999E-3</v>
+        <v>3.96716E-3</v>
       </c>
       <c r="K106" s="16">
-        <v>3.2660372600000001</v>
+        <v>7.6967464799999998</v>
       </c>
       <c r="L106" s="21">
-        <v>4.150742209884161E-14</v>
+        <v>1.5187790760508941E-14</v>
       </c>
       <c r="M106" s="21">
-        <v>3.7494034505499536E-16</v>
+        <v>2.0590819941881997E-16</v>
       </c>
       <c r="Q106" s="16">
-        <v>1.7813614600000001</v>
+        <v>16.5025662</v>
       </c>
       <c r="R106" s="23">
-        <v>3.6171699606032962E-13</v>
+        <v>4.6948410934586531E-9</v>
       </c>
       <c r="S106" s="23">
-        <v>5.1917279638947215E-15</v>
+        <v>1.2651012022538633E-11</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.3">
@@ -6392,10 +6385,10 @@
         <v>5</v>
       </c>
       <c r="B107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D107">
         <v>5</v>
@@ -6404,37 +6397,37 @@
         <v>0</v>
       </c>
       <c r="F107">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G107">
-        <v>1250</v>
+        <v>1375</v>
       </c>
       <c r="H107" s="8">
-        <v>4.9439999999999998E-2</v>
+        <v>1.5854545454545454E-2</v>
       </c>
       <c r="I107" s="10">
-        <v>36.797759999999997</v>
+        <v>46.487854545454546</v>
       </c>
       <c r="J107" s="16">
-        <v>2.25494E-3</v>
+        <v>4.53806E-3</v>
       </c>
       <c r="K107" s="16">
-        <v>8.1999447800000009</v>
+        <v>9.8030528199999996</v>
       </c>
       <c r="L107" s="21">
-        <v>3.6750446427367134E-14</v>
+        <v>4.6464405109889013E-14</v>
       </c>
       <c r="M107" s="21">
-        <v>3.312044730280428E-16</v>
+        <v>2.068181647074715E-16</v>
       </c>
       <c r="Q107" s="16">
-        <v>12.733139099999999</v>
+        <v>31.790000933333335</v>
       </c>
       <c r="R107" s="23">
-        <v>5.3492872272192522E-12</v>
+        <v>4.1617999672704015E-9</v>
       </c>
       <c r="S107" s="23">
-        <v>4.4684299183482005E-14</v>
+        <v>1.6428829304690858E-12</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.3">
@@ -6445,46 +6438,46 @@
         <v>3</v>
       </c>
       <c r="C108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E108">
         <v>0</v>
       </c>
       <c r="F108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G108">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="H108" s="8">
-        <v>4.2533333333333333E-2</v>
+        <v>6.5200000000000008E-2</v>
       </c>
       <c r="I108" s="10">
-        <v>38.0944</v>
+        <v>35.793599999999998</v>
       </c>
       <c r="J108" s="16">
-        <v>3.6237333333333337E-3</v>
+        <v>1.0643599999999999E-3</v>
       </c>
       <c r="K108" s="16">
-        <v>18.169718133333333</v>
+        <v>3.2660372600000001</v>
       </c>
       <c r="L108" s="21">
-        <v>3.5960977846467271E-14</v>
+        <v>4.150742209884161E-14</v>
       </c>
       <c r="M108" s="21">
-        <v>3.1375495388067941E-16</v>
+        <v>3.7494034505499536E-16</v>
       </c>
       <c r="Q108" s="16">
-        <v>106.53776413333333</v>
+        <v>1.7813614600000001</v>
       </c>
       <c r="R108" s="23">
-        <v>3.5097177365450714E-11</v>
+        <v>3.6171699606032962E-13</v>
       </c>
       <c r="S108" s="23">
-        <v>3.9393172071118404E-14</v>
+        <v>5.1917279638947215E-15</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.3">
@@ -6495,37 +6488,46 @@
         <v>3</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G109">
-        <v>4375</v>
+        <v>1250</v>
       </c>
       <c r="H109" s="8">
-        <v>4.3428571428571427E-2</v>
+        <v>4.9439999999999998E-2</v>
       </c>
       <c r="I109" s="10">
-        <v>40.537371428571426</v>
+        <v>36.797759999999997</v>
       </c>
       <c r="J109" s="16">
-        <v>7.2175E-3</v>
+        <v>2.25494E-3</v>
       </c>
       <c r="K109" s="16">
-        <v>40.470895000000006</v>
+        <v>8.1999447800000009</v>
       </c>
       <c r="L109" s="21">
-        <v>3.7320878384676091E-12</v>
+        <v>3.6750446427367134E-14</v>
       </c>
       <c r="M109" s="21">
-        <v>3.035776384633188E-16</v>
+        <v>3.312044730280428E-16</v>
+      </c>
+      <c r="Q109" s="16">
+        <v>12.733139099999999</v>
+      </c>
+      <c r="R109" s="23">
+        <v>5.3492872272192522E-12</v>
+      </c>
+      <c r="S109" s="23">
+        <v>4.4684299183482005E-14</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.3">
@@ -6533,140 +6535,131 @@
         <v>5</v>
       </c>
       <c r="B110">
+        <v>3</v>
+      </c>
+      <c r="C110">
         <v>4</v>
       </c>
-      <c r="C110">
-        <v>2</v>
-      </c>
       <c r="D110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G110">
-        <v>3125</v>
+        <v>2500</v>
       </c>
       <c r="H110" s="8">
-        <v>9.1200000000000003E-2</v>
+        <v>4.2533333333333333E-2</v>
       </c>
       <c r="I110" s="10">
-        <v>36.86112</v>
+        <v>38.0944</v>
       </c>
       <c r="J110" s="16">
-        <v>3.5699999999999998E-3</v>
+        <v>3.6237333333333337E-3</v>
       </c>
       <c r="K110" s="16">
-        <v>36.600457300000002</v>
+        <v>18.169718133333333</v>
       </c>
       <c r="L110" s="21">
-        <v>7.586296295965602E-14</v>
+        <v>3.5960977846467271E-14</v>
       </c>
       <c r="M110" s="21">
-        <v>5.0452484515548831E-16</v>
+        <v>3.1375495388067941E-16</v>
+      </c>
+      <c r="Q110" s="16">
+        <v>106.53776413333333</v>
+      </c>
+      <c r="R110" s="23">
+        <v>3.5097177365450714E-11</v>
+      </c>
+      <c r="S110" s="23">
+        <v>3.9393172071118404E-14</v>
       </c>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G111">
-        <v>108</v>
+        <v>4375</v>
       </c>
       <c r="H111" s="8">
-        <v>3.7037037037037035E-2</v>
+        <v>4.3428571428571427E-2</v>
       </c>
       <c r="I111" s="10">
-        <v>34.296296296296291</v>
+        <v>40.537371428571426</v>
       </c>
       <c r="J111" s="16">
-        <v>5.7476000000000001E-4</v>
+        <v>7.2175E-3</v>
       </c>
       <c r="K111" s="16">
-        <v>0.49949194000000008</v>
+        <v>40.470895000000006</v>
       </c>
       <c r="L111" s="21">
-        <v>3.2951693518883698E-14</v>
+        <v>3.7320878384676091E-12</v>
       </c>
       <c r="M111" s="21">
-        <v>3.2604089195961668E-16</v>
-      </c>
-      <c r="Q111" s="16">
-        <v>0.15657246</v>
-      </c>
-      <c r="R111" s="23">
-        <v>6.5121299890427066E-13</v>
-      </c>
-      <c r="S111" s="23">
-        <v>5.8327545996067954E-15</v>
+        <v>3.035776384633188E-16</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D112">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G112">
-        <v>216</v>
+        <v>3125</v>
       </c>
       <c r="H112" s="8">
-        <v>1.8518518518518517E-2</v>
+        <v>9.1200000000000003E-2</v>
       </c>
       <c r="I112" s="10">
-        <v>35.411111111111111</v>
+        <v>36.86112</v>
       </c>
       <c r="J112" s="16">
-        <v>8.6555999999999992E-4</v>
+        <v>3.5699999999999998E-3</v>
       </c>
       <c r="K112" s="16">
-        <v>0.96189133999999998</v>
+        <v>36.600457300000002</v>
       </c>
       <c r="L112" s="21">
-        <v>2.2280773584797067E-14</v>
+        <v>7.586296295965602E-14</v>
       </c>
       <c r="M112" s="21">
-        <v>2.775353550537815E-16</v>
-      </c>
-      <c r="Q112" s="16">
-        <v>0.38666301999999997</v>
-      </c>
-      <c r="R112" s="23">
-        <v>1.4114124593626313E-13</v>
-      </c>
-      <c r="S112" s="23">
-        <v>5.8111683878486103E-15</v>
+        <v>5.0452484515548831E-16</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.3">
@@ -6677,7 +6670,7 @@
         <v>2</v>
       </c>
       <c r="C113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D113">
         <v>5</v>
@@ -6689,34 +6682,34 @@
         <v>5</v>
       </c>
       <c r="G113">
-        <v>360</v>
+        <v>108</v>
       </c>
       <c r="H113" s="8">
-        <v>2.6111111111111113E-2</v>
+        <v>3.7037037037037035E-2</v>
       </c>
       <c r="I113" s="10">
-        <v>38.152222222222221</v>
+        <v>34.296296296296291</v>
       </c>
       <c r="J113" s="16">
-        <v>1.1808600000000002E-3</v>
+        <v>5.7476000000000001E-4</v>
       </c>
       <c r="K113" s="16">
-        <v>1.7728660199999999</v>
+        <v>0.49949194000000008</v>
       </c>
       <c r="L113" s="21">
-        <v>2.2335024315275464E-14</v>
+        <v>3.2951693518883698E-14</v>
       </c>
       <c r="M113" s="21">
-        <v>2.6826869574784005E-16</v>
+        <v>3.2604089195961668E-16</v>
       </c>
       <c r="Q113" s="16">
-        <v>0.89140035999999989</v>
+        <v>0.15657246</v>
       </c>
       <c r="R113" s="23">
-        <v>3.4187730159447699E-12</v>
+        <v>6.5121299890427066E-13</v>
       </c>
       <c r="S113" s="23">
-        <v>1.6614278870848769E-14</v>
+        <v>5.8327545996067954E-15</v>
       </c>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.3">
@@ -6727,7 +6720,7 @@
         <v>2</v>
       </c>
       <c r="C114">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D114">
         <v>5</v>
@@ -6739,34 +6732,34 @@
         <v>5</v>
       </c>
       <c r="G114">
-        <v>540</v>
+        <v>216</v>
       </c>
       <c r="H114" s="8">
-        <v>1.740740740740741E-2</v>
+        <v>1.8518518518518517E-2</v>
       </c>
       <c r="I114" s="10">
-        <v>38.810740740740741</v>
+        <v>35.411111111111111</v>
       </c>
       <c r="J114" s="16">
-        <v>1.5954200000000002E-3</v>
+        <v>8.6555999999999992E-4</v>
       </c>
       <c r="K114" s="16">
-        <v>2.7022699399999999</v>
+        <v>0.96189133999999998</v>
       </c>
       <c r="L114" s="21">
-        <v>4.2929370064810047E-14</v>
+        <v>2.2280773584797067E-14</v>
       </c>
       <c r="M114" s="21">
-        <v>2.5682826709524424E-16</v>
+        <v>2.775353550537815E-16</v>
       </c>
       <c r="Q114" s="16">
-        <v>2.0624484000000001</v>
+        <v>0.38666301999999997</v>
       </c>
       <c r="R114" s="23">
-        <v>2.8885148571738064E-12</v>
+        <v>1.4114124593626313E-13</v>
       </c>
       <c r="S114" s="23">
-        <v>3.3668543790314038E-14</v>
+        <v>5.8111683878486103E-15</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.3">
@@ -6777,7 +6770,7 @@
         <v>2</v>
       </c>
       <c r="C115">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D115">
         <v>5</v>
@@ -6789,34 +6782,34 @@
         <v>5</v>
       </c>
       <c r="G115">
-        <v>756</v>
+        <v>360</v>
       </c>
       <c r="H115" s="8">
-        <v>2.1693121693121691E-2</v>
+        <v>2.6111111111111113E-2</v>
       </c>
       <c r="I115" s="10">
-        <v>41.141269841269839</v>
+        <v>38.152222222222221</v>
       </c>
       <c r="J115" s="16">
-        <v>2.0802400000000006E-3</v>
+        <v>1.1808600000000002E-3</v>
       </c>
       <c r="K115" s="16">
-        <v>4.4196238999999995</v>
+        <v>1.7728660199999999</v>
       </c>
       <c r="L115" s="21">
-        <v>2.4881551421311994E-14</v>
+        <v>2.2335024315275464E-14</v>
       </c>
       <c r="M115" s="21">
-        <v>2.5134843055559786E-16</v>
+        <v>2.6826869574784005E-16</v>
       </c>
       <c r="Q115" s="16">
-        <v>4.7410546200000008</v>
+        <v>0.89140035999999989</v>
       </c>
       <c r="R115" s="23">
-        <v>1.527669279158425E-11</v>
+        <v>3.4187730159447699E-12</v>
       </c>
       <c r="S115" s="23">
-        <v>5.4042023543274418E-14</v>
+        <v>1.6614278870848769E-14</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.3">
@@ -6827,7 +6820,7 @@
         <v>2</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D116">
         <v>5</v>
@@ -6836,37 +6829,37 @@
         <v>0</v>
       </c>
       <c r="F116">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G116">
-        <v>1008</v>
+        <v>540</v>
       </c>
       <c r="H116" s="8">
-        <v>2.103174603174603E-2</v>
+        <v>1.740740740740741E-2</v>
       </c>
       <c r="I116" s="10">
-        <v>42.817261904761907</v>
+        <v>38.810740740740741</v>
       </c>
       <c r="J116" s="16">
-        <v>2.6401599999999999E-3</v>
+        <v>1.5954200000000002E-3</v>
       </c>
       <c r="K116" s="16">
-        <v>6.8269274400000004</v>
+        <v>2.7022699399999999</v>
       </c>
       <c r="L116" s="21">
-        <v>3.989523845769286E-13</v>
+        <v>4.2929370064810047E-14</v>
       </c>
       <c r="M116" s="21">
-        <v>2.4368210289639596E-16</v>
+        <v>2.5682826709524424E-16</v>
       </c>
       <c r="Q116" s="16">
-        <v>10.820841566666667</v>
+        <v>2.0624484000000001</v>
       </c>
       <c r="R116" s="23">
-        <v>5.4407729093785094E-10</v>
+        <v>2.8885148571738064E-12</v>
       </c>
       <c r="S116" s="23">
-        <v>2.2454569809768172E-13</v>
+        <v>3.3668543790314038E-14</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.3">
@@ -6877,7 +6870,7 @@
         <v>2</v>
       </c>
       <c r="C117">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D117">
         <v>5</v>
@@ -6886,37 +6879,37 @@
         <v>0</v>
       </c>
       <c r="F117">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G117">
-        <v>1296</v>
+        <v>756</v>
       </c>
       <c r="H117" s="8">
-        <v>1.1574074074074075E-2</v>
+        <v>2.1693121693121691E-2</v>
       </c>
       <c r="I117" s="10">
-        <v>43.284104938271604</v>
+        <v>41.141269841269839</v>
       </c>
       <c r="J117" s="16">
-        <v>3.5624599999999999E-3</v>
+        <v>2.0802400000000006E-3</v>
       </c>
       <c r="K117" s="16">
-        <v>8.5879345600000008</v>
+        <v>4.4196238999999995</v>
       </c>
       <c r="L117" s="21">
-        <v>2.8940116364988023E-14</v>
+        <v>2.4881551421311994E-14</v>
       </c>
       <c r="M117" s="21">
-        <v>2.38730216706383E-16</v>
+        <v>2.5134843055559786E-16</v>
       </c>
       <c r="Q117" s="16">
-        <v>23.0620048</v>
+        <v>4.7410546200000008</v>
       </c>
       <c r="R117" s="23">
-        <v>1.6392681843978063E-9</v>
+        <v>1.527669279158425E-11</v>
       </c>
       <c r="S117" s="23">
-        <v>3.8379790369403259E-12</v>
+        <v>5.4042023543274418E-14</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.3">
@@ -6927,46 +6920,46 @@
         <v>2</v>
       </c>
       <c r="C118">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G118">
-        <v>1620</v>
+        <v>1008</v>
       </c>
       <c r="H118" s="8">
-        <v>1.5637860082304524E-2</v>
+        <v>2.103174603174603E-2</v>
       </c>
       <c r="I118" s="10">
-        <v>45.101851851851855</v>
+        <v>42.817261904761907</v>
       </c>
       <c r="J118" s="16">
-        <v>5.1473333333333336E-3</v>
+        <v>2.6401599999999999E-3</v>
       </c>
       <c r="K118" s="16">
-        <v>11.7958102</v>
+        <v>6.8269274400000004</v>
       </c>
       <c r="L118" s="21">
-        <v>2.7295618335376128E-14</v>
+        <v>3.989523845769286E-13</v>
       </c>
       <c r="M118" s="21">
-        <v>2.338866286165698E-16</v>
+        <v>2.4368210289639596E-16</v>
       </c>
       <c r="Q118" s="16">
-        <v>46.985986799999999</v>
+        <v>10.820841566666667</v>
       </c>
       <c r="R118" s="23">
-        <v>1.0093041449742465E-9</v>
+        <v>5.4407729093785094E-10</v>
       </c>
       <c r="S118" s="23">
-        <v>7.5560159000718528E-13</v>
+        <v>2.2454569809768172E-13</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.3">
@@ -6977,46 +6970,46 @@
         <v>2</v>
       </c>
       <c r="C119">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G119">
-        <v>1980</v>
+        <v>1296</v>
       </c>
       <c r="H119" s="8">
-        <v>1.8013468013468013E-2</v>
+        <v>1.1574074074074075E-2</v>
       </c>
       <c r="I119" s="10">
-        <v>46.935690235690238</v>
+        <v>43.284104938271604</v>
       </c>
       <c r="J119" s="16">
-        <v>6.3254666666666673E-3</v>
+        <v>3.5624599999999999E-3</v>
       </c>
       <c r="K119" s="16">
-        <v>16.711406533333331</v>
+        <v>8.5879345600000008</v>
       </c>
       <c r="L119" s="21">
-        <v>2.6698552285433069E-14</v>
+        <v>2.8940116364988023E-14</v>
       </c>
       <c r="M119" s="21">
-        <v>2.378899902841658E-16</v>
+        <v>2.38730216706383E-16</v>
       </c>
       <c r="Q119" s="16">
-        <v>102.3523395</v>
+        <v>23.0620048</v>
       </c>
       <c r="R119" s="23">
-        <v>2.2121601319005154E-8</v>
+        <v>1.6392681843978063E-9</v>
       </c>
       <c r="S119" s="23">
-        <v>6.3436970207141882E-11</v>
+        <v>3.8379790369403259E-12</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.3">
@@ -7024,49 +7017,49 @@
         <v>6</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D120">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G120">
-        <v>864</v>
+        <v>1620</v>
       </c>
       <c r="H120" s="8">
-        <v>7.1990740740740744E-2</v>
+        <v>1.5637860082304524E-2</v>
       </c>
       <c r="I120" s="10">
-        <v>35.144675925925924</v>
+        <v>45.101851851851855</v>
       </c>
       <c r="J120" s="16">
-        <v>1.1869600000000001E-3</v>
+        <v>5.1473333333333336E-3</v>
       </c>
       <c r="K120" s="16">
-        <v>6.5706771599999998</v>
+        <v>11.7958102</v>
       </c>
       <c r="L120" s="21">
-        <v>9.1869981011647501E-14</v>
+        <v>2.7295618335376128E-14</v>
       </c>
       <c r="M120" s="21">
-        <v>4.5479560188518037E-16</v>
+        <v>2.338866286165698E-16</v>
       </c>
       <c r="Q120" s="16">
-        <v>5.5931552</v>
+        <v>46.985986799999999</v>
       </c>
       <c r="R120" s="23">
-        <v>3.6933869379721647E-13</v>
+        <v>1.0093041449742465E-9</v>
       </c>
       <c r="S120" s="23">
-        <v>8.1950857685226958E-15</v>
+        <v>7.5560159000718528E-13</v>
       </c>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.3">
@@ -7074,10 +7067,10 @@
         <v>6</v>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D121">
         <v>3</v>
@@ -7089,131 +7082,134 @@
         <v>1</v>
       </c>
       <c r="G121">
-        <v>2160</v>
+        <v>1980</v>
       </c>
       <c r="H121" s="8">
-        <v>6.2808641975308638E-2</v>
+        <v>1.8013468013468013E-2</v>
       </c>
       <c r="I121" s="10">
-        <v>36.88148148148148</v>
+        <v>46.935690235690238</v>
       </c>
       <c r="J121" s="16">
-        <v>2.448733333333333E-3</v>
+        <v>6.3254666666666673E-3</v>
       </c>
       <c r="K121" s="16">
-        <v>19.087586566666669</v>
+        <v>16.711406533333331</v>
       </c>
       <c r="L121" s="21">
-        <v>7.3427908324914067E-14</v>
+        <v>2.6698552285433069E-14</v>
       </c>
       <c r="M121" s="21">
-        <v>4.0285231789900132E-16</v>
+        <v>2.378899902841658E-16</v>
       </c>
       <c r="Q121" s="16">
-        <v>63.633648000000001</v>
+        <v>102.3523395</v>
       </c>
       <c r="R121" s="23">
-        <v>8.4922962994015287E-12</v>
+        <v>2.2121601319005154E-8</v>
       </c>
       <c r="S121" s="23">
-        <v>1.1454824067240635E-13</v>
+        <v>6.3436970207141882E-11</v>
       </c>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A122" s="12">
+      <c r="A122">
         <v>6</v>
       </c>
-      <c r="B122" s="12">
-        <v>4</v>
-      </c>
-      <c r="C122" s="12">
-        <v>1</v>
-      </c>
-      <c r="D122" s="12">
-        <v>1</v>
-      </c>
-      <c r="E122" s="12">
-        <v>0</v>
-      </c>
-      <c r="F122" s="12">
-        <v>0</v>
-      </c>
-      <c r="G122" s="12">
-        <v>1296</v>
-      </c>
-      <c r="H122" s="13">
-        <v>3</v>
-      </c>
-      <c r="I122" s="14">
-        <v>235.04706790123456</v>
-      </c>
-      <c r="J122" s="17">
-        <v>1.5852999999999999E-2</v>
-      </c>
-      <c r="K122" s="17">
-        <v>185.23384769999998</v>
-      </c>
-      <c r="L122" s="22">
-        <v>9.4173073500436701E-7</v>
-      </c>
-      <c r="M122" s="22">
-        <v>2.3286213950755185E-14</v>
-      </c>
-      <c r="N122" s="17"/>
-      <c r="O122" s="24"/>
-      <c r="P122" s="24"/>
-      <c r="Q122" s="17"/>
-      <c r="R122" s="24"/>
-      <c r="S122" s="24"/>
+      <c r="B122">
+        <v>3</v>
+      </c>
+      <c r="C122">
+        <v>2</v>
+      </c>
+      <c r="D122">
+        <v>5</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>5</v>
+      </c>
+      <c r="G122">
+        <v>864</v>
+      </c>
+      <c r="H122" s="8">
+        <v>7.1990740740740744E-2</v>
+      </c>
+      <c r="I122" s="10">
+        <v>35.144675925925924</v>
+      </c>
+      <c r="J122" s="16">
+        <v>1.1869600000000001E-3</v>
+      </c>
+      <c r="K122" s="16">
+        <v>6.5706771599999998</v>
+      </c>
+      <c r="L122" s="21">
+        <v>9.1869981011647501E-14</v>
+      </c>
+      <c r="M122" s="21">
+        <v>4.5479560188518037E-16</v>
+      </c>
+      <c r="Q122" s="16">
+        <v>5.5931552</v>
+      </c>
+      <c r="R122" s="23">
+        <v>3.6933869379721647E-13</v>
+      </c>
+      <c r="S122" s="23">
+        <v>8.1950857685226958E-15</v>
+      </c>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D123">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E123">
         <v>0</v>
       </c>
       <c r="F123">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G123">
-        <v>147</v>
+        <v>2160</v>
       </c>
       <c r="H123" s="8">
-        <v>5.8503401360544216E-2</v>
+        <v>6.2808641975308638E-2</v>
       </c>
       <c r="I123" s="10">
-        <v>35.657142857142858</v>
+        <v>36.88148148148148</v>
       </c>
       <c r="J123" s="16">
-        <v>5.7081999999999999E-4</v>
+        <v>2.448733333333333E-3</v>
       </c>
       <c r="K123" s="16">
-        <v>0.84981883999999996</v>
+        <v>19.087586566666669</v>
       </c>
       <c r="L123" s="21">
-        <v>4.3767370310090991E-14</v>
+        <v>7.3427908324914067E-14</v>
       </c>
       <c r="M123" s="21">
-        <v>3.6229968385960142E-16</v>
+        <v>4.0285231789900132E-16</v>
       </c>
       <c r="Q123" s="16">
-        <v>0.24576959999999998</v>
+        <v>63.633648000000001</v>
       </c>
       <c r="R123" s="23">
-        <v>4.682050455932844E-13</v>
+        <v>8.4922962994015287E-12</v>
       </c>
       <c r="S123" s="23">
-        <v>6.0345259148311915E-15</v>
+        <v>1.1454824067240635E-13</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.3">
@@ -7224,7 +7220,7 @@
         <v>2</v>
       </c>
       <c r="C124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D124">
         <v>5</v>
@@ -7236,34 +7232,34 @@
         <v>5</v>
       </c>
       <c r="G124">
-        <v>294</v>
+        <v>147</v>
       </c>
       <c r="H124" s="8">
-        <v>3.1292517006802717E-2</v>
+        <v>5.8503401360544216E-2</v>
       </c>
       <c r="I124" s="10">
-        <v>35.801360544217687</v>
+        <v>35.657142857142858</v>
       </c>
       <c r="J124" s="16">
-        <v>9.1216000000000008E-4</v>
+        <v>5.7081999999999999E-4</v>
       </c>
       <c r="K124" s="16">
-        <v>1.4183857999999998</v>
+        <v>0.84981883999999996</v>
       </c>
       <c r="L124" s="21">
-        <v>4.9959691434702983E-14</v>
+        <v>4.3767370310090991E-14</v>
       </c>
       <c r="M124" s="21">
-        <v>3.3077393165211246E-16</v>
+        <v>3.6229968385960142E-16</v>
       </c>
       <c r="Q124" s="16">
-        <v>0.67656028000000001</v>
+        <v>0.24576959999999998</v>
       </c>
       <c r="R124" s="23">
-        <v>1.5703322068510688E-13</v>
+        <v>4.682050455932844E-13</v>
       </c>
       <c r="S124" s="23">
-        <v>5.48789117115168E-15</v>
+        <v>6.0345259148311915E-15</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.3">
@@ -7274,7 +7270,7 @@
         <v>2</v>
       </c>
       <c r="C125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D125">
         <v>5</v>
@@ -7286,34 +7282,34 @@
         <v>5</v>
       </c>
       <c r="G125">
-        <v>490</v>
+        <v>294</v>
       </c>
       <c r="H125" s="8">
-        <v>2.6122448979591838E-2</v>
+        <v>3.1292517006802717E-2</v>
       </c>
       <c r="I125" s="10">
-        <v>37.667755102040815</v>
+        <v>35.801360544217687</v>
       </c>
       <c r="J125" s="16">
-        <v>1.13868E-3</v>
+        <v>9.1216000000000008E-4</v>
       </c>
       <c r="K125" s="16">
-        <v>2.55513536</v>
+        <v>1.4183857999999998</v>
       </c>
       <c r="L125" s="21">
-        <v>4.1938934253409277E-14</v>
+        <v>4.9959691434702983E-14</v>
       </c>
       <c r="M125" s="21">
-        <v>2.9447861754664451E-16</v>
+        <v>3.3077393165211246E-16</v>
       </c>
       <c r="Q125" s="16">
-        <v>1.6750416399999999</v>
+        <v>0.67656028000000001</v>
       </c>
       <c r="R125" s="23">
-        <v>1.000249708918202E-11</v>
+        <v>1.5703322068510688E-13</v>
       </c>
       <c r="S125" s="23">
-        <v>1.9009847282048258E-13</v>
+        <v>5.48789117115168E-15</v>
       </c>
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.3">
@@ -7324,7 +7320,7 @@
         <v>2</v>
       </c>
       <c r="C126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D126">
         <v>5</v>
@@ -7336,34 +7332,34 @@
         <v>5</v>
       </c>
       <c r="G126">
-        <v>735</v>
+        <v>490</v>
       </c>
       <c r="H126" s="8">
-        <v>1.5238095238095236E-2</v>
+        <v>2.6122448979591838E-2</v>
       </c>
       <c r="I126" s="10">
-        <v>38.644081632653062</v>
+        <v>37.667755102040815</v>
       </c>
       <c r="J126" s="16">
-        <v>1.5916200000000002E-3</v>
+        <v>1.13868E-3</v>
       </c>
       <c r="K126" s="16">
-        <v>4.0244523599999997</v>
+        <v>2.55513536</v>
       </c>
       <c r="L126" s="21">
-        <v>4.7144511320644433E-14</v>
+        <v>4.1938934253409277E-14</v>
       </c>
       <c r="M126" s="21">
-        <v>2.9218715468571781E-16</v>
+        <v>2.9447861754664451E-16</v>
       </c>
       <c r="Q126" s="16">
-        <v>4.4124036600000007</v>
+        <v>1.6750416399999999</v>
       </c>
       <c r="R126" s="23">
-        <v>1.6457575049729394E-11</v>
+        <v>1.000249708918202E-11</v>
       </c>
       <c r="S126" s="23">
-        <v>4.3295340963389813E-14</v>
+        <v>1.9009847282048258E-13</v>
       </c>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.3">
@@ -7374,7 +7370,7 @@
         <v>2</v>
       </c>
       <c r="C127">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D127">
         <v>5</v>
@@ -7383,37 +7379,37 @@
         <v>0</v>
       </c>
       <c r="F127">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G127">
-        <v>1029</v>
+        <v>735</v>
       </c>
       <c r="H127" s="8">
-        <v>1.6132167152575316E-2</v>
+        <v>1.5238095238095236E-2</v>
       </c>
       <c r="I127" s="10">
-        <v>40.696404275996109</v>
+        <v>38.644081632653062</v>
       </c>
       <c r="J127" s="16">
-        <v>2.3885600000000001E-3</v>
+        <v>1.5916200000000002E-3</v>
       </c>
       <c r="K127" s="16">
-        <v>6.4889960000000002</v>
+        <v>4.0244523599999997</v>
       </c>
       <c r="L127" s="21">
-        <v>4.4763491019978893E-14</v>
+        <v>4.7144511320644433E-14</v>
       </c>
       <c r="M127" s="21">
-        <v>2.8133949240236638E-16</v>
+        <v>2.9218715468571781E-16</v>
       </c>
       <c r="Q127" s="16">
-        <v>11.320121700000001</v>
+        <v>4.4124036600000007</v>
       </c>
       <c r="R127" s="23">
-        <v>7.0330988126507419E-11</v>
+        <v>1.6457575049729394E-11</v>
       </c>
       <c r="S127" s="23">
-        <v>9.3471650781588237E-14</v>
+        <v>4.3295340963389813E-14</v>
       </c>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.3">
@@ -7424,7 +7420,7 @@
         <v>2</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D128">
         <v>5</v>
@@ -7436,34 +7432,34 @@
         <v>3</v>
       </c>
       <c r="G128">
-        <v>1372</v>
+        <v>1029</v>
       </c>
       <c r="H128" s="8">
-        <v>1.6763848396501458E-2</v>
+        <v>1.6132167152575316E-2</v>
       </c>
       <c r="I128" s="10">
-        <v>42.527551020408161</v>
+        <v>40.696404275996109</v>
       </c>
       <c r="J128" s="16">
-        <v>3.0201999999999998E-3</v>
+        <v>2.3885600000000001E-3</v>
       </c>
       <c r="K128" s="16">
-        <v>9.5750178399999992</v>
+        <v>6.4889960000000002</v>
       </c>
       <c r="L128" s="21">
-        <v>6.165547267498417E-14</v>
+        <v>4.4763491019978893E-14</v>
       </c>
       <c r="M128" s="21">
-        <v>2.7313915013056855E-16</v>
+        <v>2.8133949240236638E-16</v>
       </c>
       <c r="Q128" s="16">
-        <v>26.342604733333335</v>
+        <v>11.320121700000001</v>
       </c>
       <c r="R128" s="23">
-        <v>1.1004515970393257E-9</v>
+        <v>7.0330988126507419E-11</v>
       </c>
       <c r="S128" s="23">
-        <v>1.7125696000692982E-12</v>
+        <v>9.3471650781588237E-14</v>
       </c>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.3">
@@ -7474,46 +7470,46 @@
         <v>2</v>
       </c>
       <c r="C129">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D129">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G129">
-        <v>1764</v>
+        <v>1372</v>
       </c>
       <c r="H129" s="8">
-        <v>2.1352985638699924E-2</v>
+        <v>1.6763848396501458E-2</v>
       </c>
       <c r="I129" s="10">
-        <v>44.256046863189717</v>
+        <v>42.527551020408161</v>
       </c>
       <c r="J129" s="16">
-        <v>3.678866666666667E-3</v>
+        <v>3.0201999999999998E-3</v>
       </c>
       <c r="K129" s="16">
-        <v>13.549375533333333</v>
+        <v>9.5750178399999992</v>
       </c>
       <c r="L129" s="21">
-        <v>4.6109730141503417E-14</v>
+        <v>6.165547267498417E-14</v>
       </c>
       <c r="M129" s="21">
-        <v>2.691275822995595E-16</v>
+        <v>2.7313915013056855E-16</v>
       </c>
       <c r="Q129" s="16">
-        <v>61.218966299999998</v>
+        <v>26.342604733333335</v>
       </c>
       <c r="R129" s="23">
-        <v>6.3768511610331396E-9</v>
+        <v>1.1004515970393257E-9</v>
       </c>
       <c r="S129" s="23">
-        <v>1.8693299570517099E-11</v>
+        <v>1.7125696000692982E-12</v>
       </c>
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.3">
@@ -7524,7 +7520,7 @@
         <v>2</v>
       </c>
       <c r="C130">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D130">
         <v>3</v>
@@ -7536,34 +7532,34 @@
         <v>1</v>
       </c>
       <c r="G130">
-        <v>2205</v>
+        <v>1764</v>
       </c>
       <c r="H130" s="8">
-        <v>1.7687074829931974E-2</v>
+        <v>2.1352985638699924E-2</v>
       </c>
       <c r="I130" s="10">
-        <v>45.458956916099773</v>
+        <v>44.256046863189717</v>
       </c>
       <c r="J130" s="16">
-        <v>4.5929999999999999E-3</v>
+        <v>3.678866666666667E-3</v>
       </c>
       <c r="K130" s="16">
-        <v>18.652216299999999</v>
+        <v>13.549375533333333</v>
       </c>
       <c r="L130" s="21">
-        <v>6.9914269748995936E-14</v>
+        <v>4.6109730141503417E-14</v>
       </c>
       <c r="M130" s="21">
-        <v>2.6717841905966925E-16</v>
+        <v>2.691275822995595E-16</v>
       </c>
       <c r="Q130" s="16">
-        <v>148.0203487</v>
+        <v>61.218966299999998</v>
       </c>
       <c r="R130" s="23">
-        <v>6.4137765172045439E-9</v>
+        <v>6.3768511610331396E-9</v>
       </c>
       <c r="S130" s="23">
-        <v>1.2826927984398869E-11</v>
+        <v>1.8693299570517099E-11</v>
       </c>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.3">
@@ -7574,7 +7570,7 @@
         <v>2</v>
       </c>
       <c r="C131">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D131">
         <v>3</v>
@@ -7586,34 +7582,34 @@
         <v>1</v>
       </c>
       <c r="G131">
-        <v>2695</v>
+        <v>2205</v>
       </c>
       <c r="H131" s="8">
-        <v>1.5089672232529374E-2</v>
+        <v>1.7687074829931974E-2</v>
       </c>
       <c r="I131" s="10">
-        <v>45.776870748299324</v>
+        <v>45.458956916099773</v>
       </c>
       <c r="J131" s="16">
-        <v>5.7049333333333329E-3</v>
+        <v>4.5929999999999999E-3</v>
       </c>
       <c r="K131" s="16">
-        <v>23.026384266666668</v>
+        <v>18.652216299999999</v>
       </c>
       <c r="L131" s="21">
-        <v>4.3380543653820285E-14</v>
+        <v>6.9914269748995936E-14</v>
       </c>
       <c r="M131" s="21">
-        <v>2.6953202427085754E-16</v>
+        <v>2.6717841905966925E-16</v>
       </c>
       <c r="Q131" s="16">
-        <v>205.9769426</v>
+        <v>148.0203487</v>
       </c>
       <c r="R131" s="23">
-        <v>3.5186731033620087E-8</v>
+        <v>6.4137765172045439E-9</v>
       </c>
       <c r="S131" s="23">
-        <v>3.3139170574329736E-11</v>
+        <v>1.2826927984398869E-11</v>
       </c>
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.3">
@@ -7621,10 +7617,10 @@
         <v>7</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D132">
         <v>3</v>
@@ -7633,37 +7629,37 @@
         <v>0</v>
       </c>
       <c r="F132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G132">
-        <v>1372</v>
+        <v>2695</v>
       </c>
       <c r="H132" s="8">
-        <v>9.8882410106899896E-2</v>
+        <v>1.5089672232529374E-2</v>
       </c>
       <c r="I132" s="10">
-        <v>36.218901846452866</v>
+        <v>45.776870748299324</v>
       </c>
       <c r="J132" s="16">
-        <v>1.2840999999999998E-3</v>
+        <v>5.7049333333333329E-3</v>
       </c>
       <c r="K132" s="16">
-        <v>14.6364207</v>
+        <v>23.026384266666668</v>
       </c>
       <c r="L132" s="21">
-        <v>1.642595691875193E-13</v>
+        <v>4.3380543653820285E-14</v>
       </c>
       <c r="M132" s="21">
-        <v>5.3245455941085429E-16</v>
+        <v>2.6953202427085754E-16</v>
       </c>
       <c r="Q132" s="16">
-        <v>17.948652633333335</v>
+        <v>205.9769426</v>
       </c>
       <c r="R132" s="23">
-        <v>2.0200024259194053E-12</v>
+        <v>3.5186731033620087E-8</v>
       </c>
       <c r="S132" s="23">
-        <v>8.7584853768689402E-15</v>
+        <v>3.3139170574329736E-11</v>
       </c>
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.3">
@@ -7674,87 +7670,87 @@
         <v>3</v>
       </c>
       <c r="C133">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G133">
-        <v>3430</v>
+        <v>1372</v>
       </c>
       <c r="H133" s="8">
-        <v>7.1720116618075799E-2</v>
+        <v>9.8882410106899896E-2</v>
       </c>
       <c r="I133" s="10">
-        <v>37.159183673469386</v>
+        <v>36.218901846452866</v>
       </c>
       <c r="J133" s="16">
-        <v>2.7268000000000001E-3</v>
+        <v>1.2840999999999998E-3</v>
       </c>
       <c r="K133" s="16">
-        <v>39.222806599999998</v>
+        <v>14.6364207</v>
       </c>
       <c r="L133" s="21">
-        <v>1.3577917115858543E-13</v>
+        <v>1.642595691875193E-13</v>
       </c>
       <c r="M133" s="21">
-        <v>4.6700913246606915E-16</v>
+        <v>5.3245455941085429E-16</v>
+      </c>
+      <c r="Q133" s="16">
+        <v>17.948652633333335</v>
+      </c>
+      <c r="R133" s="23">
+        <v>2.0200024259194053E-12</v>
+      </c>
+      <c r="S133" s="23">
+        <v>8.7584853768689402E-15</v>
       </c>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D134">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G134">
-        <v>300</v>
+        <v>3430</v>
       </c>
       <c r="H134" s="8">
-        <v>4.9333333333333333E-2</v>
+        <v>7.1720116618075799E-2</v>
       </c>
       <c r="I134" s="10">
-        <v>34.320000000000007</v>
+        <v>37.159183673469386</v>
       </c>
       <c r="J134" s="16">
-        <v>6.4199999999999999E-4</v>
+        <v>2.7268000000000001E-3</v>
       </c>
       <c r="K134" s="16">
-        <v>1.8261372000000002</v>
+        <v>39.222806599999998</v>
       </c>
       <c r="L134" s="21">
-        <v>2.9126520917189191E-13</v>
+        <v>1.3577917115858543E-13</v>
       </c>
       <c r="M134" s="21">
-        <v>5.214004548961415E-16</v>
-      </c>
-      <c r="Q134" s="16">
-        <v>0.88176655999999998</v>
-      </c>
-      <c r="R134" s="23">
-        <v>6.1198168891026161E-13</v>
-      </c>
-      <c r="S134" s="23">
-        <v>9.4429430014736385E-15</v>
+        <v>4.6700913246606915E-16</v>
       </c>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.3">
@@ -7765,7 +7761,7 @@
         <v>2</v>
       </c>
       <c r="C135">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D135">
         <v>5</v>
@@ -7777,34 +7773,34 @@
         <v>5</v>
       </c>
       <c r="G135">
-        <v>600</v>
-      </c>
-      <c r="H135" s="8">
-        <v>3.5666666666666666E-2</v>
-      </c>
-      <c r="I135" s="10">
-        <v>35.509</v>
-      </c>
-      <c r="J135" s="16">
-        <v>9.6982000000000004E-4</v>
-      </c>
-      <c r="K135" s="16">
-        <v>3.8893313200000001</v>
-      </c>
-      <c r="L135" s="21">
-        <v>2.438231097973018E-13</v>
-      </c>
-      <c r="M135" s="21">
-        <v>4.5247805810635977E-16</v>
+        <v>300</v>
+      </c>
+      <c r="H135" s="49">
+        <v>6.13E-2</v>
+      </c>
+      <c r="I135" s="50">
+        <v>34.5</v>
+      </c>
+      <c r="J135" s="51">
+        <v>7.4599999999999996E-3</v>
+      </c>
+      <c r="K135" s="51">
+        <v>2.375</v>
+      </c>
+      <c r="L135" s="52">
+        <v>1.2999999999999999E-12</v>
+      </c>
+      <c r="M135" s="52">
+        <v>5.34E-16</v>
       </c>
       <c r="Q135" s="16">
-        <v>2.8232591999999999</v>
+        <v>0.88176655999999998</v>
       </c>
       <c r="R135" s="23">
-        <v>5.0217809093392962E-12</v>
+        <v>6.1198168891026161E-13</v>
       </c>
       <c r="S135" s="23">
-        <v>5.9206065875100495E-14</v>
+        <v>9.4429430014736385E-15</v>
       </c>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.3">
@@ -7815,7 +7811,7 @@
         <v>2</v>
       </c>
       <c r="C136">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D136">
         <v>5</v>
@@ -7827,34 +7823,34 @@
         <v>5</v>
       </c>
       <c r="G136">
-        <v>1000</v>
-      </c>
-      <c r="H136" s="8">
-        <v>3.0600000000000002E-2</v>
-      </c>
-      <c r="I136" s="10">
-        <v>37.687199999999997</v>
-      </c>
-      <c r="J136" s="16">
-        <v>1.3290400000000001E-3</v>
-      </c>
-      <c r="K136" s="16">
-        <v>7.3652457600000005</v>
-      </c>
-      <c r="L136" s="21">
-        <v>2.5668629829524697E-13</v>
-      </c>
-      <c r="M136" s="21">
-        <v>4.2010198969791927E-16</v>
+        <v>600</v>
+      </c>
+      <c r="H136" s="49">
+        <v>4.36E-2</v>
+      </c>
+      <c r="I136" s="50">
+        <v>36.137999999999998</v>
+      </c>
+      <c r="J136" s="51">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="K136" s="51">
+        <v>3.9319000000000002</v>
+      </c>
+      <c r="L136" s="52">
+        <v>2.4199999999999998E-13</v>
+      </c>
+      <c r="M136" s="52">
+        <v>4.5899999999999996E-16</v>
       </c>
       <c r="Q136" s="16">
-        <v>9.4948389399999993</v>
+        <v>2.8232591999999999</v>
       </c>
       <c r="R136" s="23">
-        <v>5.4344423379448989E-12</v>
+        <v>5.0217809093392962E-12</v>
       </c>
       <c r="S136" s="23">
-        <v>2.6273268378747125E-14</v>
+        <v>5.9206065875100495E-14</v>
       </c>
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.3">
@@ -7865,46 +7861,46 @@
         <v>2</v>
       </c>
       <c r="C137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D137">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E137">
         <v>0</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G137">
-        <v>1500</v>
-      </c>
-      <c r="H137" s="8">
-        <v>2.7111111111111107E-2</v>
-      </c>
-      <c r="I137" s="10">
-        <v>39.382444444444445</v>
-      </c>
-      <c r="J137" s="16">
-        <v>1.8703333333333332E-3</v>
-      </c>
-      <c r="K137" s="16">
-        <v>12.103892199999999</v>
-      </c>
-      <c r="L137" s="21">
-        <v>2.1720586198365025E-13</v>
-      </c>
-      <c r="M137" s="21">
-        <v>4.104803516767629E-16</v>
+        <v>1000</v>
+      </c>
+      <c r="H137" s="49">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="I137" s="50">
+        <v>37.22</v>
+      </c>
+      <c r="J137" s="51">
+        <v>1E-3</v>
+      </c>
+      <c r="K137" s="51">
+        <v>6.31</v>
+      </c>
+      <c r="L137" s="52">
+        <v>2.37E-13</v>
+      </c>
+      <c r="M137" s="52">
+        <v>4.2600000000000002E-16</v>
       </c>
       <c r="Q137" s="16">
-        <v>31.7727264</v>
+        <v>9.4948389399999993</v>
       </c>
       <c r="R137" s="23">
-        <v>1.0818483964618036E-11</v>
+        <v>5.4344423379448989E-12</v>
       </c>
       <c r="S137" s="23">
-        <v>4.5887318376204904E-14</v>
+        <v>2.6273268378747125E-14</v>
       </c>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.3">
@@ -7915,7 +7911,7 @@
         <v>2</v>
       </c>
       <c r="C138">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -7927,144 +7923,194 @@
         <v>1</v>
       </c>
       <c r="G138">
+        <v>1500</v>
+      </c>
+      <c r="H138" s="49">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="I138" s="50">
+        <v>38.636000000000003</v>
+      </c>
+      <c r="J138" s="51">
+        <v>1.8703333333333332E-3</v>
+      </c>
+      <c r="K138" s="51">
+        <v>10.183</v>
+      </c>
+      <c r="L138" s="52">
+        <v>2.41E-14</v>
+      </c>
+      <c r="M138" s="52">
+        <v>4.0599999999999999E-16</v>
+      </c>
+      <c r="Q138" s="16">
+        <v>31.7727264</v>
+      </c>
+      <c r="R138" s="23">
+        <v>1.0818483964618036E-11</v>
+      </c>
+      <c r="S138" s="23">
+        <v>4.5887318376204904E-14</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>10</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139">
+        <v>6</v>
+      </c>
+      <c r="D139">
+        <v>3</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="G139">
         <v>2100</v>
       </c>
-      <c r="H138" s="8">
-        <v>2.507936507936508E-2</v>
-      </c>
-      <c r="I138" s="10">
-        <v>40.977777777777781</v>
-      </c>
-      <c r="J138" s="16">
+      <c r="H139" s="49">
+        <v>2.41E-2</v>
+      </c>
+      <c r="I139" s="50">
+        <v>40.487000000000002</v>
+      </c>
+      <c r="J139" s="51">
         <v>2.7100000000000002E-3</v>
       </c>
-      <c r="K138" s="16">
-        <v>19.715993999999998</v>
-      </c>
-      <c r="L138" s="21">
-        <v>2.3600570397010183E-13</v>
-      </c>
-      <c r="M138" s="21">
+      <c r="K139" s="51">
+        <v>16.943999999999999</v>
+      </c>
+      <c r="L139" s="52">
+        <v>2.5900000000000001E-13</v>
+      </c>
+      <c r="M139" s="52">
         <v>3.954135446458232E-16</v>
       </c>
-      <c r="Q138" s="16">
+      <c r="Q139" s="16">
         <v>105.6478079</v>
       </c>
-      <c r="R138" s="23">
+      <c r="R139" s="23">
         <v>3.549609196044045E-9</v>
       </c>
-      <c r="S138" s="23">
+      <c r="S139" s="23">
         <v>2.5864833288222837E-12</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A139" s="12">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A140" s="12">
         <v>15</v>
       </c>
-      <c r="B139" s="12">
-        <v>2</v>
-      </c>
-      <c r="C139" s="12">
-        <v>2</v>
-      </c>
-      <c r="D139" s="12">
-        <v>5</v>
-      </c>
-      <c r="E139" s="12">
-        <v>0</v>
-      </c>
-      <c r="F139" s="12">
-        <v>5</v>
-      </c>
-      <c r="G139" s="12">
+      <c r="B140" s="12">
+        <v>2</v>
+      </c>
+      <c r="C140" s="12">
+        <v>2</v>
+      </c>
+      <c r="D140" s="12">
+        <v>5</v>
+      </c>
+      <c r="E140" s="12">
+        <v>0</v>
+      </c>
+      <c r="F140" s="12">
+        <v>5</v>
+      </c>
+      <c r="G140" s="12">
         <v>675</v>
       </c>
-      <c r="H139" s="13">
-        <v>6.9629629629629625E-2</v>
-      </c>
-      <c r="I139" s="14">
-        <v>35.016000000000005</v>
-      </c>
-      <c r="J139" s="17">
+      <c r="H140" s="13">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="I140" s="14">
+        <v>34.292000000000002</v>
+      </c>
+      <c r="J140" s="17">
         <v>6.7227999999999993E-4</v>
       </c>
-      <c r="K139" s="17">
-        <v>7.439250620000001</v>
-      </c>
-      <c r="L139" s="22">
+      <c r="K140" s="17">
+        <v>5.9416000000000002</v>
+      </c>
+      <c r="L140" s="22">
         <v>0.17199566509229403</v>
       </c>
-      <c r="M139" s="22">
+      <c r="M140" s="22">
         <v>8.7618527618346915E-16</v>
       </c>
-      <c r="N139" s="17"/>
-      <c r="O139" s="24"/>
-      <c r="P139" s="24"/>
-      <c r="Q139" s="17">
+      <c r="N140" s="17"/>
+      <c r="O140" s="24"/>
+      <c r="P140" s="24"/>
+      <c r="Q140" s="17">
         <v>4.5755377399999997</v>
       </c>
-      <c r="R139" s="24">
+      <c r="R140" s="24">
         <v>6.2632535913292558E-12</v>
       </c>
-      <c r="S139" s="24">
+      <c r="S140" s="24">
         <v>1.6035885772533078E-13</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A140">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A141">
         <v>20</v>
       </c>
-      <c r="B140">
-        <v>2</v>
-      </c>
-      <c r="C140">
-        <v>2</v>
-      </c>
-      <c r="D140">
-        <v>3</v>
-      </c>
-      <c r="E140">
-        <v>0</v>
-      </c>
-      <c r="F140">
-        <v>3</v>
-      </c>
-      <c r="G140">
+      <c r="B141">
+        <v>2</v>
+      </c>
+      <c r="C141">
+        <v>2</v>
+      </c>
+      <c r="D141">
+        <v>3</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="F141">
+        <v>3</v>
+      </c>
+      <c r="G141">
         <v>1200</v>
       </c>
-      <c r="H140" s="8">
-        <v>7.166666666666667E-2</v>
-      </c>
-      <c r="I140" s="10">
-        <v>34.649722222222231</v>
-      </c>
-      <c r="J140" s="16">
+      <c r="H141" s="49">
+        <v>8.1100000000000005E-2</v>
+      </c>
+      <c r="I141" s="50">
+        <v>35.186999999999998</v>
+      </c>
+      <c r="J141" s="51">
         <v>7.9946666666666673E-4</v>
       </c>
-      <c r="K140" s="16">
-        <v>18.792143266666667</v>
-      </c>
-      <c r="L140" s="21">
-        <v>7.9551902803752698E-11</v>
-      </c>
-      <c r="M140" s="21">
-        <v>3.6872558626559525E-15</v>
-      </c>
-      <c r="Q140" s="16">
+      <c r="K141" s="51">
+        <v>16.3</v>
+      </c>
+      <c r="L141" s="52">
+        <v>8.84E-11</v>
+      </c>
+      <c r="M141" s="52">
+        <v>3.5399999999999999E-15</v>
+      </c>
+      <c r="Q141" s="16">
         <v>18.132396066666669</v>
       </c>
-      <c r="R140" s="23">
+      <c r="R141" s="23">
         <v>1.1242075415885675E-12</v>
       </c>
-      <c r="S140" s="23">
+      <c r="S141" s="23">
         <v>3.4699449019803669E-14</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X140">
-    <sortCondition ref="A2:A140"/>
-    <sortCondition ref="B2:B140"/>
-    <sortCondition ref="C2:C140"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X141">
+    <sortCondition ref="A2:A141"/>
+    <sortCondition ref="B2:B141"/>
+    <sortCondition ref="C2:C141"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8217,25 +8263,25 @@
       <c r="B5">
         <v>12</v>
       </c>
-      <c r="C5" s="48">
+      <c r="C5" s="47">
         <v>1.456E-2</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="39">
         <v>2.6800000000000001E-3</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="48">
         <v>7.1800000000000003E-2</v>
       </c>
       <c r="F5">
         <v>32</v>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="47">
         <v>3.1260000000000003E-2</v>
       </c>
-      <c r="H5" s="40">
+      <c r="H5" s="39">
         <v>1.9066E-2</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="48">
         <v>0.15060000000000001</v>
       </c>
       <c r="J5">
@@ -8244,10 +8290,10 @@
       <c r="K5" s="17">
         <v>9.4890000000000002E-2</v>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="33">
         <v>0.42111999999999999</v>
       </c>
-      <c r="M5" s="33">
+      <c r="M5" s="32">
         <v>0.40943000000000002</v>
       </c>
       <c r="N5">
@@ -8256,13 +8302,13 @@
       <c r="O5" s="17">
         <v>0.64177055999999999</v>
       </c>
-      <c r="P5" s="33">
+      <c r="P5" s="32">
         <v>0.97364485999999995</v>
       </c>
       <c r="Q5">
         <v>448</v>
       </c>
-      <c r="R5" s="33">
+      <c r="R5" s="32">
         <v>20.133113666666667</v>
       </c>
       <c r="S5" s="17">
@@ -8271,7 +8317,7 @@
       <c r="T5">
         <v>1024</v>
       </c>
-      <c r="U5" s="33">
+      <c r="U5" s="32">
         <v>797.36940379999999</v>
       </c>
       <c r="V5" s="17">
@@ -8281,7 +8327,7 @@
         <v>2304</v>
       </c>
       <c r="X5" s="31"/>
-      <c r="Y5" s="35">
+      <c r="Y5" s="34">
         <v>23.085000000000001</v>
       </c>
       <c r="Z5">
@@ -8301,25 +8347,25 @@
       <c r="B6">
         <v>24</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="32">
         <v>3.3101779999999997E-2</v>
       </c>
       <c r="D6" s="17">
         <v>5.7861200000000005E-3</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="33">
         <v>0.12391429999999999</v>
       </c>
       <c r="F6">
         <v>80</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="32">
         <v>8.1120920000000013E-2</v>
       </c>
       <c r="H6" s="17">
         <v>7.2285719999999998E-2</v>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="33">
         <v>0.32396923999999994</v>
       </c>
       <c r="J6">
@@ -8328,16 +8374,16 @@
       <c r="K6" s="17">
         <v>0.49177758000000005</v>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="33">
         <v>3.5624355000000003</v>
       </c>
-      <c r="M6" s="33">
+      <c r="M6" s="32">
         <v>1.11676252</v>
       </c>
       <c r="N6">
         <v>672</v>
       </c>
-      <c r="O6" s="33">
+      <c r="O6" s="32">
         <v>15.3490509</v>
       </c>
       <c r="P6" s="17">
@@ -8346,14 +8392,14 @@
       <c r="Q6">
         <v>1792</v>
       </c>
-      <c r="R6" s="36"/>
+      <c r="R6" s="35"/>
       <c r="S6" s="17">
         <v>12.103082633333335</v>
       </c>
       <c r="T6">
         <v>4608</v>
       </c>
-      <c r="V6" s="35">
+      <c r="V6" s="34">
         <v>40.802999999999997</v>
       </c>
       <c r="W6">
@@ -8370,34 +8416,34 @@
       <c r="B7">
         <v>40</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="32">
         <v>4.1166700000000007E-2</v>
       </c>
       <c r="D7" s="17">
         <v>7.790179999999999E-3</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="33">
         <v>0.18882724000000001</v>
       </c>
       <c r="F7">
         <v>160</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="32">
         <v>0.19288916</v>
       </c>
       <c r="H7" s="17">
         <v>0.15644017999999998</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="33">
         <v>0.67267960000000004</v>
       </c>
       <c r="J7">
         <v>560</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="32">
         <v>2.8222610800000005</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="33">
         <v>29.830308399999996</v>
       </c>
       <c r="M7" s="17">
@@ -8406,7 +8452,7 @@
       <c r="N7">
         <v>1792</v>
       </c>
-      <c r="O7" s="33">
+      <c r="O7" s="32">
         <v>146.44020839999999</v>
       </c>
       <c r="P7" s="17">
@@ -8423,34 +8469,34 @@
       <c r="B8">
         <v>60</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="32">
         <v>6.3321619999999995E-2</v>
       </c>
       <c r="D8" s="17">
         <v>1.80378E-2</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="33">
         <v>0.29901776000000002</v>
       </c>
       <c r="F8">
         <v>280</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="32">
         <v>0.52549763999999999</v>
       </c>
       <c r="H8" s="17">
         <v>0.37111724000000001</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="33">
         <v>1.1616523999999999</v>
       </c>
       <c r="J8">
         <v>1120</v>
       </c>
-      <c r="K8" s="33">
+      <c r="K8" s="32">
         <v>21.385045633333334</v>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="33">
         <v>129.86155880000001</v>
       </c>
       <c r="M8" s="17">
@@ -8464,34 +8510,34 @@
       <c r="B9">
         <v>84</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="32">
         <v>8.2514799999999999E-2</v>
       </c>
       <c r="D9" s="17">
         <v>2.1122419999999999E-2</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="33">
         <v>0.48918363999999998</v>
       </c>
       <c r="F9">
         <v>448</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="32">
         <v>1.2825436400000001</v>
       </c>
       <c r="H9" s="17">
         <v>0.85323156</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="33">
         <v>1.9996489400000002</v>
       </c>
       <c r="J9">
         <v>2016</v>
       </c>
-      <c r="K9" s="33">
+      <c r="K9" s="32">
         <v>97.669234900000006</v>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="33">
         <v>510.56971420000002</v>
       </c>
       <c r="M9" s="17">
@@ -8505,34 +8551,34 @@
       <c r="B10">
         <v>112</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="32">
         <v>0.12037446</v>
       </c>
       <c r="D10" s="17">
         <v>2.4502400000000001E-2</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>0.60028532000000001</v>
       </c>
       <c r="F10">
         <v>672</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="33">
         <v>3.5853993399999999</v>
       </c>
       <c r="H10" s="17">
         <v>2.38377412</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10" s="32">
         <v>3.3273325599999999</v>
       </c>
       <c r="J10">
         <v>3360</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10" s="32">
         <v>410.93238270000001</v>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="33">
         <v>1781.36878</v>
       </c>
       <c r="M10" s="17">
@@ -8546,22 +8592,22 @@
       <c r="B11">
         <v>144</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="32">
         <v>0.17820569999999999</v>
       </c>
       <c r="D11" s="17">
         <v>3.2688840000000004E-2</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="33">
         <v>0.68624240000000003</v>
       </c>
       <c r="F11">
         <v>960</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="33">
         <v>8.6804971000000002</v>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="32">
         <v>5.6533195000000003</v>
       </c>
       <c r="I11" s="17">
@@ -8581,22 +8627,22 @@
       <c r="B12">
         <v>180</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="32">
         <v>0.27661429999999998</v>
       </c>
       <c r="D12" s="17">
         <v>4.4987140000000002E-2</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="33">
         <v>0.95401378000000003</v>
       </c>
       <c r="F12">
         <v>1320</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="33">
         <v>22.925975366666666</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="32">
         <v>13.759604299999999</v>
       </c>
       <c r="I12" s="17">
@@ -8610,22 +8656,22 @@
       <c r="B13">
         <v>220</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="32">
         <v>0.42966146</v>
       </c>
       <c r="D13" s="17">
         <v>6.1849279999999993E-2</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="33">
         <v>1.1096839199999999</v>
       </c>
       <c r="F13">
         <v>1760</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="33">
         <v>56.422378700000003</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="32">
         <v>31.474254066666663</v>
       </c>
       <c r="I13" s="17">
@@ -8642,22 +8688,22 @@
       <c r="B14">
         <v>264</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="32">
         <v>0.61052154000000003</v>
       </c>
       <c r="D14" s="17">
         <v>8.3866940000000015E-2</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="33">
         <v>1.4068060199999999</v>
       </c>
       <c r="F14">
         <v>2288</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="33">
         <v>142.17392190000001</v>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="32">
         <v>60.830471299999999</v>
       </c>
       <c r="I14" s="17">
@@ -8671,22 +8717,22 @@
       <c r="B15">
         <v>312</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="32">
         <v>0.88440069999999993</v>
       </c>
       <c r="D15" s="17">
         <v>0.11716675999999999</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="33">
         <v>1.6275462999999999</v>
       </c>
       <c r="F15">
         <v>2912</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="33">
         <v>265.75037309999999</v>
       </c>
-      <c r="H15" s="33">
+      <c r="H15" s="32">
         <v>120.2011317</v>
       </c>
       <c r="I15" s="17">
@@ -8700,21 +8746,21 @@
       <c r="B16">
         <v>364</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="32">
         <v>1.21474254</v>
       </c>
       <c r="D16" s="17">
         <v>0.14681959999999999</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="33">
         <v>2.1406280400000002</v>
       </c>
       <c r="F16">
         <v>3640</v>
       </c>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
@@ -8723,21 +8769,21 @@
       <c r="B17">
         <v>420</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="32">
         <v>1.7193622399999999</v>
       </c>
       <c r="D17" s="17">
         <v>0.19400054</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="33">
         <v>2.54902914</v>
       </c>
       <c r="F17">
         <v>4480</v>
       </c>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
@@ -8746,22 +8792,22 @@
       <c r="B18">
         <v>480</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="32">
         <v>2.5835721</v>
       </c>
       <c r="D18" s="17">
         <v>0.24957826</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="33">
         <v>3.0537190000000001</v>
       </c>
       <c r="F18">
         <v>5440</v>
       </c>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="32">
-        <v>53.073</v>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="39">
+        <v>43.233600000000003</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -8771,13 +8817,13 @@
       <c r="B19">
         <v>544</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="32">
         <v>3.6694164400000004</v>
       </c>
       <c r="D19" s="17">
         <v>0.35193524000000004</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="33">
         <v>4.1349755400000001</v>
       </c>
     </row>
@@ -8788,13 +8834,13 @@
       <c r="B20">
         <v>612</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="33">
         <v>5.2292617000000003</v>
       </c>
       <c r="D20" s="17">
         <v>0.44027638000000008</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="32">
         <v>4.73403872</v>
       </c>
     </row>
@@ -8805,13 +8851,13 @@
       <c r="B21">
         <v>684</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="33">
         <v>7.3286209600000003</v>
       </c>
       <c r="D21" s="17">
         <v>0.54613226000000004</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="32">
         <v>5.6608862999999996</v>
       </c>
     </row>
@@ -8822,13 +8868,13 @@
       <c r="B22">
         <v>760</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="33">
         <v>9.2023878799999999</v>
       </c>
       <c r="D22" s="17">
         <v>0.67160551999999996</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="32">
         <v>6.6097214600000003</v>
       </c>
     </row>
@@ -8839,13 +8885,13 @@
       <c r="B23">
         <v>840</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="33">
         <v>12.469067840000001</v>
       </c>
       <c r="D23" s="17">
         <v>0.83263458000000001</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="32">
         <v>7.5984335999999999</v>
       </c>
       <c r="F23">
@@ -8865,13 +8911,13 @@
       <c r="B25">
         <v>1300</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="33">
         <v>51.865085866666668</v>
       </c>
       <c r="D25" s="17">
         <v>2.3909596799999999</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="32">
         <v>15.829994300000001</v>
       </c>
     </row>
@@ -8882,13 +8928,13 @@
       <c r="B26">
         <v>1860</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="33">
         <v>178.48379843333336</v>
       </c>
       <c r="D26" s="17">
         <v>6.9553134599999993</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="32">
         <v>27.1588198</v>
       </c>
     </row>
@@ -8899,13 +8945,13 @@
       <c r="B27">
         <v>2520</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="33">
         <v>482.37181850000002</v>
       </c>
       <c r="D27" s="17">
         <v>17.947832966666667</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="32">
         <v>49.696633899999995</v>
       </c>
     </row>
@@ -8916,11 +8962,11 @@
       <c r="B28">
         <v>3280</v>
       </c>
-      <c r="C28" s="37"/>
+      <c r="C28" s="36"/>
       <c r="D28" s="17">
         <v>32.920549899999997</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="32">
         <v>75.911284199999997</v>
       </c>
     </row>
@@ -8931,11 +8977,11 @@
       <c r="B29">
         <v>4140</v>
       </c>
-      <c r="C29" s="37"/>
+      <c r="C29" s="36"/>
       <c r="D29" s="17">
         <v>58.148794799999997</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="32">
         <v>121.182087</v>
       </c>
     </row>
@@ -8946,11 +8992,11 @@
       <c r="B30">
         <v>5100</v>
       </c>
-      <c r="C30" s="37"/>
+      <c r="C30" s="36"/>
       <c r="D30" s="17">
         <v>105.3500128</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="32">
         <v>206.50301629999998</v>
       </c>
     </row>
@@ -8971,7 +9017,7 @@
       <c r="D32" s="17">
         <v>284.70219170000001</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="32">
         <v>380.51593280000003</v>
       </c>
     </row>
@@ -9062,37 +9108,37 @@
       <c r="B5">
         <v>27</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="39">
         <v>2.854508E-2</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="37">
         <v>9.1658920000000005E-2</v>
       </c>
       <c r="E5">
         <v>108</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="39">
         <v>0.13805464000000001</v>
       </c>
-      <c r="G5" s="39">
+      <c r="G5" s="38">
         <v>0.51993237999999997</v>
       </c>
       <c r="H5">
         <v>405</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="39">
         <v>1.4845759599999999</v>
       </c>
-      <c r="J5" s="39">
+      <c r="J5" s="38">
         <v>2.0923164999999999</v>
       </c>
       <c r="K5">
         <v>1458</v>
       </c>
-      <c r="L5" s="39">
+      <c r="L5" s="38">
         <v>122.30894290000001</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="39">
         <v>11.113312899999999</v>
       </c>
     </row>
@@ -9103,35 +9149,35 @@
       <c r="B6">
         <v>54</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="39">
         <v>5.1364100000000003E-2</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="38">
         <v>0.20890132</v>
       </c>
       <c r="E6">
         <v>270</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="39">
         <v>0.50736621999999998</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="38">
         <v>1.2148881799999998</v>
       </c>
       <c r="H6">
         <v>1215</v>
       </c>
-      <c r="I6" s="39">
+      <c r="I6" s="38">
         <v>22.499410633333337</v>
       </c>
-      <c r="J6" s="40">
+      <c r="J6" s="39">
         <v>7.1276070666666671</v>
       </c>
       <c r="K6">
         <v>5103</v>
       </c>
       <c r="L6" s="28"/>
-      <c r="M6" s="39">
+      <c r="M6" s="38">
         <v>48.186458100000003</v>
       </c>
     </row>
@@ -9142,26 +9188,26 @@
       <c r="B7">
         <v>90</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="39">
         <v>8.743244E-2</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="38">
         <v>0.33099373999999998</v>
       </c>
       <c r="E7">
         <v>540</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="39">
         <v>1.7538317999999999</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="38">
         <v>2.6355545600000001</v>
       </c>
       <c r="H7">
         <v>2835</v>
       </c>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
@@ -9170,19 +9216,19 @@
       <c r="B8">
         <v>135</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="39">
         <v>0.1536121</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="38">
         <v>0.58145332000000005</v>
       </c>
       <c r="E8">
         <v>945</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="38">
         <v>6.6834589399999995</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="39">
         <v>5.0415852799999996</v>
       </c>
       <c r="I8" s="28"/>
@@ -9195,19 +9241,19 @@
       <c r="B9">
         <v>189</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="39">
         <v>0.27204255999999999</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="38">
         <v>0.88395478000000005</v>
       </c>
       <c r="E9">
         <v>1512</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="38">
         <v>24.829009833333334</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="39">
         <v>8.8886184400000001</v>
       </c>
       <c r="I9" s="28"/>
@@ -9220,19 +9266,19 @@
       <c r="B10">
         <v>252</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="39">
         <v>0.49989713999999996</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="38">
         <v>1.1752707599999999</v>
       </c>
       <c r="E10">
         <v>2268</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="41">
         <v>96.311044699999997</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="39">
         <v>14.110998100000002</v>
       </c>
     </row>
@@ -9243,17 +9289,17 @@
       <c r="B11">
         <v>324</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="39">
         <v>0.86330987999999986</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="38">
         <v>1.5456309799999999</v>
       </c>
       <c r="E11">
         <v>3240</v>
       </c>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
@@ -9262,10 +9308,10 @@
       <c r="B12">
         <v>405</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="39">
         <v>1.3349343</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="38">
         <v>2.2644156999999998</v>
       </c>
     </row>
@@ -9276,10 +9322,10 @@
       <c r="B13">
         <v>495</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="39">
         <v>2.3797572799999998</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="38">
         <v>2.9446504199999999</v>
       </c>
     </row>
@@ -9290,10 +9336,10 @@
       <c r="B14">
         <v>594</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="38">
         <v>3.9744627600000002</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="39">
         <v>3.7090702800000002</v>
       </c>
     </row>
@@ -9304,10 +9350,10 @@
       <c r="B15">
         <v>702</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="38">
         <v>5.9765022200000004</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="39">
         <v>4.4542152000000002</v>
       </c>
     </row>
@@ -9318,10 +9364,10 @@
       <c r="B16">
         <v>819</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="38">
         <v>8.5986568400000003</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="39">
         <v>5.0332620600000002</v>
       </c>
     </row>
@@ -9332,10 +9378,10 @@
       <c r="B17">
         <v>945</v>
       </c>
-      <c r="C17" s="39">
+      <c r="C17" s="38">
         <v>13.158509120000002</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="39">
         <v>6.4888700200000002</v>
       </c>
     </row>
@@ -9346,10 +9392,10 @@
       <c r="B18">
         <v>1080</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="38">
         <v>20.056435433333334</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="39">
         <v>7.7876606600000002</v>
       </c>
     </row>
@@ -9360,8 +9406,8 @@
       <c r="B19">
         <v>1224</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="25">
@@ -9370,8 +9416,8 @@
       <c r="B20">
         <v>1377</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
@@ -9380,8 +9426,8 @@
       <c r="B21">
         <v>1539</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="25">
@@ -9390,8 +9436,8 @@
       <c r="B22">
         <v>1710</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="25">
@@ -9400,8 +9446,8 @@
       <c r="B23">
         <v>1890</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9488,10 +9534,10 @@
       <c r="B5">
         <v>48</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="39">
         <v>5.1319119999999996E-2</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="37">
         <v>0.20406301999999998</v>
       </c>
       <c r="E5">
@@ -9525,10 +9571,10 @@
       <c r="B6">
         <v>96</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="39">
         <v>0.1038462</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="38">
         <v>0.35155676000000002</v>
       </c>
       <c r="E6">
@@ -9557,10 +9603,10 @@
       <c r="B7">
         <v>160</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="39">
         <v>0.20346367999999998</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="38">
         <v>0.63653746</v>
       </c>
       <c r="E7">
@@ -9582,10 +9628,10 @@
       <c r="B8">
         <v>240</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="39">
         <v>0.41042536000000007</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="38">
         <v>1.0186321599999999</v>
       </c>
       <c r="E8">
@@ -9607,17 +9653,17 @@
       <c r="B9">
         <v>336</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="39">
         <v>0.86774325999999991</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="38">
         <v>1.5951258799999999</v>
       </c>
       <c r="E9">
         <v>3584</v>
       </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
       <c r="I9" s="28"/>
       <c r="J9" s="28"/>
     </row>
@@ -9628,10 +9674,10 @@
       <c r="B10">
         <v>448</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="39">
         <v>1.41559104</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="38">
         <v>2.1699046600000003</v>
       </c>
     </row>
@@ -9642,10 +9688,10 @@
       <c r="B11">
         <v>576</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="39">
         <v>2.6988541599999998</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="38">
         <v>3.0337073399999999</v>
       </c>
     </row>
@@ -9656,10 +9702,10 @@
       <c r="B12">
         <v>720</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="38">
         <v>5.3663346399999998</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>4.1214200400000003</v>
       </c>
     </row>
@@ -9670,10 +9716,10 @@
       <c r="B13">
         <v>880</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="38">
         <v>8.6941763399999985</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="39">
         <v>5.1804248600000005</v>
       </c>
     </row>
@@ -9684,10 +9730,10 @@
       <c r="B14">
         <v>1056</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="40">
         <v>15.056374466666668</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="42">
         <v>6.70655512</v>
       </c>
     </row>
@@ -9698,10 +9744,10 @@
       <c r="B15">
         <v>1248</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="40">
         <v>25.834941299999997</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="42">
         <v>8.1608353799999982</v>
       </c>
     </row>
@@ -9712,10 +9758,10 @@
       <c r="B16">
         <v>1456</v>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="40">
         <v>43.764413300000001</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="42">
         <v>10.554905466666666</v>
       </c>
     </row>
@@ -9726,10 +9772,10 @@
       <c r="B17">
         <v>1680</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="40">
         <v>68.735169999999997</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="42">
         <v>12.699480933333334</v>
       </c>
     </row>
@@ -9740,10 +9786,10 @@
       <c r="B18">
         <v>1920</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="40">
         <v>115.3274906</v>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="42">
         <v>15.405627433333331</v>
       </c>
     </row>
@@ -9754,8 +9800,8 @@
       <c r="B19">
         <v>2176</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="25">
@@ -9764,8 +9810,8 @@
       <c r="B20">
         <v>2448</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
@@ -9774,8 +9820,8 @@
       <c r="B21">
         <v>2736</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="25">
@@ -9784,8 +9830,8 @@
       <c r="B22">
         <v>3040</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="25">
@@ -9794,8 +9840,8 @@
       <c r="B23">
         <v>3360</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9899,7 +9945,7 @@
       <c r="H5">
         <v>3125</v>
       </c>
-      <c r="I5" s="44"/>
+      <c r="I5" s="43"/>
       <c r="J5" s="17">
         <v>36.600457300000002</v>
       </c>
@@ -9977,7 +10023,7 @@
       <c r="E8">
         <v>4375</v>
       </c>
-      <c r="F8" s="44"/>
+      <c r="F8" s="43"/>
       <c r="G8" s="17">
         <v>40.470895000000006</v>
       </c>
@@ -10242,8 +10288,8 @@
       <c r="E7">
         <v>4320</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
       <c r="I7" s="28"/>
       <c r="J7" s="28"/>
     </row>
@@ -10346,8 +10392,8 @@
       <c r="B14">
         <v>2376</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
@@ -10356,8 +10402,8 @@
       <c r="B15">
         <v>2808</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
@@ -10366,8 +10412,8 @@
       <c r="B16">
         <v>3276</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
@@ -10376,8 +10422,8 @@
       <c r="B17">
         <v>3780</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="25">
@@ -10386,8 +10432,8 @@
       <c r="B18">
         <v>4320</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10467,10 +10513,10 @@
       <c r="B6">
         <v>147</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="39">
         <v>0.24576959999999998</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="37">
         <v>0.84981883999999996</v>
       </c>
       <c r="E6">
@@ -10479,7 +10525,7 @@
       <c r="F6" s="16">
         <v>17.948652633333335</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="39">
         <v>14.6364207</v>
       </c>
       <c r="H6">
@@ -10497,17 +10543,17 @@
       <c r="B7">
         <v>294</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="39">
         <v>0.67656028000000001</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="38">
         <v>1.4183857999999998</v>
       </c>
       <c r="E7">
         <v>3430</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="40">
+      <c r="F7" s="43"/>
+      <c r="G7" s="39">
         <v>39.222806599999998</v>
       </c>
       <c r="I7" s="28"/>
@@ -10522,10 +10568,10 @@
       <c r="B8">
         <v>490</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="39">
         <v>1.6750416399999999</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="38">
         <v>2.55513536</v>
       </c>
       <c r="F8" s="28"/>
@@ -10540,10 +10586,10 @@
       <c r="B9">
         <v>735</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="41">
         <v>4.4124036600000007</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="39">
         <v>4.0244523599999997</v>
       </c>
       <c r="F9" s="28"/>
@@ -10558,10 +10604,10 @@
       <c r="B10">
         <v>1029</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="41">
         <v>11.320121700000001</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="39">
         <v>6.4889960000000002</v>
       </c>
       <c r="F10" s="28"/>
@@ -10576,10 +10622,10 @@
       <c r="B11">
         <v>1372</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="41">
         <v>26.342604733333335</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="39">
         <v>9.5750178399999992</v>
       </c>
     </row>
@@ -10590,10 +10636,10 @@
       <c r="B12">
         <v>1764</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="41">
         <v>61.218966299999998</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>13.549375533333333</v>
       </c>
     </row>
@@ -10604,10 +10650,10 @@
       <c r="B13">
         <v>2205</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="38">
         <v>148.0203487</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="39">
         <v>18.652216299999999</v>
       </c>
     </row>
@@ -10618,10 +10664,10 @@
       <c r="B14">
         <v>2695</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="38">
         <v>205.9769426</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="39">
         <v>23.026384266666668</v>
       </c>
     </row>
@@ -10728,10 +10774,10 @@
       <c r="B6">
         <v>300</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="39">
         <v>0.88176655999999998</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="37">
         <v>1.8261372000000002</v>
       </c>
       <c r="E6">
@@ -10751,10 +10797,10 @@
       <c r="B7">
         <v>600</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="39">
         <v>2.8232591999999999</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="38">
         <v>3.8893313200000001</v>
       </c>
       <c r="F7" s="29"/>
@@ -10771,10 +10817,10 @@
       <c r="B8">
         <v>1000</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="41">
         <v>9.4948389399999993</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="39">
         <v>7.3652457600000005</v>
       </c>
       <c r="F8" s="28"/>
@@ -10789,10 +10835,10 @@
       <c r="B9">
         <v>1500</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="41">
         <v>31.7727264</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="39">
         <v>12.103892199999999</v>
       </c>
       <c r="F9" s="28"/>
@@ -10807,10 +10853,10 @@
       <c r="B10">
         <v>2100</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="41">
         <v>105.6478079</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="39">
         <v>19.715993999999998</v>
       </c>
       <c r="F10" s="28"/>
@@ -10955,7 +11001,7 @@
       <c r="N5" s="17">
         <v>4.5755377399999997</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="45">
         <v>7.439250620000001</v>
       </c>
     </row>
@@ -10996,8 +11042,8 @@
       <c r="B7">
         <v>2400</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
       <c r="F7" s="29"/>
       <c r="G7" s="29"/>
       <c r="I7" s="29"/>

--- a/Comparison_polynomial_RMEP.xlsx
+++ b/Comparison_polynomial_RMEP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\MEP\RMEP_homotopy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1299C9C6-ECFB-49B2-B792-63CB552D0344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21136CF9-9A8A-4958-BC24-0F0EABAECE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21936" yWindow="636" windowWidth="22176" windowHeight="17028" xr2:uid="{7D2D116B-6D63-4BF8-9BBB-ECD7956D1860}"/>
+    <workbookView xWindow="19140" yWindow="624" windowWidth="25860" windowHeight="17028" xr2:uid="{7D2D116B-6D63-4BF8-9BBB-ECD7956D1860}"/>
   </bookViews>
   <sheets>
     <sheet name="All data" sheetId="1" r:id="rId1"/>
@@ -760,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E596BE4F-61BA-409F-8651-028AAF812182}">
-  <dimension ref="A1:V141"/>
+  <dimension ref="A1:V142"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
@@ -4903,49 +4903,37 @@
         <v>3</v>
       </c>
       <c r="B77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77">
-        <v>1458</v>
+        <v>2835</v>
       </c>
       <c r="H77" s="8">
-        <v>5.8984910836762688E-2</v>
+        <v>4.3099999999999999E-2</v>
       </c>
       <c r="I77" s="10">
-        <v>37.772519433013265</v>
-      </c>
-      <c r="J77" s="16">
-        <v>4.7204666666666667E-3</v>
+        <v>61.473999999999997</v>
       </c>
       <c r="K77" s="16">
-        <v>11.113312899999999</v>
+        <v>22.348199999999999</v>
       </c>
       <c r="L77" s="21">
-        <v>2.162323697391369E-14</v>
+        <v>3.4300000000000003E-14</v>
       </c>
       <c r="M77" s="21">
-        <v>3.3125786688416323E-16</v>
-      </c>
-      <c r="Q77" s="16">
-        <v>122.30894290000001</v>
-      </c>
-      <c r="R77" s="23">
-        <v>4.3606464890911999E-13</v>
-      </c>
-      <c r="S77" s="23">
-        <v>5.7434796010409036E-15</v>
+        <v>2.5000000000000002E-16</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
@@ -4956,87 +4944,87 @@
         <v>5</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
         <v>1</v>
       </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-      <c r="F78">
-        <v>0</v>
-      </c>
       <c r="G78">
-        <v>5103</v>
+        <v>1458</v>
       </c>
       <c r="H78" s="8">
-        <v>6.8979031941994909E-2</v>
+        <v>5.8984910836762688E-2</v>
       </c>
       <c r="I78" s="10">
-        <v>39.8432294728591</v>
+        <v>37.772519433013265</v>
       </c>
       <c r="J78" s="16">
-        <v>1.4519900000000001E-2</v>
+        <v>4.7204666666666667E-3</v>
       </c>
       <c r="K78" s="16">
-        <v>48.186458100000003</v>
+        <v>11.113312899999999</v>
       </c>
       <c r="L78" s="21">
-        <v>1.2265086244831076E-13</v>
+        <v>2.162323697391369E-14</v>
       </c>
       <c r="M78" s="21">
-        <v>3.0241030583310743E-16</v>
+        <v>3.3125786688416323E-16</v>
+      </c>
+      <c r="Q78" s="16">
+        <v>122.30894290000001</v>
+      </c>
+      <c r="R78" s="23">
+        <v>4.3606464890911999E-13</v>
+      </c>
+      <c r="S78" s="23">
+        <v>5.7434796010409036E-15</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E79">
         <v>0</v>
       </c>
       <c r="F79">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G79">
-        <v>48</v>
+        <v>5103</v>
       </c>
       <c r="H79" s="8">
-        <v>2.4999999999999998E-2</v>
+        <v>6.8979031941994909E-2</v>
       </c>
       <c r="I79" s="10">
-        <v>35.091666666666661</v>
+        <v>39.8432294728591</v>
       </c>
       <c r="J79" s="16">
-        <v>6.6166E-4</v>
+        <v>1.4519900000000001E-2</v>
       </c>
       <c r="K79" s="16">
-        <v>0.20406301999999998</v>
+        <v>48.186458100000003</v>
       </c>
       <c r="L79" s="21">
-        <v>5.1636162701444704E-15</v>
+        <v>1.2265086244831076E-13</v>
       </c>
       <c r="M79" s="21">
-        <v>2.4050541761169982E-16</v>
-      </c>
-      <c r="Q79" s="16">
-        <v>5.1319119999999996E-2</v>
-      </c>
-      <c r="R79" s="23">
-        <v>1.9039088267757576E-14</v>
-      </c>
-      <c r="S79" s="23">
-        <v>1.9803021753882212E-15</v>
+        <v>3.0241030583310743E-16</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
@@ -5047,7 +5035,7 @@
         <v>2</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>5</v>
@@ -5059,34 +5047,34 @@
         <v>5</v>
       </c>
       <c r="G80">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="H80" s="8">
         <v>2.4999999999999998E-2</v>
       </c>
       <c r="I80" s="10">
-        <v>35.543750000000003</v>
+        <v>35.091666666666661</v>
       </c>
       <c r="J80" s="16">
-        <v>8.9022000000000005E-4</v>
+        <v>6.6166E-4</v>
       </c>
       <c r="K80" s="16">
-        <v>0.35155676000000002</v>
+        <v>0.20406301999999998</v>
       </c>
       <c r="L80" s="21">
-        <v>6.6044339903193766E-15</v>
+        <v>5.1636162701444704E-15</v>
       </c>
       <c r="M80" s="21">
-        <v>2.0503553178939857E-16</v>
+        <v>2.4050541761169982E-16</v>
       </c>
       <c r="Q80" s="16">
-        <v>0.1038462</v>
+        <v>5.1319119999999996E-2</v>
       </c>
       <c r="R80" s="23">
-        <v>3.1544251439102089E-14</v>
+        <v>1.9039088267757576E-14</v>
       </c>
       <c r="S80" s="23">
-        <v>2.5974700552963143E-15</v>
+        <v>1.9803021753882212E-15</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.3">
@@ -5097,7 +5085,7 @@
         <v>2</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D81">
         <v>5</v>
@@ -5109,34 +5097,34 @@
         <v>5</v>
       </c>
       <c r="G81">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="H81" s="8">
-        <v>1.7499999999999998E-2</v>
+        <v>2.4999999999999998E-2</v>
       </c>
       <c r="I81" s="10">
-        <v>37.651250000000005</v>
+        <v>35.543750000000003</v>
       </c>
       <c r="J81" s="16">
-        <v>1.12224E-3</v>
+        <v>8.9022000000000005E-4</v>
       </c>
       <c r="K81" s="16">
-        <v>0.63653746</v>
+        <v>0.35155676000000002</v>
       </c>
       <c r="L81" s="21">
-        <v>8.3112832032632516E-15</v>
+        <v>6.6044339903193766E-15</v>
       </c>
       <c r="M81" s="21">
-        <v>1.9875401159569674E-16</v>
+        <v>2.0503553178939857E-16</v>
       </c>
       <c r="Q81" s="16">
-        <v>0.20346367999999998</v>
+        <v>0.1038462</v>
       </c>
       <c r="R81" s="23">
-        <v>9.778811515855743E-13</v>
+        <v>3.1544251439102089E-14</v>
       </c>
       <c r="S81" s="23">
-        <v>2.2822300132756392E-14</v>
+        <v>2.5974700552963143E-15</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.3">
@@ -5147,7 +5135,7 @@
         <v>2</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D82">
         <v>5</v>
@@ -5159,34 +5147,34 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="H82" s="8">
-        <v>2.5000000000000001E-2</v>
+        <v>1.7499999999999998E-2</v>
       </c>
       <c r="I82" s="10">
-        <v>39.858333333333334</v>
+        <v>37.651250000000005</v>
       </c>
       <c r="J82" s="16">
-        <v>1.5599599999999998E-3</v>
+        <v>1.12224E-3</v>
       </c>
       <c r="K82" s="16">
-        <v>1.0186321599999999</v>
+        <v>0.63653746</v>
       </c>
       <c r="L82" s="21">
-        <v>8.0165326312548139E-15</v>
+        <v>8.3112832032632516E-15</v>
       </c>
       <c r="M82" s="21">
-        <v>1.9164943387905609E-16</v>
+        <v>1.9875401159569674E-16</v>
       </c>
       <c r="Q82" s="16">
-        <v>0.41042536000000007</v>
+        <v>0.20346367999999998</v>
       </c>
       <c r="R82" s="23">
-        <v>1.8151501146785406E-13</v>
+        <v>9.778811515855743E-13</v>
       </c>
       <c r="S82" s="23">
-        <v>3.5174345616668639E-15</v>
+        <v>2.2822300132756392E-14</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.3">
@@ -5197,7 +5185,7 @@
         <v>2</v>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -5209,34 +5197,34 @@
         <v>5</v>
       </c>
       <c r="G83">
-        <v>336</v>
+        <v>240</v>
       </c>
       <c r="H83" s="8">
-        <v>1.6666666666666666E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I83" s="10">
-        <v>41.69583333333334</v>
+        <v>39.858333333333334</v>
       </c>
       <c r="J83" s="16">
-        <v>1.9404399999999999E-3</v>
+        <v>1.5599599999999998E-3</v>
       </c>
       <c r="K83" s="16">
-        <v>1.5951258799999999</v>
+        <v>1.0186321599999999</v>
       </c>
       <c r="L83" s="21">
-        <v>8.2164339524242991E-15</v>
+        <v>8.0165326312548139E-15</v>
       </c>
       <c r="M83" s="21">
-        <v>1.8189827594694064E-16</v>
+        <v>1.9164943387905609E-16</v>
       </c>
       <c r="Q83" s="16">
-        <v>0.86774325999999991</v>
+        <v>0.41042536000000007</v>
       </c>
       <c r="R83" s="23">
-        <v>1.9036289092995512E-12</v>
+        <v>1.8151501146785406E-13</v>
       </c>
       <c r="S83" s="23">
-        <v>2.451769638850862E-14</v>
+        <v>3.5174345616668639E-15</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.3">
@@ -5247,7 +5235,7 @@
         <v>2</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D84">
         <v>5</v>
@@ -5259,34 +5247,34 @@
         <v>5</v>
       </c>
       <c r="G84">
-        <v>448</v>
+        <v>336</v>
       </c>
       <c r="H84" s="8">
-        <v>1.9642857142857146E-2</v>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="I84" s="10">
-        <v>42.666964285714279</v>
+        <v>41.69583333333334</v>
       </c>
       <c r="J84" s="16">
-        <v>2.43888E-3</v>
+        <v>1.9404399999999999E-3</v>
       </c>
       <c r="K84" s="16">
-        <v>2.1699046600000003</v>
+        <v>1.5951258799999999</v>
       </c>
       <c r="L84" s="21">
-        <v>8.0746483171160317E-15</v>
+        <v>8.2164339524242991E-15</v>
       </c>
       <c r="M84" s="21">
-        <v>1.8361153524691382E-16</v>
+        <v>1.8189827594694064E-16</v>
       </c>
       <c r="Q84" s="16">
-        <v>1.41559104</v>
+        <v>0.86774325999999991</v>
       </c>
       <c r="R84" s="23">
-        <v>7.8049497441862349E-11</v>
+        <v>1.9036289092995512E-12</v>
       </c>
       <c r="S84" s="23">
-        <v>1.1124407655959028E-13</v>
+        <v>2.451769638850862E-14</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.3">
@@ -5297,7 +5285,7 @@
         <v>2</v>
       </c>
       <c r="C85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -5309,34 +5297,34 @@
         <v>5</v>
       </c>
       <c r="G85">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="H85" s="8">
-        <v>1.6319444444444445E-2</v>
+        <v>1.9642857142857146E-2</v>
       </c>
       <c r="I85" s="10">
-        <v>43.930902777777774</v>
+        <v>42.666964285714279</v>
       </c>
       <c r="J85" s="16">
-        <v>2.9625200000000002E-3</v>
+        <v>2.43888E-3</v>
       </c>
       <c r="K85" s="16">
-        <v>3.0337073399999999</v>
+        <v>2.1699046600000003</v>
       </c>
       <c r="L85" s="21">
-        <v>8.7563421659102526E-15</v>
+        <v>8.0746483171160317E-15</v>
       </c>
       <c r="M85" s="21">
-        <v>1.8086193569675066E-16</v>
+        <v>1.8361153524691382E-16</v>
       </c>
       <c r="Q85" s="16">
-        <v>2.6988541599999998</v>
+        <v>1.41559104</v>
       </c>
       <c r="R85" s="23">
-        <v>3.1965184679858536E-10</v>
+        <v>7.8049497441862349E-11</v>
       </c>
       <c r="S85" s="23">
-        <v>1.8248833852568277E-13</v>
+        <v>1.1124407655959028E-13</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.3">
@@ -5347,7 +5335,7 @@
         <v>2</v>
       </c>
       <c r="C86">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D86">
         <v>5</v>
@@ -5359,34 +5347,34 @@
         <v>5</v>
       </c>
       <c r="G86">
-        <v>720</v>
+        <v>576</v>
       </c>
       <c r="H86" s="8">
-        <v>1.7499999999999998E-2</v>
+        <v>1.6319444444444445E-2</v>
       </c>
       <c r="I86" s="10">
-        <v>45.905277777777783</v>
+        <v>43.930902777777774</v>
       </c>
       <c r="J86" s="16">
-        <v>3.6048000000000005E-3</v>
+        <v>2.9625200000000002E-3</v>
       </c>
       <c r="K86" s="16">
-        <v>4.1214200400000003</v>
+        <v>3.0337073399999999</v>
       </c>
       <c r="L86" s="21">
-        <v>8.1221604086442086E-15</v>
+        <v>8.7563421659102526E-15</v>
       </c>
       <c r="M86" s="21">
-        <v>1.7674696975267334E-16</v>
+        <v>1.8086193569675066E-16</v>
       </c>
       <c r="Q86" s="16">
-        <v>5.3663346399999998</v>
+        <v>2.6988541599999998</v>
       </c>
       <c r="R86" s="23">
-        <v>8.9366837878838275E-11</v>
+        <v>3.1965184679858536E-10</v>
       </c>
       <c r="S86" s="23">
-        <v>5.983322273343556E-13</v>
+        <v>1.8248833852568277E-13</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.3">
@@ -5397,7 +5385,7 @@
         <v>2</v>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D87">
         <v>5</v>
@@ -5409,34 +5397,34 @@
         <v>5</v>
       </c>
       <c r="G87">
-        <v>880</v>
+        <v>720</v>
       </c>
       <c r="H87" s="8">
-        <v>1.0909090909090908E-2</v>
+        <v>1.7499999999999998E-2</v>
       </c>
       <c r="I87" s="10">
-        <v>46.384545454545453</v>
+        <v>45.905277777777783</v>
       </c>
       <c r="J87" s="16">
-        <v>4.5217199999999999E-3</v>
+        <v>3.6048000000000005E-3</v>
       </c>
       <c r="K87" s="16">
-        <v>5.1804248600000005</v>
+        <v>4.1214200400000003</v>
       </c>
       <c r="L87" s="21">
-        <v>4.0563133109035229E-13</v>
+        <v>8.1221604086442086E-15</v>
       </c>
       <c r="M87" s="21">
-        <v>1.7946917554982332E-16</v>
+        <v>1.7674696975267334E-16</v>
       </c>
       <c r="Q87" s="16">
-        <v>8.6941763399999985</v>
+        <v>5.3663346399999998</v>
       </c>
       <c r="R87" s="23">
-        <v>3.4883819294068199E-10</v>
+        <v>8.9366837878838275E-11</v>
       </c>
       <c r="S87" s="23">
-        <v>1.266692535217473E-12</v>
+        <v>5.983322273343556E-13</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.3">
@@ -5447,7 +5435,7 @@
         <v>2</v>
       </c>
       <c r="C88">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D88">
         <v>5</v>
@@ -5456,37 +5444,37 @@
         <v>0</v>
       </c>
       <c r="F88">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G88">
-        <v>1056</v>
+        <v>880</v>
       </c>
       <c r="H88" s="8">
-        <v>1.3636363636363637E-2</v>
+        <v>1.0909090909090908E-2</v>
       </c>
       <c r="I88" s="10">
-        <v>47.596780303030307</v>
+        <v>46.384545454545453</v>
       </c>
       <c r="J88" s="16">
-        <v>5.1335600000000006E-3</v>
+        <v>4.5217199999999999E-3</v>
       </c>
       <c r="K88" s="16">
-        <v>6.70655512</v>
+        <v>5.1804248600000005</v>
       </c>
       <c r="L88" s="21">
-        <v>8.856099390063399E-15</v>
+        <v>4.0563133109035229E-13</v>
       </c>
       <c r="M88" s="21">
-        <v>1.8085618481595117E-16</v>
+        <v>1.7946917554982332E-16</v>
       </c>
       <c r="Q88" s="16">
-        <v>15.056374466666668</v>
+        <v>8.6941763399999985</v>
       </c>
       <c r="R88" s="23">
-        <v>2.4295018337047839E-8</v>
+        <v>3.4883819294068199E-10</v>
       </c>
       <c r="S88" s="23">
-        <v>2.308890906404235E-12</v>
+        <v>1.266692535217473E-12</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.3">
@@ -5497,7 +5485,7 @@
         <v>2</v>
       </c>
       <c r="C89">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D89">
         <v>5</v>
@@ -5509,34 +5497,34 @@
         <v>3</v>
       </c>
       <c r="G89">
-        <v>1248</v>
+        <v>1056</v>
       </c>
       <c r="H89" s="8">
-        <v>9.935897435897437E-3</v>
+        <v>1.3636363636363637E-2</v>
       </c>
       <c r="I89" s="10">
-        <v>48.495993589743591</v>
+        <v>47.596780303030307</v>
       </c>
       <c r="J89" s="16">
-        <v>6.1504000000000003E-3</v>
+        <v>5.1335600000000006E-3</v>
       </c>
       <c r="K89" s="16">
-        <v>8.1608353799999982</v>
+        <v>6.70655512</v>
       </c>
       <c r="L89" s="21">
-        <v>4.5313439140602873E-14</v>
+        <v>8.856099390063399E-15</v>
       </c>
       <c r="M89" s="21">
-        <v>1.7779168818308106E-16</v>
+        <v>1.8085618481595117E-16</v>
       </c>
       <c r="Q89" s="16">
-        <v>25.834941299999997</v>
+        <v>15.056374466666668</v>
       </c>
       <c r="R89" s="23">
-        <v>1.1219879282896385E-7</v>
+        <v>2.4295018337047839E-8</v>
       </c>
       <c r="S89" s="23">
-        <v>6.0061331322282475E-11</v>
+        <v>2.308890906404235E-12</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.3">
@@ -5547,46 +5535,46 @@
         <v>2</v>
       </c>
       <c r="C90">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G90">
-        <v>1456</v>
+        <v>1248</v>
       </c>
       <c r="H90" s="8">
-        <v>1.510989010989011E-2</v>
+        <v>9.935897435897437E-3</v>
       </c>
       <c r="I90" s="10">
-        <v>50.130494505494504</v>
+        <v>48.495993589743591</v>
       </c>
       <c r="J90" s="16">
-        <v>7.1642999999999993E-3</v>
+        <v>6.1504000000000003E-3</v>
       </c>
       <c r="K90" s="16">
-        <v>10.554905466666666</v>
+        <v>8.1608353799999982</v>
       </c>
       <c r="L90" s="21">
-        <v>7.1176206096708818E-13</v>
+        <v>4.5313439140602873E-14</v>
       </c>
       <c r="M90" s="21">
-        <v>1.7861793287256898E-16</v>
+        <v>1.7779168818308106E-16</v>
       </c>
       <c r="Q90" s="16">
-        <v>43.764413300000001</v>
+        <v>25.834941299999997</v>
       </c>
       <c r="R90" s="23">
-        <v>4.2691807837727752E-8</v>
+        <v>1.1219879282896385E-7</v>
       </c>
       <c r="S90" s="23">
-        <v>6.2430990554405218E-11</v>
+        <v>6.0061331322282475E-11</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.3">
@@ -5597,7 +5585,7 @@
         <v>2</v>
       </c>
       <c r="C91">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D91">
         <v>3</v>
@@ -5609,34 +5597,34 @@
         <v>1</v>
       </c>
       <c r="G91">
-        <v>1680</v>
+        <v>1456</v>
       </c>
       <c r="H91" s="8">
-        <v>1.1309523809523809E-2</v>
+        <v>1.510989010989011E-2</v>
       </c>
       <c r="I91" s="10">
-        <v>50.704563492063492</v>
+        <v>50.130494505494504</v>
       </c>
       <c r="J91" s="16">
-        <v>8.1736666666666676E-3</v>
+        <v>7.1642999999999993E-3</v>
       </c>
       <c r="K91" s="16">
-        <v>12.699480933333334</v>
+        <v>10.554905466666666</v>
       </c>
       <c r="L91" s="21">
-        <v>8.8981459305272474E-15</v>
+        <v>7.1176206096708818E-13</v>
       </c>
       <c r="M91" s="21">
-        <v>1.7513656631602058E-16</v>
+        <v>1.7861793287256898E-16</v>
       </c>
       <c r="Q91" s="16">
-        <v>68.735169999999997</v>
+        <v>43.764413300000001</v>
       </c>
       <c r="R91" s="23">
-        <v>2.9854311789293022E-7</v>
+        <v>4.2691807837727752E-8</v>
       </c>
       <c r="S91" s="23">
-        <v>2.3696610952665727E-10</v>
+        <v>6.2430990554405218E-11</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.3">
@@ -5647,7 +5635,7 @@
         <v>2</v>
       </c>
       <c r="C92">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D92">
         <v>3</v>
@@ -5659,34 +5647,34 @@
         <v>1</v>
       </c>
       <c r="G92">
-        <v>1920</v>
+        <v>1680</v>
       </c>
       <c r="H92" s="8">
-        <v>1.2847222222222223E-2</v>
+        <v>1.1309523809523809E-2</v>
       </c>
       <c r="I92" s="10">
-        <v>51.958506944444444</v>
+        <v>50.704563492063492</v>
       </c>
       <c r="J92" s="16">
-        <v>9.1122333333333323E-3</v>
+        <v>8.1736666666666676E-3</v>
       </c>
       <c r="K92" s="16">
-        <v>15.405627433333331</v>
+        <v>12.699480933333334</v>
       </c>
       <c r="L92" s="21">
-        <v>8.5753805662679717E-15</v>
+        <v>8.8981459305272474E-15</v>
       </c>
       <c r="M92" s="21">
-        <v>1.7745128677302042E-16</v>
+        <v>1.7513656631602058E-16</v>
       </c>
       <c r="Q92" s="16">
-        <v>115.3274906</v>
+        <v>68.735169999999997</v>
       </c>
       <c r="R92" s="23">
-        <v>9.7650735782652114E-8</v>
+        <v>2.9854311789293022E-7</v>
       </c>
       <c r="S92" s="23">
-        <v>1.468131376872587E-10</v>
+        <v>2.3696610952665727E-10</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.3">
@@ -5694,49 +5682,49 @@
         <v>4</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E93">
         <v>0</v>
       </c>
       <c r="F93">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G93">
-        <v>256</v>
+        <v>1920</v>
       </c>
       <c r="H93" s="8">
-        <v>3.7499999999999999E-2</v>
+        <v>1.2847222222222223E-2</v>
       </c>
       <c r="I93" s="10">
-        <v>34.6796875</v>
+        <v>51.958506944444444</v>
       </c>
       <c r="J93" s="16">
-        <v>1.0819E-3</v>
+        <v>9.1122333333333323E-3</v>
       </c>
       <c r="K93" s="16">
-        <v>1.2695744000000002</v>
+        <v>15.405627433333331</v>
       </c>
       <c r="L93" s="21">
-        <v>2.0132970511526198E-14</v>
+        <v>8.5753805662679717E-15</v>
       </c>
       <c r="M93" s="21">
-        <v>3.1160955247749329E-16</v>
+        <v>1.7745128677302042E-16</v>
       </c>
       <c r="Q93" s="16">
-        <v>0.54818089999999997</v>
+        <v>115.3274906</v>
       </c>
       <c r="R93" s="23">
-        <v>4.6418020215540686E-13</v>
+        <v>9.7650735782652114E-8</v>
       </c>
       <c r="S93" s="23">
-        <v>4.7421697260468803E-15</v>
+        <v>1.468131376872587E-10</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.3">
@@ -5747,7 +5735,7 @@
         <v>3</v>
       </c>
       <c r="C94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94">
         <v>5</v>
@@ -5759,34 +5747,34 @@
         <v>5</v>
       </c>
       <c r="G94">
-        <v>640</v>
+        <v>256</v>
       </c>
       <c r="H94" s="8">
-        <v>4.4687500000000005E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="I94" s="10">
-        <v>37.266875000000006</v>
+        <v>34.6796875</v>
       </c>
       <c r="J94" s="16">
-        <v>1.9033400000000003E-3</v>
+        <v>1.0819E-3</v>
       </c>
       <c r="K94" s="16">
-        <v>3.4576043599999999</v>
+        <v>1.2695744000000002</v>
       </c>
       <c r="L94" s="21">
-        <v>1.7151996279412218E-14</v>
+        <v>2.0132970511526198E-14</v>
       </c>
       <c r="M94" s="21">
-        <v>2.7287804132474252E-16</v>
+        <v>3.1160955247749329E-16</v>
       </c>
       <c r="Q94" s="16">
-        <v>2.5991152799999995</v>
+        <v>0.54818089999999997</v>
       </c>
       <c r="R94" s="23">
-        <v>5.8968561566010554E-12</v>
+        <v>4.6418020215540686E-13</v>
       </c>
       <c r="S94" s="23">
-        <v>5.5666729068412767E-15</v>
+        <v>4.7421697260468803E-15</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.3">
@@ -5797,7 +5785,7 @@
         <v>3</v>
       </c>
       <c r="C95">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D95">
         <v>5</v>
@@ -5806,37 +5794,37 @@
         <v>0</v>
       </c>
       <c r="F95">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G95">
-        <v>1280</v>
+        <v>640</v>
       </c>
       <c r="H95" s="8">
-        <v>4.8437500000000001E-2</v>
+        <v>4.4687500000000005E-2</v>
       </c>
       <c r="I95" s="10">
-        <v>39.59796875</v>
+        <v>37.266875000000006</v>
       </c>
       <c r="J95" s="16">
-        <v>3.72822E-3</v>
+        <v>1.9033400000000003E-3</v>
       </c>
       <c r="K95" s="16">
-        <v>7.8842147200000001</v>
+        <v>3.4576043599999999</v>
       </c>
       <c r="L95" s="21">
-        <v>2.9964443174956343E-14</v>
+        <v>1.7151996279412218E-14</v>
       </c>
       <c r="M95" s="21">
-        <v>2.5838472390410206E-16</v>
+        <v>2.7287804132474252E-16</v>
       </c>
       <c r="Q95" s="16">
-        <v>13.694324433333334</v>
+        <v>2.5991152799999995</v>
       </c>
       <c r="R95" s="23">
-        <v>5.6072664396495966E-12</v>
+        <v>5.8968561566010554E-12</v>
       </c>
       <c r="S95" s="23">
-        <v>1.0970575168905956E-14</v>
+        <v>5.5666729068412767E-15</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.3">
@@ -5847,46 +5835,46 @@
         <v>3</v>
       </c>
       <c r="C96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D96">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E96">
         <v>0</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G96">
-        <v>2240</v>
+        <v>1280</v>
       </c>
       <c r="H96" s="8">
-        <v>3.4375000000000003E-2</v>
+        <v>4.8437500000000001E-2</v>
       </c>
       <c r="I96" s="10">
-        <v>39.656845238095237</v>
+        <v>39.59796875</v>
       </c>
       <c r="J96" s="16">
-        <v>6.4512333333333338E-3</v>
+        <v>3.72822E-3</v>
       </c>
       <c r="K96" s="16">
-        <v>14.612070233333334</v>
+        <v>7.8842147200000001</v>
       </c>
       <c r="L96" s="21">
-        <v>1.0285622689536414E-12</v>
+        <v>2.9964443174956343E-14</v>
       </c>
       <c r="M96" s="21">
-        <v>2.4789962864686991E-16</v>
+        <v>2.5838472390410206E-16</v>
       </c>
       <c r="Q96" s="16">
-        <v>78.473416999999998</v>
+        <v>13.694324433333334</v>
       </c>
       <c r="R96" s="23">
-        <v>1.8499076792100177E-11</v>
+        <v>5.6072664396495966E-12</v>
       </c>
       <c r="S96" s="23">
-        <v>3.3888450136734267E-14</v>
+        <v>1.0970575168905956E-14</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
@@ -5894,10 +5882,10 @@
         <v>4</v>
       </c>
       <c r="B97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -5906,37 +5894,37 @@
         <v>0</v>
       </c>
       <c r="F97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G97">
-        <v>1280</v>
+        <v>2240</v>
       </c>
       <c r="H97" s="8">
-        <v>7.239583333333334E-2</v>
+        <v>3.4375000000000003E-2</v>
       </c>
       <c r="I97" s="10">
-        <v>37.006510416666664</v>
+        <v>39.656845238095237</v>
       </c>
       <c r="J97" s="16">
-        <v>2.7899666666666664E-3</v>
+        <v>6.4512333333333338E-3</v>
       </c>
       <c r="K97" s="16">
-        <v>10.7165324</v>
+        <v>14.612070233333334</v>
       </c>
       <c r="L97" s="21">
-        <v>4.4504646015332152E-14</v>
+        <v>1.0285622689536414E-12</v>
       </c>
       <c r="M97" s="21">
-        <v>3.8130984615729509E-16</v>
+        <v>2.4789962864686991E-16</v>
       </c>
       <c r="Q97" s="16">
-        <v>26.523647033333333</v>
+        <v>78.473416999999998</v>
       </c>
       <c r="R97" s="23">
-        <v>4.1193002835668419E-11</v>
+        <v>1.8499076792100177E-11</v>
       </c>
       <c r="S97" s="23">
-        <v>8.1716021343870607E-15</v>
+        <v>3.3888450136734267E-14</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.3">
@@ -5947,87 +5935,87 @@
         <v>4</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E98">
         <v>0</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G98">
-        <v>3840</v>
+        <v>1280</v>
       </c>
       <c r="H98" s="8">
-        <v>6.458333333333334E-2</v>
+        <v>7.239583333333334E-2</v>
       </c>
       <c r="I98" s="10">
-        <v>38.025260416666669</v>
+        <v>37.006510416666664</v>
       </c>
       <c r="J98" s="16">
-        <v>7.5215000000000004E-3</v>
+        <v>2.7899666666666664E-3</v>
       </c>
       <c r="K98" s="16">
-        <v>33.928097700000002</v>
+        <v>10.7165324</v>
       </c>
       <c r="L98" s="21">
-        <v>2.8704818616543717E-14</v>
+        <v>4.4504646015332152E-14</v>
       </c>
       <c r="M98" s="21">
-        <v>3.4110084723815503E-16</v>
+        <v>3.8130984615729509E-16</v>
+      </c>
+      <c r="Q98" s="16">
+        <v>26.523647033333333</v>
+      </c>
+      <c r="R98" s="23">
+        <v>4.1193002835668419E-11</v>
+      </c>
+      <c r="S98" s="23">
+        <v>8.1716021343870607E-15</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E99">
         <v>0</v>
       </c>
       <c r="F99">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>75</v>
+        <v>3840</v>
       </c>
       <c r="H99" s="8">
-        <v>3.2000000000000001E-2</v>
+        <v>6.458333333333334E-2</v>
       </c>
       <c r="I99" s="10">
-        <v>34.058666666666667</v>
+        <v>38.025260416666669</v>
       </c>
       <c r="J99" s="16">
-        <v>6.623E-4</v>
+        <v>7.5215000000000004E-3</v>
       </c>
       <c r="K99" s="16">
-        <v>0.31772778000000002</v>
+        <v>33.928097700000002</v>
       </c>
       <c r="L99" s="21">
-        <v>8.1802588652744995E-15</v>
+        <v>2.8704818616543717E-14</v>
       </c>
       <c r="M99" s="21">
-        <v>2.7054990438010407E-16</v>
-      </c>
-      <c r="Q99" s="16">
-        <v>9.5071459999999997E-2</v>
-      </c>
-      <c r="R99" s="23">
-        <v>2.1230176129388547E-13</v>
-      </c>
-      <c r="S99" s="23">
-        <v>2.6554082342794527E-15</v>
+        <v>3.4110084723815503E-16</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.3">
@@ -6038,7 +6026,7 @@
         <v>2</v>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D100">
         <v>5</v>
@@ -6050,34 +6038,34 @@
         <v>5</v>
       </c>
       <c r="G100">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="H100" s="8">
-        <v>3.7333333333333329E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="I100" s="10">
-        <v>36.805333333333337</v>
+        <v>34.058666666666667</v>
       </c>
       <c r="J100" s="16">
-        <v>8.6505999999999996E-4</v>
+        <v>6.623E-4</v>
       </c>
       <c r="K100" s="16">
-        <v>0.68472791999999993</v>
+        <v>0.31772778000000002</v>
       </c>
       <c r="L100" s="21">
-        <v>7.9992386291296098E-14</v>
+        <v>8.1802588652744995E-15</v>
       </c>
       <c r="M100" s="21">
-        <v>2.3437174106603008E-16</v>
+        <v>2.7054990438010407E-16</v>
       </c>
       <c r="Q100" s="16">
-        <v>0.20571149999999999</v>
+        <v>9.5071459999999997E-2</v>
       </c>
       <c r="R100" s="23">
-        <v>3.9276827367189106E-13</v>
+        <v>2.1230176129388547E-13</v>
       </c>
       <c r="S100" s="23">
-        <v>3.887301769157956E-15</v>
+        <v>2.6554082342794527E-15</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.3">
@@ -6088,7 +6076,7 @@
         <v>2</v>
       </c>
       <c r="C101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D101">
         <v>5</v>
@@ -6100,34 +6088,34 @@
         <v>5</v>
       </c>
       <c r="G101">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H101" s="8">
-        <v>2.7199999999999998E-2</v>
+        <v>3.7333333333333329E-2</v>
       </c>
       <c r="I101" s="10">
-        <v>37.944000000000003</v>
+        <v>36.805333333333337</v>
       </c>
       <c r="J101" s="16">
-        <v>1.1263600000000001E-3</v>
+        <v>8.6505999999999996E-4</v>
       </c>
       <c r="K101" s="16">
-        <v>1.1483679399999998</v>
+        <v>0.68472791999999993</v>
       </c>
       <c r="L101" s="21">
-        <v>1.4703385801104632E-14</v>
+        <v>7.9992386291296098E-14</v>
       </c>
       <c r="M101" s="21">
-        <v>2.249163067383749E-16</v>
+        <v>2.3437174106603008E-16</v>
       </c>
       <c r="Q101" s="16">
-        <v>0.45794532000000004</v>
+        <v>0.20571149999999999</v>
       </c>
       <c r="R101" s="23">
-        <v>7.9015136443126549E-13</v>
+        <v>3.9276827367189106E-13</v>
       </c>
       <c r="S101" s="23">
-        <v>1.0980834697690558E-14</v>
+        <v>3.887301769157956E-15</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.3">
@@ -6138,7 +6126,7 @@
         <v>2</v>
       </c>
       <c r="C102">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -6150,34 +6138,34 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="H102" s="8">
-        <v>2.4E-2</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="I102" s="10">
-        <v>39.789333333333332</v>
+        <v>37.944000000000003</v>
       </c>
       <c r="J102" s="16">
-        <v>1.5102200000000001E-3</v>
+        <v>1.1263600000000001E-3</v>
       </c>
       <c r="K102" s="16">
-        <v>1.8615628799999999</v>
+        <v>1.1483679399999998</v>
       </c>
       <c r="L102" s="21">
-        <v>1.5468578750210955E-14</v>
+        <v>1.4703385801104632E-14</v>
       </c>
       <c r="M102" s="21">
-        <v>2.2084568777386575E-16</v>
+        <v>2.249163067383749E-16</v>
       </c>
       <c r="Q102" s="16">
-        <v>0.94974728000000008</v>
+        <v>0.45794532000000004</v>
       </c>
       <c r="R102" s="23">
-        <v>2.9094147727193586E-12</v>
+        <v>7.9015136443126549E-13</v>
       </c>
       <c r="S102" s="23">
-        <v>7.9947913515779821E-14</v>
+        <v>1.0980834697690558E-14</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.3">
@@ -6188,7 +6176,7 @@
         <v>2</v>
       </c>
       <c r="C103">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D103">
         <v>5</v>
@@ -6200,34 +6188,34 @@
         <v>5</v>
       </c>
       <c r="G103">
-        <v>525</v>
+        <v>375</v>
       </c>
       <c r="H103" s="8">
-        <v>2.1333333333333333E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="I103" s="10">
-        <v>41.500571428571426</v>
+        <v>39.789333333333332</v>
       </c>
       <c r="J103" s="16">
-        <v>1.9948000000000001E-3</v>
+        <v>1.5102200000000001E-3</v>
       </c>
       <c r="K103" s="16">
-        <v>2.8250143000000003</v>
+        <v>1.8615628799999999</v>
       </c>
       <c r="L103" s="21">
-        <v>1.4833348118405114E-14</v>
+        <v>1.5468578750210955E-14</v>
       </c>
       <c r="M103" s="21">
-        <v>2.1174835996058322E-16</v>
+        <v>2.2084568777386575E-16</v>
       </c>
       <c r="Q103" s="16">
-        <v>2.0045685999999998</v>
+        <v>0.94974728000000008</v>
       </c>
       <c r="R103" s="23">
-        <v>9.6685578236614547E-12</v>
+        <v>2.9094147727193586E-12</v>
       </c>
       <c r="S103" s="23">
-        <v>5.0820155852136305E-14</v>
+        <v>7.9947913515779821E-14</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.3">
@@ -6238,7 +6226,7 @@
         <v>2</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D104">
         <v>5</v>
@@ -6250,34 +6238,34 @@
         <v>5</v>
       </c>
       <c r="G104">
-        <v>700</v>
+        <v>525</v>
       </c>
       <c r="H104" s="8">
-        <v>2.4285714285714285E-2</v>
+        <v>2.1333333333333333E-2</v>
       </c>
       <c r="I104" s="10">
-        <v>43.141428571428577</v>
+        <v>41.500571428571426</v>
       </c>
       <c r="J104" s="16">
-        <v>2.5738999999999996E-3</v>
+        <v>1.9948000000000001E-3</v>
       </c>
       <c r="K104" s="16">
-        <v>4.0745186200000001</v>
+        <v>2.8250143000000003</v>
       </c>
       <c r="L104" s="21">
-        <v>3.8779438915317176E-13</v>
+        <v>1.4833348118405114E-14</v>
       </c>
       <c r="M104" s="21">
-        <v>2.1531211961687913E-16</v>
+        <v>2.1174835996058322E-16</v>
       </c>
       <c r="Q104" s="16">
-        <v>4.3959003600000006</v>
+        <v>2.0045685999999998</v>
       </c>
       <c r="R104" s="23">
-        <v>1.5402273032896525E-10</v>
+        <v>9.6685578236614547E-12</v>
       </c>
       <c r="S104" s="23">
-        <v>1.3596143244377566E-13</v>
+        <v>5.0820155852136305E-14</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.3">
@@ -6288,7 +6276,7 @@
         <v>2</v>
       </c>
       <c r="C105">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D105">
         <v>5</v>
@@ -6300,34 +6288,34 @@
         <v>5</v>
       </c>
       <c r="G105">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="H105" s="8">
-        <v>2.0222222222222221E-2</v>
+        <v>2.4285714285714285E-2</v>
       </c>
       <c r="I105" s="10">
-        <v>44.225555555555552</v>
+        <v>43.141428571428577</v>
       </c>
       <c r="J105" s="16">
-        <v>2.9292000000000003E-3</v>
+        <v>2.5738999999999996E-3</v>
       </c>
       <c r="K105" s="16">
-        <v>5.5390185399999998</v>
+        <v>4.0745186200000001</v>
       </c>
       <c r="L105" s="21">
-        <v>1.4901997469166348E-14</v>
+        <v>3.8779438915317176E-13</v>
       </c>
       <c r="M105" s="21">
-        <v>2.1025872780187197E-16</v>
+        <v>2.1531211961687913E-16</v>
       </c>
       <c r="Q105" s="16">
-        <v>8.3908084400000007</v>
+        <v>4.3959003600000006</v>
       </c>
       <c r="R105" s="23">
-        <v>9.3880357060867293E-11</v>
+        <v>1.5402273032896525E-10</v>
       </c>
       <c r="S105" s="23">
-        <v>3.3585867021730076E-13</v>
+        <v>1.3596143244377566E-13</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.3">
@@ -6338,7 +6326,7 @@
         <v>2</v>
       </c>
       <c r="C106">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D106">
         <v>5</v>
@@ -6347,37 +6335,37 @@
         <v>0</v>
       </c>
       <c r="F106">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G106">
-        <v>1125</v>
+        <v>900</v>
       </c>
       <c r="H106" s="8">
-        <v>1.2977777777777777E-2</v>
+        <v>2.0222222222222221E-2</v>
       </c>
       <c r="I106" s="10">
-        <v>45.380622222222222</v>
+        <v>44.225555555555552</v>
       </c>
       <c r="J106" s="16">
-        <v>3.96716E-3</v>
+        <v>2.9292000000000003E-3</v>
       </c>
       <c r="K106" s="16">
-        <v>7.6967464799999998</v>
+        <v>5.5390185399999998</v>
       </c>
       <c r="L106" s="21">
-        <v>1.5187790760508941E-14</v>
+        <v>1.4901997469166348E-14</v>
       </c>
       <c r="M106" s="21">
-        <v>2.0590819941881997E-16</v>
+        <v>2.1025872780187197E-16</v>
       </c>
       <c r="Q106" s="16">
-        <v>16.5025662</v>
+        <v>8.3908084400000007</v>
       </c>
       <c r="R106" s="23">
-        <v>4.6948410934586531E-9</v>
+        <v>9.3880357060867293E-11</v>
       </c>
       <c r="S106" s="23">
-        <v>1.2651012022538633E-11</v>
+        <v>3.3585867021730076E-13</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.3">
@@ -6388,7 +6376,7 @@
         <v>2</v>
       </c>
       <c r="C107">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D107">
         <v>5</v>
@@ -6400,34 +6388,34 @@
         <v>3</v>
       </c>
       <c r="G107">
-        <v>1375</v>
+        <v>1125</v>
       </c>
       <c r="H107" s="8">
-        <v>1.5854545454545454E-2</v>
+        <v>1.2977777777777777E-2</v>
       </c>
       <c r="I107" s="10">
-        <v>46.487854545454546</v>
+        <v>45.380622222222222</v>
       </c>
       <c r="J107" s="16">
-        <v>4.53806E-3</v>
+        <v>3.96716E-3</v>
       </c>
       <c r="K107" s="16">
-        <v>9.8030528199999996</v>
+        <v>7.6967464799999998</v>
       </c>
       <c r="L107" s="21">
-        <v>4.6464405109889013E-14</v>
+        <v>1.5187790760508941E-14</v>
       </c>
       <c r="M107" s="21">
-        <v>2.068181647074715E-16</v>
+        <v>2.0590819941881997E-16</v>
       </c>
       <c r="Q107" s="16">
-        <v>31.790000933333335</v>
+        <v>16.5025662</v>
       </c>
       <c r="R107" s="23">
-        <v>4.1617999672704015E-9</v>
+        <v>4.6948410934586531E-9</v>
       </c>
       <c r="S107" s="23">
-        <v>1.6428829304690858E-12</v>
+        <v>1.2651012022538633E-11</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.3">
@@ -6435,10 +6423,10 @@
         <v>5</v>
       </c>
       <c r="B108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D108">
         <v>5</v>
@@ -6447,37 +6435,37 @@
         <v>0</v>
       </c>
       <c r="F108">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G108">
-        <v>500</v>
+        <v>1375</v>
       </c>
       <c r="H108" s="8">
-        <v>6.5200000000000008E-2</v>
+        <v>1.5854545454545454E-2</v>
       </c>
       <c r="I108" s="10">
-        <v>35.793599999999998</v>
+        <v>46.487854545454546</v>
       </c>
       <c r="J108" s="16">
-        <v>1.0643599999999999E-3</v>
+        <v>4.53806E-3</v>
       </c>
       <c r="K108" s="16">
-        <v>3.2660372600000001</v>
+        <v>9.8030528199999996</v>
       </c>
       <c r="L108" s="21">
-        <v>4.150742209884161E-14</v>
+        <v>4.6464405109889013E-14</v>
       </c>
       <c r="M108" s="21">
-        <v>3.7494034505499536E-16</v>
+        <v>2.068181647074715E-16</v>
       </c>
       <c r="Q108" s="16">
-        <v>1.7813614600000001</v>
+        <v>31.790000933333335</v>
       </c>
       <c r="R108" s="23">
-        <v>3.6171699606032962E-13</v>
+        <v>4.1617999672704015E-9</v>
       </c>
       <c r="S108" s="23">
-        <v>5.1917279638947215E-15</v>
+        <v>1.6428829304690858E-12</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.3">
@@ -6488,7 +6476,7 @@
         <v>3</v>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D109">
         <v>5</v>
@@ -6500,34 +6488,34 @@
         <v>5</v>
       </c>
       <c r="G109">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="H109" s="8">
-        <v>4.9439999999999998E-2</v>
+        <v>6.5200000000000008E-2</v>
       </c>
       <c r="I109" s="10">
-        <v>36.797759999999997</v>
+        <v>35.793599999999998</v>
       </c>
       <c r="J109" s="16">
-        <v>2.25494E-3</v>
+        <v>1.0643599999999999E-3</v>
       </c>
       <c r="K109" s="16">
-        <v>8.1999447800000009</v>
+        <v>3.2660372600000001</v>
       </c>
       <c r="L109" s="21">
-        <v>3.6750446427367134E-14</v>
+        <v>4.150742209884161E-14</v>
       </c>
       <c r="M109" s="21">
-        <v>3.312044730280428E-16</v>
+        <v>3.7494034505499536E-16</v>
       </c>
       <c r="Q109" s="16">
-        <v>12.733139099999999</v>
+        <v>1.7813614600000001</v>
       </c>
       <c r="R109" s="23">
-        <v>5.3492872272192522E-12</v>
+        <v>3.6171699606032962E-13</v>
       </c>
       <c r="S109" s="23">
-        <v>4.4684299183482005E-14</v>
+        <v>5.1917279638947215E-15</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.3">
@@ -6538,46 +6526,46 @@
         <v>3</v>
       </c>
       <c r="C110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D110">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G110">
-        <v>2500</v>
+        <v>1250</v>
       </c>
       <c r="H110" s="8">
-        <v>4.2533333333333333E-2</v>
+        <v>4.9439999999999998E-2</v>
       </c>
       <c r="I110" s="10">
-        <v>38.0944</v>
+        <v>36.797759999999997</v>
       </c>
       <c r="J110" s="16">
-        <v>3.6237333333333337E-3</v>
+        <v>2.25494E-3</v>
       </c>
       <c r="K110" s="16">
-        <v>18.169718133333333</v>
+        <v>8.1999447800000009</v>
       </c>
       <c r="L110" s="21">
-        <v>3.5960977846467271E-14</v>
+        <v>3.6750446427367134E-14</v>
       </c>
       <c r="M110" s="21">
-        <v>3.1375495388067941E-16</v>
+        <v>3.312044730280428E-16</v>
       </c>
       <c r="Q110" s="16">
-        <v>106.53776413333333</v>
+        <v>12.733139099999999</v>
       </c>
       <c r="R110" s="23">
-        <v>3.5097177365450714E-11</v>
+        <v>5.3492872272192522E-12</v>
       </c>
       <c r="S110" s="23">
-        <v>3.9393172071118404E-14</v>
+        <v>4.4684299183482005E-14</v>
       </c>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.3">
@@ -6588,37 +6576,46 @@
         <v>3</v>
       </c>
       <c r="C111">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G111">
-        <v>4375</v>
+        <v>2500</v>
       </c>
       <c r="H111" s="8">
-        <v>4.3428571428571427E-2</v>
+        <v>4.2533333333333333E-2</v>
       </c>
       <c r="I111" s="10">
-        <v>40.537371428571426</v>
+        <v>38.0944</v>
       </c>
       <c r="J111" s="16">
-        <v>7.2175E-3</v>
+        <v>3.6237333333333337E-3</v>
       </c>
       <c r="K111" s="16">
-        <v>40.470895000000006</v>
+        <v>18.169718133333333</v>
       </c>
       <c r="L111" s="21">
-        <v>3.7320878384676091E-12</v>
+        <v>3.5960977846467271E-14</v>
       </c>
       <c r="M111" s="21">
-        <v>3.035776384633188E-16</v>
+        <v>3.1375495388067941E-16</v>
+      </c>
+      <c r="Q111" s="16">
+        <v>106.53776413333333</v>
+      </c>
+      <c r="R111" s="23">
+        <v>3.5097177365450714E-11</v>
+      </c>
+      <c r="S111" s="23">
+        <v>3.9393172071118404E-14</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.3">
@@ -6626,10 +6623,10 @@
         <v>5</v>
       </c>
       <c r="B112">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -6641,75 +6638,66 @@
         <v>0</v>
       </c>
       <c r="G112">
-        <v>3125</v>
+        <v>4375</v>
       </c>
       <c r="H112" s="8">
-        <v>9.1200000000000003E-2</v>
+        <v>4.3428571428571427E-2</v>
       </c>
       <c r="I112" s="10">
-        <v>36.86112</v>
+        <v>40.537371428571426</v>
       </c>
       <c r="J112" s="16">
-        <v>3.5699999999999998E-3</v>
+        <v>7.2175E-3</v>
       </c>
       <c r="K112" s="16">
-        <v>36.600457300000002</v>
+        <v>40.470895000000006</v>
       </c>
       <c r="L112" s="21">
-        <v>7.586296295965602E-14</v>
+        <v>3.7320878384676091E-12</v>
       </c>
       <c r="M112" s="21">
-        <v>5.0452484515548831E-16</v>
+        <v>3.035776384633188E-16</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C113">
         <v>2</v>
       </c>
       <c r="D113">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G113">
-        <v>108</v>
+        <v>3125</v>
       </c>
       <c r="H113" s="8">
-        <v>3.7037037037037035E-2</v>
+        <v>9.1200000000000003E-2</v>
       </c>
       <c r="I113" s="10">
-        <v>34.296296296296291</v>
+        <v>36.86112</v>
       </c>
       <c r="J113" s="16">
-        <v>5.7476000000000001E-4</v>
+        <v>3.5699999999999998E-3</v>
       </c>
       <c r="K113" s="16">
-        <v>0.49949194000000008</v>
+        <v>36.600457300000002</v>
       </c>
       <c r="L113" s="21">
-        <v>3.2951693518883698E-14</v>
+        <v>7.586296295965602E-14</v>
       </c>
       <c r="M113" s="21">
-        <v>3.2604089195961668E-16</v>
-      </c>
-      <c r="Q113" s="16">
-        <v>0.15657246</v>
-      </c>
-      <c r="R113" s="23">
-        <v>6.5121299890427066E-13</v>
-      </c>
-      <c r="S113" s="23">
-        <v>5.8327545996067954E-15</v>
+        <v>5.0452484515548831E-16</v>
       </c>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.3">
@@ -6720,7 +6708,7 @@
         <v>2</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <v>5</v>
@@ -6732,34 +6720,34 @@
         <v>5</v>
       </c>
       <c r="G114">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="H114" s="8">
-        <v>1.8518518518518517E-2</v>
+        <v>3.7037037037037035E-2</v>
       </c>
       <c r="I114" s="10">
-        <v>35.411111111111111</v>
+        <v>34.296296296296291</v>
       </c>
       <c r="J114" s="16">
-        <v>8.6555999999999992E-4</v>
+        <v>5.7476000000000001E-4</v>
       </c>
       <c r="K114" s="16">
-        <v>0.96189133999999998</v>
+        <v>0.49949194000000008</v>
       </c>
       <c r="L114" s="21">
-        <v>2.2280773584797067E-14</v>
+        <v>3.2951693518883698E-14</v>
       </c>
       <c r="M114" s="21">
-        <v>2.775353550537815E-16</v>
+        <v>3.2604089195961668E-16</v>
       </c>
       <c r="Q114" s="16">
-        <v>0.38666301999999997</v>
+        <v>0.15657246</v>
       </c>
       <c r="R114" s="23">
-        <v>1.4114124593626313E-13</v>
+        <v>6.5121299890427066E-13</v>
       </c>
       <c r="S114" s="23">
-        <v>5.8111683878486103E-15</v>
+        <v>5.8327545996067954E-15</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.3">
@@ -6770,7 +6758,7 @@
         <v>2</v>
       </c>
       <c r="C115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D115">
         <v>5</v>
@@ -6782,34 +6770,34 @@
         <v>5</v>
       </c>
       <c r="G115">
-        <v>360</v>
+        <v>216</v>
       </c>
       <c r="H115" s="8">
-        <v>2.6111111111111113E-2</v>
+        <v>1.8518518518518517E-2</v>
       </c>
       <c r="I115" s="10">
-        <v>38.152222222222221</v>
+        <v>35.411111111111111</v>
       </c>
       <c r="J115" s="16">
-        <v>1.1808600000000002E-3</v>
+        <v>8.6555999999999992E-4</v>
       </c>
       <c r="K115" s="16">
-        <v>1.7728660199999999</v>
+        <v>0.96189133999999998</v>
       </c>
       <c r="L115" s="21">
-        <v>2.2335024315275464E-14</v>
+        <v>2.2280773584797067E-14</v>
       </c>
       <c r="M115" s="21">
-        <v>2.6826869574784005E-16</v>
+        <v>2.775353550537815E-16</v>
       </c>
       <c r="Q115" s="16">
-        <v>0.89140035999999989</v>
+        <v>0.38666301999999997</v>
       </c>
       <c r="R115" s="23">
-        <v>3.4187730159447699E-12</v>
+        <v>1.4114124593626313E-13</v>
       </c>
       <c r="S115" s="23">
-        <v>1.6614278870848769E-14</v>
+        <v>5.8111683878486103E-15</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.3">
@@ -6820,7 +6808,7 @@
         <v>2</v>
       </c>
       <c r="C116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D116">
         <v>5</v>
@@ -6832,34 +6820,34 @@
         <v>5</v>
       </c>
       <c r="G116">
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="H116" s="8">
-        <v>1.740740740740741E-2</v>
+        <v>2.6111111111111113E-2</v>
       </c>
       <c r="I116" s="10">
-        <v>38.810740740740741</v>
+        <v>38.152222222222221</v>
       </c>
       <c r="J116" s="16">
-        <v>1.5954200000000002E-3</v>
+        <v>1.1808600000000002E-3</v>
       </c>
       <c r="K116" s="16">
-        <v>2.7022699399999999</v>
+        <v>1.7728660199999999</v>
       </c>
       <c r="L116" s="21">
-        <v>4.2929370064810047E-14</v>
+        <v>2.2335024315275464E-14</v>
       </c>
       <c r="M116" s="21">
-        <v>2.5682826709524424E-16</v>
+        <v>2.6826869574784005E-16</v>
       </c>
       <c r="Q116" s="16">
-        <v>2.0624484000000001</v>
+        <v>0.89140035999999989</v>
       </c>
       <c r="R116" s="23">
-        <v>2.8885148571738064E-12</v>
+        <v>3.4187730159447699E-12</v>
       </c>
       <c r="S116" s="23">
-        <v>3.3668543790314038E-14</v>
+        <v>1.6614278870848769E-14</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.3">
@@ -6870,7 +6858,7 @@
         <v>2</v>
       </c>
       <c r="C117">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D117">
         <v>5</v>
@@ -6882,34 +6870,34 @@
         <v>5</v>
       </c>
       <c r="G117">
-        <v>756</v>
+        <v>540</v>
       </c>
       <c r="H117" s="8">
-        <v>2.1693121693121691E-2</v>
+        <v>1.740740740740741E-2</v>
       </c>
       <c r="I117" s="10">
-        <v>41.141269841269839</v>
+        <v>38.810740740740741</v>
       </c>
       <c r="J117" s="16">
-        <v>2.0802400000000006E-3</v>
+        <v>1.5954200000000002E-3</v>
       </c>
       <c r="K117" s="16">
-        <v>4.4196238999999995</v>
+        <v>2.7022699399999999</v>
       </c>
       <c r="L117" s="21">
-        <v>2.4881551421311994E-14</v>
+        <v>4.2929370064810047E-14</v>
       </c>
       <c r="M117" s="21">
-        <v>2.5134843055559786E-16</v>
+        <v>2.5682826709524424E-16</v>
       </c>
       <c r="Q117" s="16">
-        <v>4.7410546200000008</v>
+        <v>2.0624484000000001</v>
       </c>
       <c r="R117" s="23">
-        <v>1.527669279158425E-11</v>
+        <v>2.8885148571738064E-12</v>
       </c>
       <c r="S117" s="23">
-        <v>5.4042023543274418E-14</v>
+        <v>3.3668543790314038E-14</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.3">
@@ -6920,7 +6908,7 @@
         <v>2</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D118">
         <v>5</v>
@@ -6929,37 +6917,37 @@
         <v>0</v>
       </c>
       <c r="F118">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G118">
-        <v>1008</v>
+        <v>756</v>
       </c>
       <c r="H118" s="8">
-        <v>2.103174603174603E-2</v>
+        <v>2.1693121693121691E-2</v>
       </c>
       <c r="I118" s="10">
-        <v>42.817261904761907</v>
+        <v>41.141269841269839</v>
       </c>
       <c r="J118" s="16">
-        <v>2.6401599999999999E-3</v>
+        <v>2.0802400000000006E-3</v>
       </c>
       <c r="K118" s="16">
-        <v>6.8269274400000004</v>
+        <v>4.4196238999999995</v>
       </c>
       <c r="L118" s="21">
-        <v>3.989523845769286E-13</v>
+        <v>2.4881551421311994E-14</v>
       </c>
       <c r="M118" s="21">
-        <v>2.4368210289639596E-16</v>
+        <v>2.5134843055559786E-16</v>
       </c>
       <c r="Q118" s="16">
-        <v>10.820841566666667</v>
+        <v>4.7410546200000008</v>
       </c>
       <c r="R118" s="23">
-        <v>5.4407729093785094E-10</v>
+        <v>1.527669279158425E-11</v>
       </c>
       <c r="S118" s="23">
-        <v>2.2454569809768172E-13</v>
+        <v>5.4042023543274418E-14</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.3">
@@ -6970,7 +6958,7 @@
         <v>2</v>
       </c>
       <c r="C119">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D119">
         <v>5</v>
@@ -6982,34 +6970,34 @@
         <v>3</v>
       </c>
       <c r="G119">
-        <v>1296</v>
+        <v>1008</v>
       </c>
       <c r="H119" s="8">
-        <v>1.1574074074074075E-2</v>
+        <v>2.103174603174603E-2</v>
       </c>
       <c r="I119" s="10">
-        <v>43.284104938271604</v>
+        <v>42.817261904761907</v>
       </c>
       <c r="J119" s="16">
-        <v>3.5624599999999999E-3</v>
+        <v>2.6401599999999999E-3</v>
       </c>
       <c r="K119" s="16">
-        <v>8.5879345600000008</v>
+        <v>6.8269274400000004</v>
       </c>
       <c r="L119" s="21">
-        <v>2.8940116364988023E-14</v>
+        <v>3.989523845769286E-13</v>
       </c>
       <c r="M119" s="21">
-        <v>2.38730216706383E-16</v>
+        <v>2.4368210289639596E-16</v>
       </c>
       <c r="Q119" s="16">
-        <v>23.0620048</v>
+        <v>10.820841566666667</v>
       </c>
       <c r="R119" s="23">
-        <v>1.6392681843978063E-9</v>
+        <v>5.4407729093785094E-10</v>
       </c>
       <c r="S119" s="23">
-        <v>3.8379790369403259E-12</v>
+        <v>2.2454569809768172E-13</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.3">
@@ -7020,46 +7008,46 @@
         <v>2</v>
       </c>
       <c r="C120">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D120">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G120">
-        <v>1620</v>
+        <v>1296</v>
       </c>
       <c r="H120" s="8">
-        <v>1.5637860082304524E-2</v>
+        <v>1.1574074074074075E-2</v>
       </c>
       <c r="I120" s="10">
-        <v>45.101851851851855</v>
+        <v>43.284104938271604</v>
       </c>
       <c r="J120" s="16">
-        <v>5.1473333333333336E-3</v>
+        <v>3.5624599999999999E-3</v>
       </c>
       <c r="K120" s="16">
-        <v>11.7958102</v>
+        <v>8.5879345600000008</v>
       </c>
       <c r="L120" s="21">
-        <v>2.7295618335376128E-14</v>
+        <v>2.8940116364988023E-14</v>
       </c>
       <c r="M120" s="21">
-        <v>2.338866286165698E-16</v>
+        <v>2.38730216706383E-16</v>
       </c>
       <c r="Q120" s="16">
-        <v>46.985986799999999</v>
+        <v>23.0620048</v>
       </c>
       <c r="R120" s="23">
-        <v>1.0093041449742465E-9</v>
+        <v>1.6392681843978063E-9</v>
       </c>
       <c r="S120" s="23">
-        <v>7.5560159000718528E-13</v>
+        <v>3.8379790369403259E-12</v>
       </c>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.3">
@@ -7070,7 +7058,7 @@
         <v>2</v>
       </c>
       <c r="C121">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D121">
         <v>3</v>
@@ -7082,34 +7070,34 @@
         <v>1</v>
       </c>
       <c r="G121">
-        <v>1980</v>
+        <v>1620</v>
       </c>
       <c r="H121" s="8">
-        <v>1.8013468013468013E-2</v>
+        <v>1.5637860082304524E-2</v>
       </c>
       <c r="I121" s="10">
-        <v>46.935690235690238</v>
+        <v>45.101851851851855</v>
       </c>
       <c r="J121" s="16">
-        <v>6.3254666666666673E-3</v>
+        <v>5.1473333333333336E-3</v>
       </c>
       <c r="K121" s="16">
-        <v>16.711406533333331</v>
+        <v>11.7958102</v>
       </c>
       <c r="L121" s="21">
-        <v>2.6698552285433069E-14</v>
+        <v>2.7295618335376128E-14</v>
       </c>
       <c r="M121" s="21">
-        <v>2.378899902841658E-16</v>
+        <v>2.338866286165698E-16</v>
       </c>
       <c r="Q121" s="16">
-        <v>102.3523395</v>
+        <v>46.985986799999999</v>
       </c>
       <c r="R121" s="23">
-        <v>2.2121601319005154E-8</v>
+        <v>1.0093041449742465E-9</v>
       </c>
       <c r="S121" s="23">
-        <v>6.3436970207141882E-11</v>
+        <v>7.5560159000718528E-13</v>
       </c>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.3">
@@ -7117,49 +7105,49 @@
         <v>6</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D122">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E122">
         <v>0</v>
       </c>
       <c r="F122">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G122">
-        <v>864</v>
+        <v>1980</v>
       </c>
       <c r="H122" s="8">
-        <v>7.1990740740740744E-2</v>
+        <v>1.8013468013468013E-2</v>
       </c>
       <c r="I122" s="10">
-        <v>35.144675925925924</v>
+        <v>46.935690235690238</v>
       </c>
       <c r="J122" s="16">
-        <v>1.1869600000000001E-3</v>
+        <v>6.3254666666666673E-3</v>
       </c>
       <c r="K122" s="16">
-        <v>6.5706771599999998</v>
+        <v>16.711406533333331</v>
       </c>
       <c r="L122" s="21">
-        <v>9.1869981011647501E-14</v>
+        <v>2.6698552285433069E-14</v>
       </c>
       <c r="M122" s="21">
-        <v>4.5479560188518037E-16</v>
+        <v>2.378899902841658E-16</v>
       </c>
       <c r="Q122" s="16">
-        <v>5.5931552</v>
+        <v>102.3523395</v>
       </c>
       <c r="R122" s="23">
-        <v>3.6933869379721647E-13</v>
+        <v>2.2121601319005154E-8</v>
       </c>
       <c r="S122" s="23">
-        <v>8.1950857685226958E-15</v>
+        <v>6.3436970207141882E-11</v>
       </c>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.3">
@@ -7170,96 +7158,96 @@
         <v>3</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E123">
         <v>0</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G123">
-        <v>2160</v>
+        <v>864</v>
       </c>
       <c r="H123" s="8">
-        <v>6.2808641975308638E-2</v>
+        <v>7.1990740740740744E-2</v>
       </c>
       <c r="I123" s="10">
-        <v>36.88148148148148</v>
+        <v>35.144675925925924</v>
       </c>
       <c r="J123" s="16">
-        <v>2.448733333333333E-3</v>
+        <v>1.1869600000000001E-3</v>
       </c>
       <c r="K123" s="16">
-        <v>19.087586566666669</v>
+        <v>6.5706771599999998</v>
       </c>
       <c r="L123" s="21">
-        <v>7.3427908324914067E-14</v>
+        <v>9.1869981011647501E-14</v>
       </c>
       <c r="M123" s="21">
-        <v>4.0285231789900132E-16</v>
+        <v>4.5479560188518037E-16</v>
       </c>
       <c r="Q123" s="16">
-        <v>63.633648000000001</v>
+        <v>5.5931552</v>
       </c>
       <c r="R123" s="23">
-        <v>8.4922962994015287E-12</v>
+        <v>3.6933869379721647E-13</v>
       </c>
       <c r="S123" s="23">
-        <v>1.1454824067240635E-13</v>
+        <v>8.1950857685226958E-15</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D124">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="F124">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G124">
-        <v>147</v>
+        <v>2160</v>
       </c>
       <c r="H124" s="8">
-        <v>5.8503401360544216E-2</v>
+        <v>6.2808641975308638E-2</v>
       </c>
       <c r="I124" s="10">
-        <v>35.657142857142858</v>
+        <v>36.88148148148148</v>
       </c>
       <c r="J124" s="16">
-        <v>5.7081999999999999E-4</v>
+        <v>2.448733333333333E-3</v>
       </c>
       <c r="K124" s="16">
-        <v>0.84981883999999996</v>
+        <v>19.087586566666669</v>
       </c>
       <c r="L124" s="21">
-        <v>4.3767370310090991E-14</v>
+        <v>7.3427908324914067E-14</v>
       </c>
       <c r="M124" s="21">
-        <v>3.6229968385960142E-16</v>
+        <v>4.0285231789900132E-16</v>
       </c>
       <c r="Q124" s="16">
-        <v>0.24576959999999998</v>
+        <v>63.633648000000001</v>
       </c>
       <c r="R124" s="23">
-        <v>4.682050455932844E-13</v>
+        <v>8.4922962994015287E-12</v>
       </c>
       <c r="S124" s="23">
-        <v>6.0345259148311915E-15</v>
+        <v>1.1454824067240635E-13</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.3">
@@ -7270,7 +7258,7 @@
         <v>2</v>
       </c>
       <c r="C125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D125">
         <v>5</v>
@@ -7282,34 +7270,34 @@
         <v>5</v>
       </c>
       <c r="G125">
-        <v>294</v>
+        <v>147</v>
       </c>
       <c r="H125" s="8">
-        <v>3.1292517006802717E-2</v>
+        <v>5.8503401360544216E-2</v>
       </c>
       <c r="I125" s="10">
-        <v>35.801360544217687</v>
+        <v>35.657142857142858</v>
       </c>
       <c r="J125" s="16">
-        <v>9.1216000000000008E-4</v>
+        <v>5.7081999999999999E-4</v>
       </c>
       <c r="K125" s="16">
-        <v>1.4183857999999998</v>
+        <v>0.84981883999999996</v>
       </c>
       <c r="L125" s="21">
-        <v>4.9959691434702983E-14</v>
+        <v>4.3767370310090991E-14</v>
       </c>
       <c r="M125" s="21">
-        <v>3.3077393165211246E-16</v>
+        <v>3.6229968385960142E-16</v>
       </c>
       <c r="Q125" s="16">
-        <v>0.67656028000000001</v>
+        <v>0.24576959999999998</v>
       </c>
       <c r="R125" s="23">
-        <v>1.5703322068510688E-13</v>
+        <v>4.682050455932844E-13</v>
       </c>
       <c r="S125" s="23">
-        <v>5.48789117115168E-15</v>
+        <v>6.0345259148311915E-15</v>
       </c>
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.3">
@@ -7320,7 +7308,7 @@
         <v>2</v>
       </c>
       <c r="C126">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D126">
         <v>5</v>
@@ -7332,34 +7320,34 @@
         <v>5</v>
       </c>
       <c r="G126">
-        <v>490</v>
+        <v>294</v>
       </c>
       <c r="H126" s="8">
-        <v>2.6122448979591838E-2</v>
+        <v>3.1292517006802717E-2</v>
       </c>
       <c r="I126" s="10">
-        <v>37.667755102040815</v>
+        <v>35.801360544217687</v>
       </c>
       <c r="J126" s="16">
-        <v>1.13868E-3</v>
+        <v>9.1216000000000008E-4</v>
       </c>
       <c r="K126" s="16">
-        <v>2.55513536</v>
+        <v>1.4183857999999998</v>
       </c>
       <c r="L126" s="21">
-        <v>4.1938934253409277E-14</v>
+        <v>4.9959691434702983E-14</v>
       </c>
       <c r="M126" s="21">
-        <v>2.9447861754664451E-16</v>
+        <v>3.3077393165211246E-16</v>
       </c>
       <c r="Q126" s="16">
-        <v>1.6750416399999999</v>
+        <v>0.67656028000000001</v>
       </c>
       <c r="R126" s="23">
-        <v>1.000249708918202E-11</v>
+        <v>1.5703322068510688E-13</v>
       </c>
       <c r="S126" s="23">
-        <v>1.9009847282048258E-13</v>
+        <v>5.48789117115168E-15</v>
       </c>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.3">
@@ -7370,7 +7358,7 @@
         <v>2</v>
       </c>
       <c r="C127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D127">
         <v>5</v>
@@ -7382,34 +7370,34 @@
         <v>5</v>
       </c>
       <c r="G127">
-        <v>735</v>
+        <v>490</v>
       </c>
       <c r="H127" s="8">
-        <v>1.5238095238095236E-2</v>
+        <v>2.6122448979591838E-2</v>
       </c>
       <c r="I127" s="10">
-        <v>38.644081632653062</v>
+        <v>37.667755102040815</v>
       </c>
       <c r="J127" s="16">
-        <v>1.5916200000000002E-3</v>
+        <v>1.13868E-3</v>
       </c>
       <c r="K127" s="16">
-        <v>4.0244523599999997</v>
+        <v>2.55513536</v>
       </c>
       <c r="L127" s="21">
-        <v>4.7144511320644433E-14</v>
+        <v>4.1938934253409277E-14</v>
       </c>
       <c r="M127" s="21">
-        <v>2.9218715468571781E-16</v>
+        <v>2.9447861754664451E-16</v>
       </c>
       <c r="Q127" s="16">
-        <v>4.4124036600000007</v>
+        <v>1.6750416399999999</v>
       </c>
       <c r="R127" s="23">
-        <v>1.6457575049729394E-11</v>
+        <v>1.000249708918202E-11</v>
       </c>
       <c r="S127" s="23">
-        <v>4.3295340963389813E-14</v>
+        <v>1.9009847282048258E-13</v>
       </c>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.3">
@@ -7420,7 +7408,7 @@
         <v>2</v>
       </c>
       <c r="C128">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D128">
         <v>5</v>
@@ -7429,37 +7417,37 @@
         <v>0</v>
       </c>
       <c r="F128">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G128">
-        <v>1029</v>
+        <v>735</v>
       </c>
       <c r="H128" s="8">
-        <v>1.6132167152575316E-2</v>
+        <v>1.5238095238095236E-2</v>
       </c>
       <c r="I128" s="10">
-        <v>40.696404275996109</v>
+        <v>38.644081632653062</v>
       </c>
       <c r="J128" s="16">
-        <v>2.3885600000000001E-3</v>
+        <v>1.5916200000000002E-3</v>
       </c>
       <c r="K128" s="16">
-        <v>6.4889960000000002</v>
+        <v>4.0244523599999997</v>
       </c>
       <c r="L128" s="21">
-        <v>4.4763491019978893E-14</v>
+        <v>4.7144511320644433E-14</v>
       </c>
       <c r="M128" s="21">
-        <v>2.8133949240236638E-16</v>
+        <v>2.9218715468571781E-16</v>
       </c>
       <c r="Q128" s="16">
-        <v>11.320121700000001</v>
+        <v>4.4124036600000007</v>
       </c>
       <c r="R128" s="23">
-        <v>7.0330988126507419E-11</v>
+        <v>1.6457575049729394E-11</v>
       </c>
       <c r="S128" s="23">
-        <v>9.3471650781588237E-14</v>
+        <v>4.3295340963389813E-14</v>
       </c>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.3">
@@ -7470,7 +7458,7 @@
         <v>2</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D129">
         <v>5</v>
@@ -7482,34 +7470,34 @@
         <v>3</v>
       </c>
       <c r="G129">
-        <v>1372</v>
+        <v>1029</v>
       </c>
       <c r="H129" s="8">
-        <v>1.6763848396501458E-2</v>
+        <v>1.6132167152575316E-2</v>
       </c>
       <c r="I129" s="10">
-        <v>42.527551020408161</v>
+        <v>40.696404275996109</v>
       </c>
       <c r="J129" s="16">
-        <v>3.0201999999999998E-3</v>
+        <v>2.3885600000000001E-3</v>
       </c>
       <c r="K129" s="16">
-        <v>9.5750178399999992</v>
+        <v>6.4889960000000002</v>
       </c>
       <c r="L129" s="21">
-        <v>6.165547267498417E-14</v>
+        <v>4.4763491019978893E-14</v>
       </c>
       <c r="M129" s="21">
-        <v>2.7313915013056855E-16</v>
+        <v>2.8133949240236638E-16</v>
       </c>
       <c r="Q129" s="16">
-        <v>26.342604733333335</v>
+        <v>11.320121700000001</v>
       </c>
       <c r="R129" s="23">
-        <v>1.1004515970393257E-9</v>
+        <v>7.0330988126507419E-11</v>
       </c>
       <c r="S129" s="23">
-        <v>1.7125696000692982E-12</v>
+        <v>9.3471650781588237E-14</v>
       </c>
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.3">
@@ -7520,46 +7508,46 @@
         <v>2</v>
       </c>
       <c r="C130">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D130">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E130">
         <v>0</v>
       </c>
       <c r="F130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G130">
-        <v>1764</v>
+        <v>1372</v>
       </c>
       <c r="H130" s="8">
-        <v>2.1352985638699924E-2</v>
+        <v>1.6763848396501458E-2</v>
       </c>
       <c r="I130" s="10">
-        <v>44.256046863189717</v>
+        <v>42.527551020408161</v>
       </c>
       <c r="J130" s="16">
-        <v>3.678866666666667E-3</v>
+        <v>3.0201999999999998E-3</v>
       </c>
       <c r="K130" s="16">
-        <v>13.549375533333333</v>
+        <v>9.5750178399999992</v>
       </c>
       <c r="L130" s="21">
-        <v>4.6109730141503417E-14</v>
+        <v>6.165547267498417E-14</v>
       </c>
       <c r="M130" s="21">
-        <v>2.691275822995595E-16</v>
+        <v>2.7313915013056855E-16</v>
       </c>
       <c r="Q130" s="16">
-        <v>61.218966299999998</v>
+        <v>26.342604733333335</v>
       </c>
       <c r="R130" s="23">
-        <v>6.3768511610331396E-9</v>
+        <v>1.1004515970393257E-9</v>
       </c>
       <c r="S130" s="23">
-        <v>1.8693299570517099E-11</v>
+        <v>1.7125696000692982E-12</v>
       </c>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.3">
@@ -7570,7 +7558,7 @@
         <v>2</v>
       </c>
       <c r="C131">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D131">
         <v>3</v>
@@ -7582,34 +7570,34 @@
         <v>1</v>
       </c>
       <c r="G131">
-        <v>2205</v>
+        <v>1764</v>
       </c>
       <c r="H131" s="8">
-        <v>1.7687074829931974E-2</v>
+        <v>2.1352985638699924E-2</v>
       </c>
       <c r="I131" s="10">
-        <v>45.458956916099773</v>
+        <v>44.256046863189717</v>
       </c>
       <c r="J131" s="16">
-        <v>4.5929999999999999E-3</v>
+        <v>3.678866666666667E-3</v>
       </c>
       <c r="K131" s="16">
-        <v>18.652216299999999</v>
+        <v>13.549375533333333</v>
       </c>
       <c r="L131" s="21">
-        <v>6.9914269748995936E-14</v>
+        <v>4.6109730141503417E-14</v>
       </c>
       <c r="M131" s="21">
-        <v>2.6717841905966925E-16</v>
+        <v>2.691275822995595E-16</v>
       </c>
       <c r="Q131" s="16">
-        <v>148.0203487</v>
+        <v>61.218966299999998</v>
       </c>
       <c r="R131" s="23">
-        <v>6.4137765172045439E-9</v>
+        <v>6.3768511610331396E-9</v>
       </c>
       <c r="S131" s="23">
-        <v>1.2826927984398869E-11</v>
+        <v>1.8693299570517099E-11</v>
       </c>
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.3">
@@ -7620,7 +7608,7 @@
         <v>2</v>
       </c>
       <c r="C132">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D132">
         <v>3</v>
@@ -7632,34 +7620,34 @@
         <v>1</v>
       </c>
       <c r="G132">
-        <v>2695</v>
+        <v>2205</v>
       </c>
       <c r="H132" s="8">
-        <v>1.5089672232529374E-2</v>
+        <v>1.7687074829931974E-2</v>
       </c>
       <c r="I132" s="10">
-        <v>45.776870748299324</v>
+        <v>45.458956916099773</v>
       </c>
       <c r="J132" s="16">
-        <v>5.7049333333333329E-3</v>
+        <v>4.5929999999999999E-3</v>
       </c>
       <c r="K132" s="16">
-        <v>23.026384266666668</v>
+        <v>18.652216299999999</v>
       </c>
       <c r="L132" s="21">
-        <v>4.3380543653820285E-14</v>
+        <v>6.9914269748995936E-14</v>
       </c>
       <c r="M132" s="21">
-        <v>2.6953202427085754E-16</v>
+        <v>2.6717841905966925E-16</v>
       </c>
       <c r="Q132" s="16">
-        <v>205.9769426</v>
+        <v>148.0203487</v>
       </c>
       <c r="R132" s="23">
-        <v>3.5186731033620087E-8</v>
+        <v>6.4137765172045439E-9</v>
       </c>
       <c r="S132" s="23">
-        <v>3.3139170574329736E-11</v>
+        <v>1.2826927984398869E-11</v>
       </c>
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.3">
@@ -7667,10 +7655,10 @@
         <v>7</v>
       </c>
       <c r="B133">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D133">
         <v>3</v>
@@ -7679,37 +7667,37 @@
         <v>0</v>
       </c>
       <c r="F133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G133">
-        <v>1372</v>
+        <v>2695</v>
       </c>
       <c r="H133" s="8">
-        <v>9.8882410106899896E-2</v>
+        <v>1.5089672232529374E-2</v>
       </c>
       <c r="I133" s="10">
-        <v>36.218901846452866</v>
+        <v>45.776870748299324</v>
       </c>
       <c r="J133" s="16">
-        <v>1.2840999999999998E-3</v>
+        <v>5.7049333333333329E-3</v>
       </c>
       <c r="K133" s="16">
-        <v>14.6364207</v>
+        <v>23.026384266666668</v>
       </c>
       <c r="L133" s="21">
-        <v>1.642595691875193E-13</v>
+        <v>4.3380543653820285E-14</v>
       </c>
       <c r="M133" s="21">
-        <v>5.3245455941085429E-16</v>
+        <v>2.6953202427085754E-16</v>
       </c>
       <c r="Q133" s="16">
-        <v>17.948652633333335</v>
+        <v>205.9769426</v>
       </c>
       <c r="R133" s="23">
-        <v>2.0200024259194053E-12</v>
+        <v>3.5186731033620087E-8</v>
       </c>
       <c r="S133" s="23">
-        <v>8.7584853768689402E-15</v>
+        <v>3.3139170574329736E-11</v>
       </c>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.3">
@@ -7720,87 +7708,87 @@
         <v>3</v>
       </c>
       <c r="C134">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G134">
-        <v>3430</v>
+        <v>1372</v>
       </c>
       <c r="H134" s="8">
-        <v>7.1720116618075799E-2</v>
+        <v>9.8882410106899896E-2</v>
       </c>
       <c r="I134" s="10">
-        <v>37.159183673469386</v>
+        <v>36.218901846452866</v>
       </c>
       <c r="J134" s="16">
-        <v>2.7268000000000001E-3</v>
+        <v>1.2840999999999998E-3</v>
       </c>
       <c r="K134" s="16">
-        <v>39.222806599999998</v>
+        <v>14.6364207</v>
       </c>
       <c r="L134" s="21">
-        <v>1.3577917115858543E-13</v>
+        <v>1.642595691875193E-13</v>
       </c>
       <c r="M134" s="21">
-        <v>4.6700913246606915E-16</v>
+        <v>5.3245455941085429E-16</v>
+      </c>
+      <c r="Q134" s="16">
+        <v>17.948652633333335</v>
+      </c>
+      <c r="R134" s="23">
+        <v>2.0200024259194053E-12</v>
+      </c>
+      <c r="S134" s="23">
+        <v>8.7584853768689402E-15</v>
       </c>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D135">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E135">
         <v>0</v>
       </c>
       <c r="F135">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G135">
-        <v>300</v>
-      </c>
-      <c r="H135" s="49">
-        <v>6.13E-2</v>
-      </c>
-      <c r="I135" s="50">
-        <v>34.5</v>
-      </c>
-      <c r="J135" s="51">
-        <v>7.4599999999999996E-3</v>
-      </c>
-      <c r="K135" s="51">
-        <v>2.375</v>
-      </c>
-      <c r="L135" s="52">
-        <v>1.2999999999999999E-12</v>
-      </c>
-      <c r="M135" s="52">
-        <v>5.34E-16</v>
-      </c>
-      <c r="Q135" s="16">
-        <v>0.88176655999999998</v>
-      </c>
-      <c r="R135" s="23">
-        <v>6.1198168891026161E-13</v>
-      </c>
-      <c r="S135" s="23">
-        <v>9.4429430014736385E-15</v>
+        <v>3430</v>
+      </c>
+      <c r="H135" s="8">
+        <v>7.1720116618075799E-2</v>
+      </c>
+      <c r="I135" s="10">
+        <v>37.159183673469386</v>
+      </c>
+      <c r="J135" s="16">
+        <v>2.7268000000000001E-3</v>
+      </c>
+      <c r="K135" s="16">
+        <v>39.222806599999998</v>
+      </c>
+      <c r="L135" s="21">
+        <v>1.3577917115858543E-13</v>
+      </c>
+      <c r="M135" s="21">
+        <v>4.6700913246606915E-16</v>
       </c>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.3">
@@ -7811,7 +7799,7 @@
         <v>2</v>
       </c>
       <c r="C136">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D136">
         <v>5</v>
@@ -7823,34 +7811,34 @@
         <v>5</v>
       </c>
       <c r="G136">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H136" s="49">
-        <v>4.36E-2</v>
+        <v>6.13E-2</v>
       </c>
       <c r="I136" s="50">
-        <v>36.137999999999998</v>
+        <v>34.5</v>
       </c>
       <c r="J136" s="51">
-        <v>2.0000000000000001E-4</v>
+        <v>7.4599999999999996E-3</v>
       </c>
       <c r="K136" s="51">
-        <v>3.9319000000000002</v>
+        <v>2.375</v>
       </c>
       <c r="L136" s="52">
-        <v>2.4199999999999998E-13</v>
+        <v>1.2999999999999999E-12</v>
       </c>
       <c r="M136" s="52">
-        <v>4.5899999999999996E-16</v>
+        <v>5.34E-16</v>
       </c>
       <c r="Q136" s="16">
-        <v>2.8232591999999999</v>
+        <v>0.88176655999999998</v>
       </c>
       <c r="R136" s="23">
-        <v>5.0217809093392962E-12</v>
+        <v>6.1198168891026161E-13</v>
       </c>
       <c r="S136" s="23">
-        <v>5.9206065875100495E-14</v>
+        <v>9.4429430014736385E-15</v>
       </c>
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.3">
@@ -7861,7 +7849,7 @@
         <v>2</v>
       </c>
       <c r="C137">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D137">
         <v>5</v>
@@ -7873,34 +7861,34 @@
         <v>5</v>
       </c>
       <c r="G137">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H137" s="49">
-        <v>3.7199999999999997E-2</v>
+        <v>4.36E-2</v>
       </c>
       <c r="I137" s="50">
-        <v>37.22</v>
+        <v>36.137999999999998</v>
       </c>
       <c r="J137" s="51">
-        <v>1E-3</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="K137" s="51">
-        <v>6.31</v>
+        <v>3.9319000000000002</v>
       </c>
       <c r="L137" s="52">
-        <v>2.37E-13</v>
+        <v>2.4199999999999998E-13</v>
       </c>
       <c r="M137" s="52">
-        <v>4.2600000000000002E-16</v>
+        <v>4.5899999999999996E-16</v>
       </c>
       <c r="Q137" s="16">
-        <v>9.4948389399999993</v>
+        <v>2.8232591999999999</v>
       </c>
       <c r="R137" s="23">
-        <v>5.4344423379448989E-12</v>
+        <v>5.0217809093392962E-12</v>
       </c>
       <c r="S137" s="23">
-        <v>2.6273268378747125E-14</v>
+        <v>5.9206065875100495E-14</v>
       </c>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.3">
@@ -7911,46 +7899,46 @@
         <v>2</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D138">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E138">
         <v>0</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G138">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="H138" s="49">
-        <v>2.0400000000000001E-2</v>
+        <v>3.7199999999999997E-2</v>
       </c>
       <c r="I138" s="50">
-        <v>38.636000000000003</v>
+        <v>37.22</v>
       </c>
       <c r="J138" s="51">
-        <v>1.8703333333333332E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="K138" s="51">
-        <v>10.183</v>
+        <v>6.31</v>
       </c>
       <c r="L138" s="52">
-        <v>2.41E-14</v>
+        <v>2.37E-13</v>
       </c>
       <c r="M138" s="52">
-        <v>4.0599999999999999E-16</v>
+        <v>4.2600000000000002E-16</v>
       </c>
       <c r="Q138" s="16">
-        <v>31.7727264</v>
+        <v>9.4948389399999993</v>
       </c>
       <c r="R138" s="23">
-        <v>1.0818483964618036E-11</v>
+        <v>5.4344423379448989E-12</v>
       </c>
       <c r="S138" s="23">
-        <v>4.5887318376204904E-14</v>
+        <v>2.6273268378747125E-14</v>
       </c>
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.3">
@@ -7961,7 +7949,7 @@
         <v>2</v>
       </c>
       <c r="C139">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -7973,144 +7961,194 @@
         <v>1</v>
       </c>
       <c r="G139">
+        <v>1500</v>
+      </c>
+      <c r="H139" s="49">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="I139" s="50">
+        <v>38.636000000000003</v>
+      </c>
+      <c r="J139" s="51">
+        <v>1.8703333333333332E-3</v>
+      </c>
+      <c r="K139" s="51">
+        <v>10.183</v>
+      </c>
+      <c r="L139" s="52">
+        <v>2.41E-14</v>
+      </c>
+      <c r="M139" s="52">
+        <v>4.0599999999999999E-16</v>
+      </c>
+      <c r="Q139" s="16">
+        <v>31.7727264</v>
+      </c>
+      <c r="R139" s="23">
+        <v>1.0818483964618036E-11</v>
+      </c>
+      <c r="S139" s="23">
+        <v>4.5887318376204904E-14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>10</v>
+      </c>
+      <c r="B140">
+        <v>2</v>
+      </c>
+      <c r="C140">
+        <v>6</v>
+      </c>
+      <c r="D140">
+        <v>3</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140">
         <v>2100</v>
       </c>
-      <c r="H139" s="49">
+      <c r="H140" s="49">
         <v>2.41E-2</v>
       </c>
-      <c r="I139" s="50">
+      <c r="I140" s="50">
         <v>40.487000000000002</v>
       </c>
-      <c r="J139" s="51">
+      <c r="J140" s="51">
         <v>2.7100000000000002E-3</v>
       </c>
-      <c r="K139" s="51">
+      <c r="K140" s="51">
         <v>16.943999999999999</v>
       </c>
-      <c r="L139" s="52">
+      <c r="L140" s="52">
         <v>2.5900000000000001E-13</v>
       </c>
-      <c r="M139" s="52">
+      <c r="M140" s="52">
         <v>3.954135446458232E-16</v>
       </c>
-      <c r="Q139" s="16">
+      <c r="Q140" s="16">
         <v>105.6478079</v>
       </c>
-      <c r="R139" s="23">
+      <c r="R140" s="23">
         <v>3.549609196044045E-9</v>
       </c>
-      <c r="S139" s="23">
+      <c r="S140" s="23">
         <v>2.5864833288222837E-12</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A140" s="12">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A141" s="12">
         <v>15</v>
       </c>
-      <c r="B140" s="12">
-        <v>2</v>
-      </c>
-      <c r="C140" s="12">
-        <v>2</v>
-      </c>
-      <c r="D140" s="12">
-        <v>5</v>
-      </c>
-      <c r="E140" s="12">
-        <v>0</v>
-      </c>
-      <c r="F140" s="12">
-        <v>5</v>
-      </c>
-      <c r="G140" s="12">
+      <c r="B141" s="12">
+        <v>2</v>
+      </c>
+      <c r="C141" s="12">
+        <v>2</v>
+      </c>
+      <c r="D141" s="12">
+        <v>5</v>
+      </c>
+      <c r="E141" s="12">
+        <v>0</v>
+      </c>
+      <c r="F141" s="12">
+        <v>5</v>
+      </c>
+      <c r="G141" s="12">
         <v>675</v>
       </c>
-      <c r="H140" s="13">
+      <c r="H141" s="13">
         <v>5.8900000000000001E-2</v>
       </c>
-      <c r="I140" s="14">
+      <c r="I141" s="14">
         <v>34.292000000000002</v>
       </c>
-      <c r="J140" s="17">
+      <c r="J141" s="17">
         <v>6.7227999999999993E-4</v>
       </c>
-      <c r="K140" s="17">
+      <c r="K141" s="17">
         <v>5.9416000000000002</v>
       </c>
-      <c r="L140" s="22">
+      <c r="L141" s="22">
         <v>0.17199566509229403</v>
       </c>
-      <c r="M140" s="22">
+      <c r="M141" s="22">
         <v>8.7618527618346915E-16</v>
       </c>
-      <c r="N140" s="17"/>
-      <c r="O140" s="24"/>
-      <c r="P140" s="24"/>
-      <c r="Q140" s="17">
+      <c r="N141" s="17"/>
+      <c r="O141" s="24"/>
+      <c r="P141" s="24"/>
+      <c r="Q141" s="17">
         <v>4.5755377399999997</v>
       </c>
-      <c r="R140" s="24">
+      <c r="R141" s="24">
         <v>6.2632535913292558E-12</v>
       </c>
-      <c r="S140" s="24">
+      <c r="S141" s="24">
         <v>1.6035885772533078E-13</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A141">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A142">
         <v>20</v>
       </c>
-      <c r="B141">
-        <v>2</v>
-      </c>
-      <c r="C141">
-        <v>2</v>
-      </c>
-      <c r="D141">
-        <v>3</v>
-      </c>
-      <c r="E141">
-        <v>0</v>
-      </c>
-      <c r="F141">
-        <v>3</v>
-      </c>
-      <c r="G141">
+      <c r="B142">
+        <v>2</v>
+      </c>
+      <c r="C142">
+        <v>2</v>
+      </c>
+      <c r="D142">
+        <v>3</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="F142">
+        <v>3</v>
+      </c>
+      <c r="G142">
         <v>1200</v>
       </c>
-      <c r="H141" s="49">
+      <c r="H142" s="49">
         <v>8.1100000000000005E-2</v>
       </c>
-      <c r="I141" s="50">
+      <c r="I142" s="50">
         <v>35.186999999999998</v>
       </c>
-      <c r="J141" s="51">
+      <c r="J142" s="51">
         <v>7.9946666666666673E-4</v>
       </c>
-      <c r="K141" s="51">
+      <c r="K142" s="51">
         <v>16.3</v>
       </c>
-      <c r="L141" s="52">
+      <c r="L142" s="52">
         <v>8.84E-11</v>
       </c>
-      <c r="M141" s="52">
+      <c r="M142" s="52">
         <v>3.5399999999999999E-15</v>
       </c>
-      <c r="Q141" s="16">
+      <c r="Q142" s="16">
         <v>18.132396066666669</v>
       </c>
-      <c r="R141" s="23">
+      <c r="R142" s="23">
         <v>1.1242075415885675E-12</v>
       </c>
-      <c r="S141" s="23">
+      <c r="S142" s="23">
         <v>3.4699449019803669E-14</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X141">
-    <sortCondition ref="A2:A141"/>
-    <sortCondition ref="B2:B141"/>
-    <sortCondition ref="C2:C141"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X142">
+    <sortCondition ref="A2:A142"/>
+    <sortCondition ref="B2:B142"/>
+    <sortCondition ref="C2:C142"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
